--- a/templates/periodontal-chart-full.xlsx
+++ b/templates/periodontal-chart-full.xlsx
@@ -770,7 +770,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="009A9AA0"/>
@@ -786,6 +786,12 @@
       <font>
         <strike val="1"/>
         <color rgb="009A9AA0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="000A66D6"/>
+        <u val="single"/>
       </font>
     </dxf>
     <dxf>
@@ -902,7 +908,7 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="twoCell">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
       <colOff>0</colOff>
@@ -910,14 +916,14 @@
       <rowOff>0</rowOff>
     </from>
     <to>
-      <col>50</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="1" name="Tooth 18 buccal" descr="Tooth 18 buccal"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -932,9 +938,1839 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Tooth 18 palatal" descr="Tooth 18 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Tooth 17 buccal" descr="Tooth 17 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Tooth 17 palatal" descr="Tooth 17 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Tooth 16 buccal" descr="Tooth 16 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Tooth 16 palatal" descr="Tooth 16 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Tooth 15 buccal" descr="Tooth 15 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Tooth 15 palatal" descr="Tooth 15 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Tooth 14 buccal" descr="Tooth 14 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Tooth 14 palatal" descr="Tooth 14 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Tooth 13 buccal" descr="Tooth 13 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Tooth 13 palatal" descr="Tooth 13 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Tooth 12 buccal" descr="Tooth 12 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Tooth 12 palatal" descr="Tooth 12 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Tooth 11 buccal" descr="Tooth 11 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Tooth 11 palatal" descr="Tooth 11 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Tooth 21 buccal" descr="Tooth 21 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Tooth 21 palatal" descr="Tooth 21 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Tooth 22 buccal" descr="Tooth 22 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Tooth 22 palatal" descr="Tooth 22 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Tooth 23 buccal" descr="Tooth 23 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Tooth 23 palatal" descr="Tooth 23 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Tooth 24 buccal" descr="Tooth 24 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Tooth 24 palatal" descr="Tooth 24 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Tooth 25 buccal" descr="Tooth 25 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Tooth 25 palatal" descr="Tooth 25 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Tooth 26 buccal" descr="Tooth 26 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Tooth 26 palatal" descr="Tooth 26 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Tooth 27 buccal" descr="Tooth 27 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Tooth 27 palatal" descr="Tooth 27 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Tooth 28 buccal" descr="Tooth 28 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Tooth 28 palatal" descr="Tooth 28 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Tooth 48 lingual" descr="Tooth 48 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Tooth 48 buccal" descr="Tooth 48 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Tooth 47 lingual" descr="Tooth 47 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Tooth 47 buccal" descr="Tooth 47 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Tooth 46 lingual" descr="Tooth 46 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Tooth 46 buccal" descr="Tooth 46 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Tooth 45 lingual" descr="Tooth 45 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Tooth 45 buccal" descr="Tooth 45 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Tooth 44 lingual" descr="Tooth 44 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Tooth 44 buccal" descr="Tooth 44 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Tooth 43 lingual" descr="Tooth 43 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Tooth 43 buccal" descr="Tooth 43 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Tooth 42 lingual" descr="Tooth 42 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Tooth 42 buccal" descr="Tooth 42 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Tooth 41 lingual" descr="Tooth 41 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Tooth 41 buccal" descr="Tooth 41 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Tooth 31 lingual" descr="Tooth 31 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Tooth 31 buccal" descr="Tooth 31 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Tooth 32 lingual" descr="Tooth 32 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Tooth 32 buccal" descr="Tooth 32 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Tooth 33 lingual" descr="Tooth 33 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Tooth 33 buccal" descr="Tooth 33 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Tooth 34 lingual" descr="Tooth 34 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Tooth 34 buccal" descr="Tooth 34 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Tooth 35 lingual" descr="Tooth 35 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Tooth 35 buccal" descr="Tooth 35 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Tooth 36 lingual" descr="Tooth 36 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Tooth 36 buccal" descr="Tooth 36 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Tooth 37 lingual" descr="Tooth 37 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Tooth 37 buccal" descr="Tooth 37 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
       <colOff>0</colOff>
       <row>36</row>
       <rowOff>0</rowOff>
@@ -942,16 +2778,46 @@
     <to>
       <col>50</col>
       <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="63" name="Tooth 38 lingual" descr="Tooth 38 lingual"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Tooth 38 buccal" descr="Tooth 38 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -967,7 +2833,7 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="twoCell">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
       <colOff>0</colOff>
@@ -975,14 +2841,14 @@
       <rowOff>0</rowOff>
     </from>
     <to>
-      <col>50</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="1" name="Tooth 18 buccal" descr="Tooth 18 buccal"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -997,9 +2863,1839 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Tooth 18 palatal" descr="Tooth 18 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Tooth 17 buccal" descr="Tooth 17 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Tooth 17 palatal" descr="Tooth 17 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Tooth 16 buccal" descr="Tooth 16 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Tooth 16 palatal" descr="Tooth 16 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Tooth 15 buccal" descr="Tooth 15 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Tooth 15 palatal" descr="Tooth 15 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Tooth 14 buccal" descr="Tooth 14 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Tooth 14 palatal" descr="Tooth 14 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Tooth 13 buccal" descr="Tooth 13 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Tooth 13 palatal" descr="Tooth 13 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Tooth 12 buccal" descr="Tooth 12 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Tooth 12 palatal" descr="Tooth 12 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Tooth 11 buccal" descr="Tooth 11 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Tooth 11 palatal" descr="Tooth 11 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Tooth 21 buccal" descr="Tooth 21 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Tooth 21 palatal" descr="Tooth 21 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Tooth 22 buccal" descr="Tooth 22 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Tooth 22 palatal" descr="Tooth 22 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Tooth 23 buccal" descr="Tooth 23 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Tooth 23 palatal" descr="Tooth 23 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Tooth 24 buccal" descr="Tooth 24 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Tooth 24 palatal" descr="Tooth 24 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Tooth 25 buccal" descr="Tooth 25 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Tooth 25 palatal" descr="Tooth 25 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Tooth 26 buccal" descr="Tooth 26 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Tooth 26 palatal" descr="Tooth 26 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Tooth 27 buccal" descr="Tooth 27 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Tooth 27 palatal" descr="Tooth 27 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Tooth 28 buccal" descr="Tooth 28 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Tooth 28 palatal" descr="Tooth 28 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Tooth 48 lingual" descr="Tooth 48 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Tooth 48 buccal" descr="Tooth 48 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Tooth 47 lingual" descr="Tooth 47 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Tooth 47 buccal" descr="Tooth 47 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Tooth 46 lingual" descr="Tooth 46 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Tooth 46 buccal" descr="Tooth 46 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Tooth 45 lingual" descr="Tooth 45 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Tooth 45 buccal" descr="Tooth 45 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Tooth 44 lingual" descr="Tooth 44 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Tooth 44 buccal" descr="Tooth 44 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Tooth 43 lingual" descr="Tooth 43 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Tooth 43 buccal" descr="Tooth 43 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Tooth 42 lingual" descr="Tooth 42 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Tooth 42 buccal" descr="Tooth 42 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Tooth 41 lingual" descr="Tooth 41 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Tooth 41 buccal" descr="Tooth 41 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Tooth 31 lingual" descr="Tooth 31 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Tooth 31 buccal" descr="Tooth 31 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Tooth 32 lingual" descr="Tooth 32 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Tooth 32 buccal" descr="Tooth 32 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Tooth 33 lingual" descr="Tooth 33 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Tooth 33 buccal" descr="Tooth 33 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Tooth 34 lingual" descr="Tooth 34 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Tooth 34 buccal" descr="Tooth 34 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Tooth 35 lingual" descr="Tooth 35 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Tooth 35 buccal" descr="Tooth 35 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Tooth 36 lingual" descr="Tooth 36 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Tooth 36 buccal" descr="Tooth 36 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Tooth 37 lingual" descr="Tooth 37 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Tooth 37 buccal" descr="Tooth 37 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
       <colOff>0</colOff>
       <row>36</row>
       <rowOff>0</rowOff>
@@ -1007,16 +4703,46 @@
     <to>
       <col>50</col>
       <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="63" name="Tooth 38 lingual" descr="Tooth 38 lingual"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Tooth 38 buccal" descr="Tooth 38 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1032,7 +4758,7 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="twoCell">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
       <colOff>0</colOff>
@@ -1040,14 +4766,14 @@
       <rowOff>0</rowOff>
     </from>
     <to>
-      <col>50</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="1" name="Tooth 18 buccal" descr="Tooth 18 buccal"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -1062,9 +4788,1839 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Tooth 18 palatal" descr="Tooth 18 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Tooth 17 buccal" descr="Tooth 17 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Tooth 17 palatal" descr="Tooth 17 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Tooth 16 buccal" descr="Tooth 16 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Tooth 16 palatal" descr="Tooth 16 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Tooth 15 buccal" descr="Tooth 15 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Tooth 15 palatal" descr="Tooth 15 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Tooth 14 buccal" descr="Tooth 14 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Tooth 14 palatal" descr="Tooth 14 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Tooth 13 buccal" descr="Tooth 13 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Tooth 13 palatal" descr="Tooth 13 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Tooth 12 buccal" descr="Tooth 12 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Tooth 12 palatal" descr="Tooth 12 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Tooth 11 buccal" descr="Tooth 11 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Tooth 11 palatal" descr="Tooth 11 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Tooth 21 buccal" descr="Tooth 21 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Tooth 21 palatal" descr="Tooth 21 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Tooth 22 buccal" descr="Tooth 22 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Tooth 22 palatal" descr="Tooth 22 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Tooth 23 buccal" descr="Tooth 23 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Tooth 23 palatal" descr="Tooth 23 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Tooth 24 buccal" descr="Tooth 24 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Tooth 24 palatal" descr="Tooth 24 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Tooth 25 buccal" descr="Tooth 25 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Tooth 25 palatal" descr="Tooth 25 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Tooth 26 buccal" descr="Tooth 26 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Tooth 26 palatal" descr="Tooth 26 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Tooth 27 buccal" descr="Tooth 27 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Tooth 27 palatal" descr="Tooth 27 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>98277</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Tooth 28 buccal" descr="Tooth 28 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>136450</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>240181</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Tooth 28 palatal" descr="Tooth 28 palatal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Tooth 48 lingual" descr="Tooth 48 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Tooth 48 buccal" descr="Tooth 48 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Tooth 47 lingual" descr="Tooth 47 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Tooth 47 buccal" descr="Tooth 47 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Tooth 46 lingual" descr="Tooth 46 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Tooth 46 buccal" descr="Tooth 46 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Tooth 45 lingual" descr="Tooth 45 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Tooth 45 buccal" descr="Tooth 45 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Tooth 44 lingual" descr="Tooth 44 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Tooth 44 buccal" descr="Tooth 44 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Tooth 43 lingual" descr="Tooth 43 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Tooth 43 buccal" descr="Tooth 43 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Tooth 42 lingual" descr="Tooth 42 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Tooth 42 buccal" descr="Tooth 42 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Tooth 41 lingual" descr="Tooth 41 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Tooth 41 buccal" descr="Tooth 41 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Tooth 31 lingual" descr="Tooth 31 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Tooth 31 buccal" descr="Tooth 31 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Tooth 32 lingual" descr="Tooth 32 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Tooth 32 buccal" descr="Tooth 32 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Tooth 33 lingual" descr="Tooth 33 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>32</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Tooth 33 buccal" descr="Tooth 33 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Tooth 34 lingual" descr="Tooth 34 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Tooth 34 buccal" descr="Tooth 34 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Tooth 35 lingual" descr="Tooth 35 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>38</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Tooth 35 buccal" descr="Tooth 35 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Tooth 36 lingual" descr="Tooth 36 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>41</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Tooth 36 buccal" descr="Tooth 36 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Tooth 37 lingual" descr="Tooth 37 lingual"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>44</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Tooth 37 buccal" descr="Tooth 37 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
       <colOff>0</colOff>
       <row>36</row>
       <rowOff>0</rowOff>
@@ -1072,16 +6628,46 @@
     <to>
       <col>50</col>
       <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
+      <row>39</row>
+      <rowOff>98801</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="63" name="Tooth 38 lingual" descr="Tooth 38 lingual"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>47</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>136973</rowOff>
+    </from>
+    <to>
+      <col>50</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>235775</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Tooth 38 buccal" descr="Tooth 38 buccal"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2693,7 +8279,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20.94" customHeight="1">
+    <row r="16" ht="18.89" customHeight="1">
       <c r="A16" s="41" t="n"/>
       <c r="B16" s="42" t="n"/>
       <c r="C16" s="42" t="n"/>
@@ -2759,7 +8345,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="20.94" customHeight="1">
+    <row r="17" ht="18.89" customHeight="1">
       <c r="A17" s="47" t="n"/>
       <c r="B17" s="48" t="n"/>
       <c r="C17" s="48" t="n"/>
@@ -2825,7 +8411,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="20.94" customHeight="1">
+    <row r="18" ht="18.89" customHeight="1">
       <c r="A18" s="47" t="n"/>
       <c r="B18" s="48" t="n"/>
       <c r="C18" s="48" t="n"/>
@@ -2891,7 +8477,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="20.94" customHeight="1">
+    <row r="19" ht="18.89" customHeight="1">
       <c r="A19" s="47" t="n"/>
       <c r="B19" s="48" t="n"/>
       <c r="C19" s="48" t="n"/>
@@ -2944,7 +8530,7 @@
       <c r="AX19" s="48" t="n"/>
       <c r="AY19" s="50" t="n"/>
     </row>
-    <row r="20" ht="20.94" customHeight="1">
+    <row r="20" ht="18.89" customHeight="1">
       <c r="A20" s="47" t="n"/>
       <c r="B20" s="48" t="n"/>
       <c r="C20" s="48" t="n"/>
@@ -3012,7 +8598,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20.94" customHeight="1">
+    <row r="21" ht="18.89" customHeight="1">
       <c r="A21" s="47" t="n"/>
       <c r="B21" s="48" t="n"/>
       <c r="C21" s="48" t="n"/>
@@ -3078,7 +8664,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20.94" customHeight="1">
+    <row r="22" ht="18.89" customHeight="1">
       <c r="A22" s="51" t="n"/>
       <c r="B22" s="52" t="n"/>
       <c r="C22" s="52" t="n"/>
@@ -4347,7 +9933,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20.76" customHeight="1">
+    <row r="37" ht="18.59" customHeight="1">
       <c r="A37" s="41" t="n"/>
       <c r="B37" s="42" t="n"/>
       <c r="C37" s="42" t="n"/>
@@ -4400,7 +9986,7 @@
       <c r="AX37" s="42" t="n"/>
       <c r="AY37" s="44" t="n"/>
     </row>
-    <row r="38" ht="20.76" customHeight="1">
+    <row r="38" ht="18.59" customHeight="1">
       <c r="A38" s="47" t="n"/>
       <c r="B38" s="48" t="n"/>
       <c r="C38" s="48" t="n"/>
@@ -4453,7 +10039,7 @@
       <c r="AX38" s="48" t="n"/>
       <c r="AY38" s="50" t="n"/>
     </row>
-    <row r="39" ht="20.76" customHeight="1">
+    <row r="39" ht="18.59" customHeight="1">
       <c r="A39" s="47" t="n"/>
       <c r="B39" s="48" t="n"/>
       <c r="C39" s="48" t="n"/>
@@ -4506,7 +10092,7 @@
       <c r="AX39" s="48" t="n"/>
       <c r="AY39" s="50" t="n"/>
     </row>
-    <row r="40" ht="20.76" customHeight="1">
+    <row r="40" ht="18.59" customHeight="1">
       <c r="A40" s="47" t="n"/>
       <c r="B40" s="48" t="n"/>
       <c r="C40" s="48" t="n"/>
@@ -4559,7 +10145,7 @@
       <c r="AX40" s="48" t="n"/>
       <c r="AY40" s="50" t="n"/>
     </row>
-    <row r="41" ht="20.76" customHeight="1">
+    <row r="41" ht="18.59" customHeight="1">
       <c r="A41" s="47" t="n"/>
       <c r="B41" s="48" t="n"/>
       <c r="C41" s="48" t="n"/>
@@ -4612,7 +10198,7 @@
       <c r="AX41" s="48" t="n"/>
       <c r="AY41" s="50" t="n"/>
     </row>
-    <row r="42" ht="20.76" customHeight="1">
+    <row r="42" ht="18.59" customHeight="1">
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="48" t="n"/>
       <c r="C42" s="48" t="n"/>
@@ -4665,7 +10251,7 @@
       <c r="AX42" s="48" t="n"/>
       <c r="AY42" s="50" t="n"/>
     </row>
-    <row r="43" ht="20.76" customHeight="1">
+    <row r="43" ht="18.59" customHeight="1">
       <c r="A43" s="51" t="n"/>
       <c r="B43" s="52" t="n"/>
       <c r="C43" s="52" t="n"/>
@@ -5324,7 +10910,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>MISSING TEETH  ·  type X under a missing tooth (not printed)</t>
+          <t>MISSING TEETH AND IMPLANTS (not printed)  ·  X = missing, crosses the tooth out  ·  I = implant (to draw it, right-click the drawing &gt; Change Picture)</t>
         </is>
       </c>
       <c r="D52" s="9" t="n"/>
@@ -5466,7 +11052,7 @@
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="72" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>X / I</t>
         </is>
       </c>
       <c r="B54" s="73" t="n"/>
@@ -5610,7 +11196,7 @@
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="72" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>X / I</t>
         </is>
       </c>
       <c r="B56" s="73" t="n"/>
@@ -5862,322 +11448,418 @@
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$C$54="X"</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>$C$54="I"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:H27">
-    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
       <formula>$F$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:H9 F28:H28">
-    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
       <formula>$F$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>$F$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:K27">
-    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
       <formula>$I$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:K9 I28:K28">
-    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
       <formula>$I$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>$I$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:N27">
-    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="10" dxfId="0" stopIfTrue="1">
       <formula>$L$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:N9 L28:N28">
-    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
       <formula>$L$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
+      <formula>$L$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:Q27">
-    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
       <formula>$O$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:Q9 O28:Q28">
-    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
       <formula>$O$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
+      <formula>$O$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:T27">
-    <cfRule type="expression" priority="11" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="16" dxfId="0" stopIfTrue="1">
       <formula>$R$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:T9 R28:T28">
-    <cfRule type="expression" priority="12" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="17" dxfId="1" stopIfTrue="1">
       <formula>$R$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+      <formula>$R$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:W27">
-    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
       <formula>$U$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:W9 U28:W28">
-    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
       <formula>$U$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+      <formula>$U$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X10:Z27">
-    <cfRule type="expression" priority="15" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="0" stopIfTrue="1">
       <formula>$X$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X9:Z9 X28:Z28">
-    <cfRule type="expression" priority="16" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="1" stopIfTrue="1">
       <formula>$X$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+      <formula>$X$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AC27">
-    <cfRule type="expression" priority="17" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
       <formula>$AA$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9:AC9 AA28:AC28">
-    <cfRule type="expression" priority="18" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
       <formula>$AA$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="2" stopIfTrue="1">
+      <formula>$AA$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD10:AF27">
-    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="0" stopIfTrue="1">
       <formula>$AD$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD9:AF9 AD28:AF28">
-    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="29" dxfId="1" stopIfTrue="1">
       <formula>$AD$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="2" stopIfTrue="1">
+      <formula>$AD$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG10:AI27">
-    <cfRule type="expression" priority="21" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
       <formula>$AG$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG9:AI9 AG28:AI28">
-    <cfRule type="expression" priority="22" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
       <formula>$AG$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="2" stopIfTrue="1">
+      <formula>$AG$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ10:AL27">
-    <cfRule type="expression" priority="23" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="0" stopIfTrue="1">
       <formula>$AJ$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ9:AL9 AJ28:AL28">
-    <cfRule type="expression" priority="24" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>$AJ$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="2" stopIfTrue="1">
+      <formula>$AJ$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM10:AO27">
-    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
       <formula>$AM$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9 AM28:AO28">
-    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>$AM$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" dxfId="2" stopIfTrue="1">
+      <formula>$AM$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10:AR27">
-    <cfRule type="expression" priority="27" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="0" stopIfTrue="1">
       <formula>$AP$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP9:AR9 AP28:AR28">
-    <cfRule type="expression" priority="28" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>$AP$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="2" stopIfTrue="1">
+      <formula>$AP$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS10:AU27">
-    <cfRule type="expression" priority="29" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
       <formula>$AS$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS9:AU9 AS28:AU28">
-    <cfRule type="expression" priority="30" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>$AS$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="2" stopIfTrue="1">
+      <formula>$AS$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV10:AX27">
-    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="0" stopIfTrue="1">
       <formula>$AV$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV9:AX9 AV28:AX28">
-    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>$AV$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="2" stopIfTrue="1">
+      <formula>$AV$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:E49">
-    <cfRule type="expression" priority="33" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
       <formula>$C$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31:E31 C50:E50">
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
       <formula>$C$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" dxfId="2" stopIfTrue="1">
+      <formula>$C$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:H49">
-    <cfRule type="expression" priority="35" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="52" dxfId="0" stopIfTrue="1">
       <formula>$F$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:H31 F50:H50">
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="53" dxfId="1" stopIfTrue="1">
       <formula>$F$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="2" stopIfTrue="1">
+      <formula>$F$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:K49">
-    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
       <formula>$I$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31:K31 I50:K50">
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
       <formula>$I$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="57" dxfId="2" stopIfTrue="1">
+      <formula>$I$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32:N49">
-    <cfRule type="expression" priority="39" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="58" dxfId="0" stopIfTrue="1">
       <formula>$L$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31:N31 L50:N50">
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="59" dxfId="1" stopIfTrue="1">
       <formula>$L$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="2" stopIfTrue="1">
+      <formula>$L$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O32:Q49">
-    <cfRule type="expression" priority="41" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
       <formula>$O$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O31:Q31 O50:Q50">
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="62" dxfId="1" stopIfTrue="1">
       <formula>$O$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="2" stopIfTrue="1">
+      <formula>$O$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32:T49">
-    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="64" dxfId="0" stopIfTrue="1">
       <formula>$R$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31:T31 R50:T50">
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="65" dxfId="1" stopIfTrue="1">
       <formula>$R$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="2" stopIfTrue="1">
+      <formula>$R$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32:W49">
-    <cfRule type="expression" priority="45" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="67" dxfId="0" stopIfTrue="1">
       <formula>$U$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31:W31 U50:W50">
-    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="68" dxfId="1" stopIfTrue="1">
       <formula>$U$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="69" dxfId="2" stopIfTrue="1">
+      <formula>$U$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X32:Z49">
-    <cfRule type="expression" priority="47" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="70" dxfId="0" stopIfTrue="1">
       <formula>$X$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X31:Z31 X50:Z50">
-    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="71" dxfId="1" stopIfTrue="1">
       <formula>$X$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="72" dxfId="2" stopIfTrue="1">
+      <formula>$X$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA32:AC49">
-    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="73" dxfId="0" stopIfTrue="1">
       <formula>$AA$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA31:AC31 AA50:AC50">
-    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="74" dxfId="1" stopIfTrue="1">
       <formula>$AA$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="75" dxfId="2" stopIfTrue="1">
+      <formula>$AA$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD32:AF49">
-    <cfRule type="expression" priority="51" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="76" dxfId="0" stopIfTrue="1">
       <formula>$AD$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD31:AF31 AD50:AF50">
-    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="77" dxfId="1" stopIfTrue="1">
       <formula>$AD$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="78" dxfId="2" stopIfTrue="1">
+      <formula>$AD$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG32:AI49">
-    <cfRule type="expression" priority="53" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="79" dxfId="0" stopIfTrue="1">
       <formula>$AG$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG31:AI31 AG50:AI50">
-    <cfRule type="expression" priority="54" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="80" dxfId="1" stopIfTrue="1">
       <formula>$AG$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="81" dxfId="2" stopIfTrue="1">
+      <formula>$AG$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ32:AL49">
-    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="82" dxfId="0" stopIfTrue="1">
       <formula>$AJ$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ31:AL31 AJ50:AL50">
-    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="83" dxfId="1" stopIfTrue="1">
       <formula>$AJ$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="84" dxfId="2" stopIfTrue="1">
+      <formula>$AJ$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM32:AO49">
-    <cfRule type="expression" priority="57" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="85" dxfId="0" stopIfTrue="1">
       <formula>$AM$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM31:AO31 AM50:AO50">
-    <cfRule type="expression" priority="58" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="86" dxfId="1" stopIfTrue="1">
       <formula>$AM$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="87" dxfId="2" stopIfTrue="1">
+      <formula>$AM$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP32:AR49">
-    <cfRule type="expression" priority="59" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="88" dxfId="0" stopIfTrue="1">
       <formula>$AP$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP31:AR31 AP50:AR50">
-    <cfRule type="expression" priority="60" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="89" dxfId="1" stopIfTrue="1">
       <formula>$AP$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="90" dxfId="2" stopIfTrue="1">
+      <formula>$AP$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS32:AU49">
-    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="91" dxfId="0" stopIfTrue="1">
       <formula>$AS$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS31:AU31 AS50:AU50">
-    <cfRule type="expression" priority="62" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="92" dxfId="1" stopIfTrue="1">
       <formula>$AS$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="93" dxfId="2" stopIfTrue="1">
+      <formula>$AS$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV32:AX49">
-    <cfRule type="expression" priority="63" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="94" dxfId="0" stopIfTrue="1">
       <formula>$AV$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV31:AX31 AV50:AX50">
-    <cfRule type="expression" priority="64" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="95" dxfId="1" stopIfTrue="1">
       <formula>$AV$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="96" dxfId="2" stopIfTrue="1">
+      <formula>$AV$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:AX14 C24:AX24 C35:AX35 C45:AX45">
-    <cfRule type="cellIs" priority="65" operator="greaterThanOrEqual" dxfId="2">
+    <cfRule type="cellIs" priority="97" operator="greaterThanOrEqual" dxfId="3">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="66" operator="between" dxfId="3">
+    <cfRule type="cellIs" priority="98" operator="between" dxfId="4">
       <formula>4</formula>
       <formula>5</formula>
     </cfRule>
@@ -6201,8 +11883,8 @@
     <dataValidation sqref="C11:AX11 C27:AX27 C32:AX32 C48:AX48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Plaque" error="Use / for plaque." type="list" errorStyle="stop">
       <formula1>"/"</formula1>
     </dataValidation>
-    <dataValidation sqref="C54:AX54 C56:AX56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Missing tooth" error="Type X under a missing tooth, or leave it empty." type="list">
-      <formula1>"X"</formula1>
+    <dataValidation sqref="C54:AX54 C56:AX56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Missing tooth or implant" error="Type X under a missing tooth, I under an implant, or leave it empty." type="list">
+      <formula1>"X,I"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -7510,7 +13192,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20.94" customHeight="1">
+    <row r="16" ht="18.89" customHeight="1">
       <c r="A16" s="41" t="n"/>
       <c r="B16" s="42" t="n"/>
       <c r="C16" s="42" t="n"/>
@@ -7576,7 +13258,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="20.94" customHeight="1">
+    <row r="17" ht="18.89" customHeight="1">
       <c r="A17" s="47" t="n"/>
       <c r="B17" s="48" t="n"/>
       <c r="C17" s="48" t="n"/>
@@ -7642,7 +13324,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="20.94" customHeight="1">
+    <row r="18" ht="18.89" customHeight="1">
       <c r="A18" s="47" t="n"/>
       <c r="B18" s="48" t="n"/>
       <c r="C18" s="48" t="n"/>
@@ -7708,7 +13390,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="20.94" customHeight="1">
+    <row r="19" ht="18.89" customHeight="1">
       <c r="A19" s="47" t="n"/>
       <c r="B19" s="48" t="n"/>
       <c r="C19" s="48" t="n"/>
@@ -7761,7 +13443,7 @@
       <c r="AX19" s="48" t="n"/>
       <c r="AY19" s="50" t="n"/>
     </row>
-    <row r="20" ht="20.94" customHeight="1">
+    <row r="20" ht="18.89" customHeight="1">
       <c r="A20" s="47" t="n"/>
       <c r="B20" s="48" t="n"/>
       <c r="C20" s="48" t="n"/>
@@ -7829,7 +13511,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20.94" customHeight="1">
+    <row r="21" ht="18.89" customHeight="1">
       <c r="A21" s="47" t="n"/>
       <c r="B21" s="48" t="n"/>
       <c r="C21" s="48" t="n"/>
@@ -7895,7 +13577,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20.94" customHeight="1">
+    <row r="22" ht="18.89" customHeight="1">
       <c r="A22" s="51" t="n"/>
       <c r="B22" s="52" t="n"/>
       <c r="C22" s="52" t="n"/>
@@ -9164,7 +14846,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20.76" customHeight="1">
+    <row r="37" ht="18.59" customHeight="1">
       <c r="A37" s="41" t="n"/>
       <c r="B37" s="42" t="n"/>
       <c r="C37" s="42" t="n"/>
@@ -9217,7 +14899,7 @@
       <c r="AX37" s="42" t="n"/>
       <c r="AY37" s="44" t="n"/>
     </row>
-    <row r="38" ht="20.76" customHeight="1">
+    <row r="38" ht="18.59" customHeight="1">
       <c r="A38" s="47" t="n"/>
       <c r="B38" s="48" t="n"/>
       <c r="C38" s="48" t="n"/>
@@ -9270,7 +14952,7 @@
       <c r="AX38" s="48" t="n"/>
       <c r="AY38" s="50" t="n"/>
     </row>
-    <row r="39" ht="20.76" customHeight="1">
+    <row r="39" ht="18.59" customHeight="1">
       <c r="A39" s="47" t="n"/>
       <c r="B39" s="48" t="n"/>
       <c r="C39" s="48" t="n"/>
@@ -9323,7 +15005,7 @@
       <c r="AX39" s="48" t="n"/>
       <c r="AY39" s="50" t="n"/>
     </row>
-    <row r="40" ht="20.76" customHeight="1">
+    <row r="40" ht="18.59" customHeight="1">
       <c r="A40" s="47" t="n"/>
       <c r="B40" s="48" t="n"/>
       <c r="C40" s="48" t="n"/>
@@ -9376,7 +15058,7 @@
       <c r="AX40" s="48" t="n"/>
       <c r="AY40" s="50" t="n"/>
     </row>
-    <row r="41" ht="20.76" customHeight="1">
+    <row r="41" ht="18.59" customHeight="1">
       <c r="A41" s="47" t="n"/>
       <c r="B41" s="48" t="n"/>
       <c r="C41" s="48" t="n"/>
@@ -9429,7 +15111,7 @@
       <c r="AX41" s="48" t="n"/>
       <c r="AY41" s="50" t="n"/>
     </row>
-    <row r="42" ht="20.76" customHeight="1">
+    <row r="42" ht="18.59" customHeight="1">
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="48" t="n"/>
       <c r="C42" s="48" t="n"/>
@@ -9482,7 +15164,7 @@
       <c r="AX42" s="48" t="n"/>
       <c r="AY42" s="50" t="n"/>
     </row>
-    <row r="43" ht="20.76" customHeight="1">
+    <row r="43" ht="18.59" customHeight="1">
       <c r="A43" s="51" t="n"/>
       <c r="B43" s="52" t="n"/>
       <c r="C43" s="52" t="n"/>
@@ -10141,7 +15823,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>MISSING TEETH  ·  type X under a missing tooth (not printed)</t>
+          <t>MISSING TEETH AND IMPLANTS (not printed)  ·  X = missing, crosses the tooth out  ·  I = implant (to draw it, right-click the drawing &gt; Change Picture)</t>
         </is>
       </c>
       <c r="D52" s="9" t="n"/>
@@ -10283,7 +15965,7 @@
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="72" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>X / I</t>
         </is>
       </c>
       <c r="B54" s="73" t="n"/>
@@ -10427,7 +16109,7 @@
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="72" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>X / I</t>
         </is>
       </c>
       <c r="B56" s="73" t="n"/>
@@ -10679,322 +16361,418 @@
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$C$54="X"</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>$C$54="I"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:H27">
-    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
       <formula>$F$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:H9 F28:H28">
-    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
       <formula>$F$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>$F$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:K27">
-    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
       <formula>$I$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:K9 I28:K28">
-    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
       <formula>$I$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>$I$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:N27">
-    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="10" dxfId="0" stopIfTrue="1">
       <formula>$L$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:N9 L28:N28">
-    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
       <formula>$L$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
+      <formula>$L$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:Q27">
-    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
       <formula>$O$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:Q9 O28:Q28">
-    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
       <formula>$O$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
+      <formula>$O$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:T27">
-    <cfRule type="expression" priority="11" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="16" dxfId="0" stopIfTrue="1">
       <formula>$R$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:T9 R28:T28">
-    <cfRule type="expression" priority="12" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="17" dxfId="1" stopIfTrue="1">
       <formula>$R$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+      <formula>$R$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:W27">
-    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
       <formula>$U$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:W9 U28:W28">
-    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
       <formula>$U$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+      <formula>$U$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X10:Z27">
-    <cfRule type="expression" priority="15" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="0" stopIfTrue="1">
       <formula>$X$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X9:Z9 X28:Z28">
-    <cfRule type="expression" priority="16" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="1" stopIfTrue="1">
       <formula>$X$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+      <formula>$X$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AC27">
-    <cfRule type="expression" priority="17" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
       <formula>$AA$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9:AC9 AA28:AC28">
-    <cfRule type="expression" priority="18" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
       <formula>$AA$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="2" stopIfTrue="1">
+      <formula>$AA$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD10:AF27">
-    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="0" stopIfTrue="1">
       <formula>$AD$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD9:AF9 AD28:AF28">
-    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="29" dxfId="1" stopIfTrue="1">
       <formula>$AD$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="2" stopIfTrue="1">
+      <formula>$AD$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG10:AI27">
-    <cfRule type="expression" priority="21" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
       <formula>$AG$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG9:AI9 AG28:AI28">
-    <cfRule type="expression" priority="22" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
       <formula>$AG$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="2" stopIfTrue="1">
+      <formula>$AG$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ10:AL27">
-    <cfRule type="expression" priority="23" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="0" stopIfTrue="1">
       <formula>$AJ$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ9:AL9 AJ28:AL28">
-    <cfRule type="expression" priority="24" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>$AJ$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="2" stopIfTrue="1">
+      <formula>$AJ$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM10:AO27">
-    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
       <formula>$AM$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9 AM28:AO28">
-    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>$AM$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" dxfId="2" stopIfTrue="1">
+      <formula>$AM$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10:AR27">
-    <cfRule type="expression" priority="27" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="0" stopIfTrue="1">
       <formula>$AP$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP9:AR9 AP28:AR28">
-    <cfRule type="expression" priority="28" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>$AP$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="2" stopIfTrue="1">
+      <formula>$AP$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS10:AU27">
-    <cfRule type="expression" priority="29" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
       <formula>$AS$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS9:AU9 AS28:AU28">
-    <cfRule type="expression" priority="30" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>$AS$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="2" stopIfTrue="1">
+      <formula>$AS$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV10:AX27">
-    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="0" stopIfTrue="1">
       <formula>$AV$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV9:AX9 AV28:AX28">
-    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>$AV$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="2" stopIfTrue="1">
+      <formula>$AV$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:E49">
-    <cfRule type="expression" priority="33" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
       <formula>$C$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31:E31 C50:E50">
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
       <formula>$C$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" dxfId="2" stopIfTrue="1">
+      <formula>$C$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:H49">
-    <cfRule type="expression" priority="35" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="52" dxfId="0" stopIfTrue="1">
       <formula>$F$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:H31 F50:H50">
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="53" dxfId="1" stopIfTrue="1">
       <formula>$F$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="2" stopIfTrue="1">
+      <formula>$F$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:K49">
-    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
       <formula>$I$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31:K31 I50:K50">
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
       <formula>$I$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="57" dxfId="2" stopIfTrue="1">
+      <formula>$I$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32:N49">
-    <cfRule type="expression" priority="39" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="58" dxfId="0" stopIfTrue="1">
       <formula>$L$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31:N31 L50:N50">
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="59" dxfId="1" stopIfTrue="1">
       <formula>$L$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="2" stopIfTrue="1">
+      <formula>$L$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O32:Q49">
-    <cfRule type="expression" priority="41" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
       <formula>$O$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O31:Q31 O50:Q50">
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="62" dxfId="1" stopIfTrue="1">
       <formula>$O$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="2" stopIfTrue="1">
+      <formula>$O$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32:T49">
-    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="64" dxfId="0" stopIfTrue="1">
       <formula>$R$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31:T31 R50:T50">
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="65" dxfId="1" stopIfTrue="1">
       <formula>$R$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="2" stopIfTrue="1">
+      <formula>$R$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32:W49">
-    <cfRule type="expression" priority="45" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="67" dxfId="0" stopIfTrue="1">
       <formula>$U$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31:W31 U50:W50">
-    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="68" dxfId="1" stopIfTrue="1">
       <formula>$U$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="69" dxfId="2" stopIfTrue="1">
+      <formula>$U$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X32:Z49">
-    <cfRule type="expression" priority="47" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="70" dxfId="0" stopIfTrue="1">
       <formula>$X$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X31:Z31 X50:Z50">
-    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="71" dxfId="1" stopIfTrue="1">
       <formula>$X$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="72" dxfId="2" stopIfTrue="1">
+      <formula>$X$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA32:AC49">
-    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="73" dxfId="0" stopIfTrue="1">
       <formula>$AA$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA31:AC31 AA50:AC50">
-    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="74" dxfId="1" stopIfTrue="1">
       <formula>$AA$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="75" dxfId="2" stopIfTrue="1">
+      <formula>$AA$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD32:AF49">
-    <cfRule type="expression" priority="51" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="76" dxfId="0" stopIfTrue="1">
       <formula>$AD$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD31:AF31 AD50:AF50">
-    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="77" dxfId="1" stopIfTrue="1">
       <formula>$AD$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="78" dxfId="2" stopIfTrue="1">
+      <formula>$AD$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG32:AI49">
-    <cfRule type="expression" priority="53" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="79" dxfId="0" stopIfTrue="1">
       <formula>$AG$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG31:AI31 AG50:AI50">
-    <cfRule type="expression" priority="54" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="80" dxfId="1" stopIfTrue="1">
       <formula>$AG$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="81" dxfId="2" stopIfTrue="1">
+      <formula>$AG$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ32:AL49">
-    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="82" dxfId="0" stopIfTrue="1">
       <formula>$AJ$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ31:AL31 AJ50:AL50">
-    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="83" dxfId="1" stopIfTrue="1">
       <formula>$AJ$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="84" dxfId="2" stopIfTrue="1">
+      <formula>$AJ$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM32:AO49">
-    <cfRule type="expression" priority="57" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="85" dxfId="0" stopIfTrue="1">
       <formula>$AM$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM31:AO31 AM50:AO50">
-    <cfRule type="expression" priority="58" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="86" dxfId="1" stopIfTrue="1">
       <formula>$AM$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="87" dxfId="2" stopIfTrue="1">
+      <formula>$AM$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP32:AR49">
-    <cfRule type="expression" priority="59" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="88" dxfId="0" stopIfTrue="1">
       <formula>$AP$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP31:AR31 AP50:AR50">
-    <cfRule type="expression" priority="60" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="89" dxfId="1" stopIfTrue="1">
       <formula>$AP$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="90" dxfId="2" stopIfTrue="1">
+      <formula>$AP$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS32:AU49">
-    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="91" dxfId="0" stopIfTrue="1">
       <formula>$AS$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS31:AU31 AS50:AU50">
-    <cfRule type="expression" priority="62" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="92" dxfId="1" stopIfTrue="1">
       <formula>$AS$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="93" dxfId="2" stopIfTrue="1">
+      <formula>$AS$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV32:AX49">
-    <cfRule type="expression" priority="63" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="94" dxfId="0" stopIfTrue="1">
       <formula>$AV$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV31:AX31 AV50:AX50">
-    <cfRule type="expression" priority="64" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="95" dxfId="1" stopIfTrue="1">
       <formula>$AV$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="96" dxfId="2" stopIfTrue="1">
+      <formula>$AV$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:AX14 C24:AX24 C35:AX35 C45:AX45">
-    <cfRule type="cellIs" priority="65" operator="greaterThanOrEqual" dxfId="2">
+    <cfRule type="cellIs" priority="97" operator="greaterThanOrEqual" dxfId="3">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="66" operator="between" dxfId="3">
+    <cfRule type="cellIs" priority="98" operator="between" dxfId="4">
       <formula>4</formula>
       <formula>5</formula>
     </cfRule>
@@ -11018,8 +16796,8 @@
     <dataValidation sqref="C11:AX11 C27:AX27 C32:AX32 C48:AX48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Plaque" error="Use / for plaque." type="list" errorStyle="stop">
       <formula1>"/"</formula1>
     </dataValidation>
-    <dataValidation sqref="C54:AX54 C56:AX56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Missing tooth" error="Type X under a missing tooth, or leave it empty." type="list">
-      <formula1>"X"</formula1>
+    <dataValidation sqref="C54:AX54 C56:AX56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Missing tooth or implant" error="Type X under a missing tooth, I under an implant, or leave it empty." type="list">
+      <formula1>"X,I"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -12880,7 +18658,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20.94" customHeight="1">
+    <row r="16" ht="18.89" customHeight="1">
       <c r="A16" s="41" t="n"/>
       <c r="B16" s="42" t="n"/>
       <c r="C16" s="42" t="n"/>
@@ -12933,7 +18711,7 @@
       <c r="AX16" s="42" t="n"/>
       <c r="AY16" s="44" t="n"/>
     </row>
-    <row r="17" ht="20.94" customHeight="1">
+    <row r="17" ht="18.89" customHeight="1">
       <c r="A17" s="47" t="n"/>
       <c r="B17" s="48" t="n"/>
       <c r="C17" s="48" t="n"/>
@@ -12986,7 +18764,7 @@
       <c r="AX17" s="48" t="n"/>
       <c r="AY17" s="50" t="n"/>
     </row>
-    <row r="18" ht="20.94" customHeight="1">
+    <row r="18" ht="18.89" customHeight="1">
       <c r="A18" s="47" t="n"/>
       <c r="B18" s="48" t="n"/>
       <c r="C18" s="48" t="n"/>
@@ -13039,7 +18817,7 @@
       <c r="AX18" s="48" t="n"/>
       <c r="AY18" s="50" t="n"/>
     </row>
-    <row r="19" ht="20.94" customHeight="1">
+    <row r="19" ht="18.89" customHeight="1">
       <c r="A19" s="47" t="n"/>
       <c r="B19" s="48" t="n"/>
       <c r="C19" s="48" t="n"/>
@@ -13092,7 +18870,7 @@
       <c r="AX19" s="48" t="n"/>
       <c r="AY19" s="50" t="n"/>
     </row>
-    <row r="20" ht="20.94" customHeight="1">
+    <row r="20" ht="18.89" customHeight="1">
       <c r="A20" s="47" t="n"/>
       <c r="B20" s="48" t="n"/>
       <c r="C20" s="48" t="n"/>
@@ -13145,7 +18923,7 @@
       <c r="AX20" s="48" t="n"/>
       <c r="AY20" s="50" t="n"/>
     </row>
-    <row r="21" ht="20.94" customHeight="1">
+    <row r="21" ht="18.89" customHeight="1">
       <c r="A21" s="47" t="n"/>
       <c r="B21" s="48" t="n"/>
       <c r="C21" s="48" t="n"/>
@@ -13198,7 +18976,7 @@
       <c r="AX21" s="48" t="n"/>
       <c r="AY21" s="50" t="n"/>
     </row>
-    <row r="22" ht="20.94" customHeight="1">
+    <row r="22" ht="18.89" customHeight="1">
       <c r="A22" s="51" t="n"/>
       <c r="B22" s="52" t="n"/>
       <c r="C22" s="52" t="n"/>
@@ -15593,7 +21371,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20.76" customHeight="1">
+    <row r="37" ht="18.59" customHeight="1">
       <c r="A37" s="41" t="n"/>
       <c r="B37" s="42" t="n"/>
       <c r="C37" s="42" t="n"/>
@@ -15646,7 +21424,7 @@
       <c r="AX37" s="42" t="n"/>
       <c r="AY37" s="44" t="n"/>
     </row>
-    <row r="38" ht="20.76" customHeight="1">
+    <row r="38" ht="18.59" customHeight="1">
       <c r="A38" s="47" t="n"/>
       <c r="B38" s="48" t="n"/>
       <c r="C38" s="48" t="n"/>
@@ -15699,7 +21477,7 @@
       <c r="AX38" s="48" t="n"/>
       <c r="AY38" s="50" t="n"/>
     </row>
-    <row r="39" ht="20.76" customHeight="1">
+    <row r="39" ht="18.59" customHeight="1">
       <c r="A39" s="47" t="n"/>
       <c r="B39" s="48" t="n"/>
       <c r="C39" s="48" t="n"/>
@@ -15752,7 +21530,7 @@
       <c r="AX39" s="48" t="n"/>
       <c r="AY39" s="50" t="n"/>
     </row>
-    <row r="40" ht="20.76" customHeight="1">
+    <row r="40" ht="18.59" customHeight="1">
       <c r="A40" s="47" t="n"/>
       <c r="B40" s="48" t="n"/>
       <c r="C40" s="48" t="n"/>
@@ -15805,7 +21583,7 @@
       <c r="AX40" s="48" t="n"/>
       <c r="AY40" s="50" t="n"/>
     </row>
-    <row r="41" ht="20.76" customHeight="1">
+    <row r="41" ht="18.59" customHeight="1">
       <c r="A41" s="47" t="n"/>
       <c r="B41" s="48" t="n"/>
       <c r="C41" s="48" t="n"/>
@@ -15858,7 +21636,7 @@
       <c r="AX41" s="48" t="n"/>
       <c r="AY41" s="50" t="n"/>
     </row>
-    <row r="42" ht="20.76" customHeight="1">
+    <row r="42" ht="18.59" customHeight="1">
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="48" t="n"/>
       <c r="C42" s="48" t="n"/>
@@ -15911,7 +21689,7 @@
       <c r="AX42" s="48" t="n"/>
       <c r="AY42" s="50" t="n"/>
     </row>
-    <row r="43" ht="20.76" customHeight="1">
+    <row r="43" ht="18.59" customHeight="1">
       <c r="A43" s="51" t="n"/>
       <c r="B43" s="52" t="n"/>
       <c r="C43" s="52" t="n"/>
@@ -17432,7 +23210,7 @@
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="72" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>X / I</t>
         </is>
       </c>
       <c r="B54" s="73" t="n"/>
@@ -17624,7 +23402,7 @@
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="72" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>X / I</t>
         </is>
       </c>
       <c r="B56" s="73" t="n"/>
@@ -17889,330 +23667,426 @@
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$C$54="X"</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>$C$54="I"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:H27">
-    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
       <formula>$F$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:H9 F28:H28">
-    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
       <formula>$F$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>$F$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:K27">
-    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
       <formula>$I$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:K9 I28:K28">
-    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
       <formula>$I$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>$I$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:N27">
-    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="10" dxfId="0" stopIfTrue="1">
       <formula>$L$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:N9 L28:N28">
-    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
       <formula>$L$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
+      <formula>$L$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:Q27">
-    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
       <formula>$O$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:Q9 O28:Q28">
-    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
       <formula>$O$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
+      <formula>$O$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:T27">
-    <cfRule type="expression" priority="11" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="16" dxfId="0" stopIfTrue="1">
       <formula>$R$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:T9 R28:T28">
-    <cfRule type="expression" priority="12" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="17" dxfId="1" stopIfTrue="1">
       <formula>$R$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+      <formula>$R$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:W27">
-    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
       <formula>$U$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:W9 U28:W28">
-    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
       <formula>$U$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+      <formula>$U$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X10:Z27">
-    <cfRule type="expression" priority="15" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="0" stopIfTrue="1">
       <formula>$X$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X9:Z9 X28:Z28">
-    <cfRule type="expression" priority="16" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="1" stopIfTrue="1">
       <formula>$X$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="2" stopIfTrue="1">
+      <formula>$X$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AC27">
-    <cfRule type="expression" priority="17" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
       <formula>$AA$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9:AC9 AA28:AC28">
-    <cfRule type="expression" priority="18" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
       <formula>$AA$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="2" stopIfTrue="1">
+      <formula>$AA$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD10:AF27">
-    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="0" stopIfTrue="1">
       <formula>$AD$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD9:AF9 AD28:AF28">
-    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="29" dxfId="1" stopIfTrue="1">
       <formula>$AD$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="2" stopIfTrue="1">
+      <formula>$AD$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG10:AI27">
-    <cfRule type="expression" priority="21" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
       <formula>$AG$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG9:AI9 AG28:AI28">
-    <cfRule type="expression" priority="22" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
       <formula>$AG$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="2" stopIfTrue="1">
+      <formula>$AG$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ10:AL27">
-    <cfRule type="expression" priority="23" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="0" stopIfTrue="1">
       <formula>$AJ$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ9:AL9 AJ28:AL28">
-    <cfRule type="expression" priority="24" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="35" dxfId="1" stopIfTrue="1">
       <formula>$AJ$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="2" stopIfTrue="1">
+      <formula>$AJ$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM10:AO27">
-    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
       <formula>$AM$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9 AM28:AO28">
-    <cfRule type="expression" priority="26" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
       <formula>$AM$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" dxfId="2" stopIfTrue="1">
+      <formula>$AM$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10:AR27">
-    <cfRule type="expression" priority="27" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="0" stopIfTrue="1">
       <formula>$AP$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP9:AR9 AP28:AR28">
-    <cfRule type="expression" priority="28" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>$AP$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="2" stopIfTrue="1">
+      <formula>$AP$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS10:AU27">
-    <cfRule type="expression" priority="29" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
       <formula>$AS$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS9:AU9 AS28:AU28">
-    <cfRule type="expression" priority="30" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
       <formula>$AS$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="2" stopIfTrue="1">
+      <formula>$AS$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV10:AX27">
-    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="46" dxfId="0" stopIfTrue="1">
       <formula>$AV$54="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV9:AX9 AV28:AX28">
-    <cfRule type="expression" priority="32" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="47" dxfId="1" stopIfTrue="1">
       <formula>$AV$54="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="2" stopIfTrue="1">
+      <formula>$AV$54="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:E49">
-    <cfRule type="expression" priority="33" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
       <formula>$C$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31:E31 C50:E50">
-    <cfRule type="expression" priority="34" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
       <formula>$C$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" dxfId="2" stopIfTrue="1">
+      <formula>$C$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:H49">
-    <cfRule type="expression" priority="35" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="52" dxfId="0" stopIfTrue="1">
       <formula>$F$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:H31 F50:H50">
-    <cfRule type="expression" priority="36" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="53" dxfId="1" stopIfTrue="1">
       <formula>$F$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="2" stopIfTrue="1">
+      <formula>$F$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:K49">
-    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
       <formula>$I$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31:K31 I50:K50">
-    <cfRule type="expression" priority="38" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
       <formula>$I$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="57" dxfId="2" stopIfTrue="1">
+      <formula>$I$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32:N49">
-    <cfRule type="expression" priority="39" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="58" dxfId="0" stopIfTrue="1">
       <formula>$L$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31:N31 L50:N50">
-    <cfRule type="expression" priority="40" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="59" dxfId="1" stopIfTrue="1">
       <formula>$L$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="2" stopIfTrue="1">
+      <formula>$L$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O32:Q49">
-    <cfRule type="expression" priority="41" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
       <formula>$O$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O31:Q31 O50:Q50">
-    <cfRule type="expression" priority="42" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="62" dxfId="1" stopIfTrue="1">
       <formula>$O$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="2" stopIfTrue="1">
+      <formula>$O$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32:T49">
-    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="64" dxfId="0" stopIfTrue="1">
       <formula>$R$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31:T31 R50:T50">
-    <cfRule type="expression" priority="44" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="65" dxfId="1" stopIfTrue="1">
       <formula>$R$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="2" stopIfTrue="1">
+      <formula>$R$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32:W49">
-    <cfRule type="expression" priority="45" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="67" dxfId="0" stopIfTrue="1">
       <formula>$U$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31:W31 U50:W50">
-    <cfRule type="expression" priority="46" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="68" dxfId="1" stopIfTrue="1">
       <formula>$U$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="69" dxfId="2" stopIfTrue="1">
+      <formula>$U$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X32:Z49">
-    <cfRule type="expression" priority="47" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="70" dxfId="0" stopIfTrue="1">
       <formula>$X$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X31:Z31 X50:Z50">
-    <cfRule type="expression" priority="48" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="71" dxfId="1" stopIfTrue="1">
       <formula>$X$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="72" dxfId="2" stopIfTrue="1">
+      <formula>$X$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA32:AC49">
-    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="73" dxfId="0" stopIfTrue="1">
       <formula>$AA$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA31:AC31 AA50:AC50">
-    <cfRule type="expression" priority="50" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="74" dxfId="1" stopIfTrue="1">
       <formula>$AA$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="75" dxfId="2" stopIfTrue="1">
+      <formula>$AA$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD32:AF49">
-    <cfRule type="expression" priority="51" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="76" dxfId="0" stopIfTrue="1">
       <formula>$AD$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD31:AF31 AD50:AF50">
-    <cfRule type="expression" priority="52" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="77" dxfId="1" stopIfTrue="1">
       <formula>$AD$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="78" dxfId="2" stopIfTrue="1">
+      <formula>$AD$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG32:AI49">
-    <cfRule type="expression" priority="53" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="79" dxfId="0" stopIfTrue="1">
       <formula>$AG$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG31:AI31 AG50:AI50">
-    <cfRule type="expression" priority="54" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="80" dxfId="1" stopIfTrue="1">
       <formula>$AG$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="81" dxfId="2" stopIfTrue="1">
+      <formula>$AG$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ32:AL49">
-    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="82" dxfId="0" stopIfTrue="1">
       <formula>$AJ$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ31:AL31 AJ50:AL50">
-    <cfRule type="expression" priority="56" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="83" dxfId="1" stopIfTrue="1">
       <formula>$AJ$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="84" dxfId="2" stopIfTrue="1">
+      <formula>$AJ$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM32:AO49">
-    <cfRule type="expression" priority="57" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="85" dxfId="0" stopIfTrue="1">
       <formula>$AM$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM31:AO31 AM50:AO50">
-    <cfRule type="expression" priority="58" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="86" dxfId="1" stopIfTrue="1">
       <formula>$AM$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="87" dxfId="2" stopIfTrue="1">
+      <formula>$AM$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP32:AR49">
-    <cfRule type="expression" priority="59" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="88" dxfId="0" stopIfTrue="1">
       <formula>$AP$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP31:AR31 AP50:AR50">
-    <cfRule type="expression" priority="60" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="89" dxfId="1" stopIfTrue="1">
       <formula>$AP$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="90" dxfId="2" stopIfTrue="1">
+      <formula>$AP$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS32:AU49">
-    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="91" dxfId="0" stopIfTrue="1">
       <formula>$AS$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS31:AU31 AS50:AU50">
-    <cfRule type="expression" priority="62" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="92" dxfId="1" stopIfTrue="1">
       <formula>$AS$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="93" dxfId="2" stopIfTrue="1">
+      <formula>$AS$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV32:AX49">
-    <cfRule type="expression" priority="63" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="94" dxfId="0" stopIfTrue="1">
       <formula>$AV$56="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV31:AX31 AV50:AX50">
-    <cfRule type="expression" priority="64" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="95" dxfId="1" stopIfTrue="1">
       <formula>$AV$56="X"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="96" dxfId="2" stopIfTrue="1">
+      <formula>$AV$56="I"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:AX14 C24:AX24 C35:AX35 C45:AX45">
-    <cfRule type="cellIs" priority="65" operator="lessThan" dxfId="4">
+    <cfRule type="cellIs" priority="97" operator="lessThan" dxfId="5">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="66" operator="greaterThan" dxfId="5">
+    <cfRule type="cellIs" priority="98" operator="greaterThan" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:AX15 C23:AX23 C36:AX36 C44:AX44">
-    <cfRule type="cellIs" priority="67" operator="lessThan" dxfId="4">
+    <cfRule type="cellIs" priority="99" operator="lessThan" dxfId="5">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="68" operator="greaterThan" dxfId="5">
+    <cfRule type="cellIs" priority="100" operator="greaterThan" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/templates/periodontal-chart-full.xlsx
+++ b/templates/periodontal-chart-full.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+0;-0;0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +80,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="001D1D1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="006E6E73"/>
       <sz val="8"/>
     </font>
@@ -88,18 +94,6 @@
       <b val="1"/>
       <color rgb="001D1D1F"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001D1D1F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C62828"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -141,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -157,118 +151,6 @@
     <border>
       <bottom style="thin">
         <color rgb="00B9B9B9"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00555555"/>
-      </left>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00555555"/>
-      </right>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00111111"/>
-      </left>
-      <top style="medium">
-        <color rgb="00111111"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="00111111"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00555555"/>
-      </left>
-      <top style="medium">
-        <color rgb="00111111"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="00111111"/>
-      </right>
-      <top style="medium">
-        <color rgb="00111111"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00555555"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00111111"/>
-      </left>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00111111"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00111111"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00555555"/>
-      </left>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00111111"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="00111111"/>
-      </right>
-      <top style="thin">
-        <color rgb="00555555"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00111111"/>
       </bottom>
     </border>
     <border>
@@ -533,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -548,7 +430,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom" indent="1"/>
     </xf>
@@ -573,190 +455,160 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6988,7 +6840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BC56"/>
+  <dimension ref="A1:BC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -7207,7 +7059,7 @@
       <c r="G3" s="9" t="n"/>
       <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n"/>
-      <c r="J3" s="91" t="b">
+      <c r="J3" s="81" t="b">
         <v>0</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -7220,7 +7072,7 @@
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
       <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="91" t="b">
+      <c r="Q3" s="81" t="b">
         <v>0</v>
       </c>
       <c r="R3" s="10" t="inlineStr">
@@ -7233,7 +7085,7 @@
       <c r="U3" s="10" t="n"/>
       <c r="V3" s="10" t="n"/>
       <c r="W3" s="10" t="n"/>
-      <c r="X3" s="91" t="b">
+      <c r="X3" s="81" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="10" t="inlineStr">
@@ -7339,7 +7191,7 @@
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="n"/>
-      <c r="C5" s="91" t="b">
+      <c r="C5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -7357,7 +7209,7 @@
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="1" t="n"/>
       <c r="N5" s="1" t="n"/>
-      <c r="O5" s="91" t="b">
+      <c r="O5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="P5" s="13" t="inlineStr">
@@ -7375,7 +7227,7 @@
       <c r="X5" s="14" t="n"/>
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
-      <c r="AA5" s="91" t="b">
+      <c r="AA5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AB5" s="13" t="inlineStr">
@@ -7393,7 +7245,7 @@
       <c r="AJ5" s="14" t="n"/>
       <c r="AK5" s="1" t="n"/>
       <c r="AL5" s="1" t="n"/>
-      <c r="AM5" s="91" t="b">
+      <c r="AM5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AN5" s="13" t="inlineStr">
@@ -7416,7 +7268,7 @@
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="n"/>
-      <c r="C6" s="91" t="b">
+      <c r="C6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -7434,7 +7286,7 @@
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="1" t="n"/>
       <c r="N6" s="1" t="n"/>
-      <c r="O6" s="91" t="b">
+      <c r="O6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="P6" s="13" t="inlineStr">
@@ -7452,7 +7304,7 @@
       <c r="X6" s="14" t="n"/>
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
-      <c r="AA6" s="91" t="b">
+      <c r="AA6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AB6" s="13" t="inlineStr">
@@ -7470,7 +7322,7 @@
       <c r="AJ6" s="14" t="n"/>
       <c r="AK6" s="1" t="n"/>
       <c r="AL6" s="1" t="n"/>
-      <c r="AM6" s="91" t="b">
+      <c r="AM6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="13" t="inlineStr">
@@ -7493,7 +7345,7 @@
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
-      <c r="C7" s="91" t="b">
+      <c r="C7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -7511,7 +7363,7 @@
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="1" t="n"/>
       <c r="N7" s="1" t="n"/>
-      <c r="O7" s="91" t="b">
+      <c r="O7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="P7" s="13" t="inlineStr">
@@ -7529,7 +7381,7 @@
       <c r="X7" s="14" t="n"/>
       <c r="Y7" s="1" t="n"/>
       <c r="Z7" s="1" t="n"/>
-      <c r="AA7" s="91" t="b">
+      <c r="AA7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AB7" s="13" t="inlineStr">
@@ -7547,7 +7399,7 @@
       <c r="AJ7" s="14" t="n"/>
       <c r="AK7" s="1" t="n"/>
       <c r="AL7" s="1" t="n"/>
-      <c r="AM7" s="91" t="b">
+      <c r="AM7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AN7" s="13" t="inlineStr">
@@ -10907,380 +10759,32 @@
       <c r="AX50" s="64" t="n"/>
       <c r="AY50" s="66" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>MISSING TEETH AND IMPLANTS (not printed)  ·  X = missing, crosses the tooth out  ·  I = implant (to draw it, right-click the drawing &gt; Change Picture)</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="9" t="n"/>
-      <c r="T52" s="9" t="n"/>
-      <c r="U52" s="9" t="n"/>
-      <c r="V52" s="9" t="n"/>
-      <c r="W52" s="9" t="n"/>
-      <c r="X52" s="9" t="n"/>
-      <c r="Y52" s="9" t="n"/>
-      <c r="Z52" s="9" t="n"/>
-      <c r="AA52" s="9" t="n"/>
-      <c r="AB52" s="9" t="n"/>
-      <c r="AC52" s="9" t="n"/>
-      <c r="AD52" s="9" t="n"/>
-      <c r="AE52" s="9" t="n"/>
-      <c r="AF52" s="9" t="n"/>
-      <c r="AG52" s="9" t="n"/>
-      <c r="AH52" s="9" t="n"/>
-      <c r="AI52" s="9" t="n"/>
-      <c r="AJ52" s="9" t="n"/>
-      <c r="AK52" s="9" t="n"/>
-      <c r="AL52" s="9" t="n"/>
-      <c r="AM52" s="9" t="n"/>
-      <c r="AN52" s="9" t="n"/>
-      <c r="AO52" s="9" t="n"/>
-      <c r="AP52" s="9" t="n"/>
-      <c r="AQ52" s="9" t="n"/>
-      <c r="AR52" s="9" t="n"/>
-      <c r="AS52" s="9" t="n"/>
-      <c r="AT52" s="9" t="n"/>
-      <c r="AU52" s="9" t="n"/>
-      <c r="AV52" s="9" t="n"/>
-      <c r="AW52" s="9" t="n"/>
-      <c r="AX52" s="9" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="67" t="inlineStr">
-        <is>
-          <t>MAXILLA</t>
-        </is>
-      </c>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="69" t="n">
-        <v>18</v>
-      </c>
-      <c r="D53" s="70" t="n"/>
-      <c r="E53" s="70" t="n"/>
-      <c r="F53" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="G53" s="70" t="n"/>
-      <c r="H53" s="70" t="n"/>
-      <c r="I53" s="69" t="n">
-        <v>16</v>
-      </c>
-      <c r="J53" s="70" t="n"/>
-      <c r="K53" s="70" t="n"/>
-      <c r="L53" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="M53" s="70" t="n"/>
-      <c r="N53" s="70" t="n"/>
-      <c r="O53" s="69" t="n">
-        <v>14</v>
-      </c>
-      <c r="P53" s="70" t="n"/>
-      <c r="Q53" s="70" t="n"/>
-      <c r="R53" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="S53" s="70" t="n"/>
-      <c r="T53" s="70" t="n"/>
-      <c r="U53" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="V53" s="70" t="n"/>
-      <c r="W53" s="70" t="n"/>
-      <c r="X53" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y53" s="70" t="n"/>
-      <c r="Z53" s="70" t="n"/>
-      <c r="AA53" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB53" s="70" t="n"/>
-      <c r="AC53" s="70" t="n"/>
-      <c r="AD53" s="69" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE53" s="70" t="n"/>
-      <c r="AF53" s="70" t="n"/>
-      <c r="AG53" s="69" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH53" s="70" t="n"/>
-      <c r="AI53" s="70" t="n"/>
-      <c r="AJ53" s="69" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK53" s="70" t="n"/>
-      <c r="AL53" s="70" t="n"/>
-      <c r="AM53" s="69" t="n">
-        <v>25</v>
-      </c>
-      <c r="AN53" s="70" t="n"/>
-      <c r="AO53" s="70" t="n"/>
-      <c r="AP53" s="69" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ53" s="70" t="n"/>
-      <c r="AR53" s="70" t="n"/>
-      <c r="AS53" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT53" s="70" t="n"/>
-      <c r="AU53" s="70" t="n"/>
-      <c r="AV53" s="69" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW53" s="70" t="n"/>
-      <c r="AX53" s="71" t="n"/>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="72" t="inlineStr">
-        <is>
-          <t>X / I</t>
-        </is>
-      </c>
-      <c r="B54" s="73" t="n"/>
-      <c r="C54" s="74" t="n"/>
-      <c r="D54" s="75" t="n"/>
-      <c r="E54" s="75" t="n"/>
-      <c r="F54" s="74" t="n"/>
-      <c r="G54" s="75" t="n"/>
-      <c r="H54" s="75" t="n"/>
-      <c r="I54" s="74" t="n"/>
-      <c r="J54" s="75" t="n"/>
-      <c r="K54" s="75" t="n"/>
-      <c r="L54" s="74" t="n"/>
-      <c r="M54" s="75" t="n"/>
-      <c r="N54" s="75" t="n"/>
-      <c r="O54" s="74" t="n"/>
-      <c r="P54" s="75" t="n"/>
-      <c r="Q54" s="75" t="n"/>
-      <c r="R54" s="74" t="n"/>
-      <c r="S54" s="75" t="n"/>
-      <c r="T54" s="75" t="n"/>
-      <c r="U54" s="74" t="n"/>
-      <c r="V54" s="75" t="n"/>
-      <c r="W54" s="75" t="n"/>
-      <c r="X54" s="74" t="n"/>
-      <c r="Y54" s="75" t="n"/>
-      <c r="Z54" s="75" t="n"/>
-      <c r="AA54" s="74" t="n"/>
-      <c r="AB54" s="75" t="n"/>
-      <c r="AC54" s="75" t="n"/>
-      <c r="AD54" s="74" t="n"/>
-      <c r="AE54" s="75" t="n"/>
-      <c r="AF54" s="75" t="n"/>
-      <c r="AG54" s="74" t="n"/>
-      <c r="AH54" s="75" t="n"/>
-      <c r="AI54" s="75" t="n"/>
-      <c r="AJ54" s="74" t="n"/>
-      <c r="AK54" s="75" t="n"/>
-      <c r="AL54" s="75" t="n"/>
-      <c r="AM54" s="74" t="n"/>
-      <c r="AN54" s="75" t="n"/>
-      <c r="AO54" s="75" t="n"/>
-      <c r="AP54" s="74" t="n"/>
-      <c r="AQ54" s="75" t="n"/>
-      <c r="AR54" s="75" t="n"/>
-      <c r="AS54" s="74" t="n"/>
-      <c r="AT54" s="75" t="n"/>
-      <c r="AU54" s="75" t="n"/>
-      <c r="AV54" s="74" t="n"/>
-      <c r="AW54" s="75" t="n"/>
-      <c r="AX54" s="76" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="67" t="inlineStr">
-        <is>
-          <t>MANDIBLE</t>
-        </is>
-      </c>
-      <c r="B55" s="68" t="n"/>
-      <c r="C55" s="69" t="n">
-        <v>48</v>
-      </c>
-      <c r="D55" s="70" t="n"/>
-      <c r="E55" s="70" t="n"/>
-      <c r="F55" s="69" t="n">
-        <v>47</v>
-      </c>
-      <c r="G55" s="70" t="n"/>
-      <c r="H55" s="70" t="n"/>
-      <c r="I55" s="69" t="n">
-        <v>46</v>
-      </c>
-      <c r="J55" s="70" t="n"/>
-      <c r="K55" s="70" t="n"/>
-      <c r="L55" s="69" t="n">
-        <v>45</v>
-      </c>
-      <c r="M55" s="70" t="n"/>
-      <c r="N55" s="70" t="n"/>
-      <c r="O55" s="69" t="n">
-        <v>44</v>
-      </c>
-      <c r="P55" s="70" t="n"/>
-      <c r="Q55" s="70" t="n"/>
-      <c r="R55" s="69" t="n">
-        <v>43</v>
-      </c>
-      <c r="S55" s="70" t="n"/>
-      <c r="T55" s="70" t="n"/>
-      <c r="U55" s="69" t="n">
-        <v>42</v>
-      </c>
-      <c r="V55" s="70" t="n"/>
-      <c r="W55" s="70" t="n"/>
-      <c r="X55" s="69" t="n">
-        <v>41</v>
-      </c>
-      <c r="Y55" s="70" t="n"/>
-      <c r="Z55" s="70" t="n"/>
-      <c r="AA55" s="69" t="n">
-        <v>31</v>
-      </c>
-      <c r="AB55" s="70" t="n"/>
-      <c r="AC55" s="70" t="n"/>
-      <c r="AD55" s="69" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE55" s="70" t="n"/>
-      <c r="AF55" s="70" t="n"/>
-      <c r="AG55" s="69" t="n">
-        <v>33</v>
-      </c>
-      <c r="AH55" s="70" t="n"/>
-      <c r="AI55" s="70" t="n"/>
-      <c r="AJ55" s="69" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK55" s="70" t="n"/>
-      <c r="AL55" s="70" t="n"/>
-      <c r="AM55" s="69" t="n">
-        <v>35</v>
-      </c>
-      <c r="AN55" s="70" t="n"/>
-      <c r="AO55" s="70" t="n"/>
-      <c r="AP55" s="69" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ55" s="70" t="n"/>
-      <c r="AR55" s="70" t="n"/>
-      <c r="AS55" s="69" t="n">
-        <v>37</v>
-      </c>
-      <c r="AT55" s="70" t="n"/>
-      <c r="AU55" s="70" t="n"/>
-      <c r="AV55" s="69" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW55" s="70" t="n"/>
-      <c r="AX55" s="71" t="n"/>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="72" t="inlineStr">
-        <is>
-          <t>X / I</t>
-        </is>
-      </c>
-      <c r="B56" s="73" t="n"/>
-      <c r="C56" s="74" t="n"/>
-      <c r="D56" s="75" t="n"/>
-      <c r="E56" s="75" t="n"/>
-      <c r="F56" s="74" t="n"/>
-      <c r="G56" s="75" t="n"/>
-      <c r="H56" s="75" t="n"/>
-      <c r="I56" s="74" t="n"/>
-      <c r="J56" s="75" t="n"/>
-      <c r="K56" s="75" t="n"/>
-      <c r="L56" s="74" t="n"/>
-      <c r="M56" s="75" t="n"/>
-      <c r="N56" s="75" t="n"/>
-      <c r="O56" s="74" t="n"/>
-      <c r="P56" s="75" t="n"/>
-      <c r="Q56" s="75" t="n"/>
-      <c r="R56" s="74" t="n"/>
-      <c r="S56" s="75" t="n"/>
-      <c r="T56" s="75" t="n"/>
-      <c r="U56" s="74" t="n"/>
-      <c r="V56" s="75" t="n"/>
-      <c r="W56" s="75" t="n"/>
-      <c r="X56" s="74" t="n"/>
-      <c r="Y56" s="75" t="n"/>
-      <c r="Z56" s="75" t="n"/>
-      <c r="AA56" s="74" t="n"/>
-      <c r="AB56" s="75" t="n"/>
-      <c r="AC56" s="75" t="n"/>
-      <c r="AD56" s="74" t="n"/>
-      <c r="AE56" s="75" t="n"/>
-      <c r="AF56" s="75" t="n"/>
-      <c r="AG56" s="74" t="n"/>
-      <c r="AH56" s="75" t="n"/>
-      <c r="AI56" s="75" t="n"/>
-      <c r="AJ56" s="74" t="n"/>
-      <c r="AK56" s="75" t="n"/>
-      <c r="AL56" s="75" t="n"/>
-      <c r="AM56" s="74" t="n"/>
-      <c r="AN56" s="75" t="n"/>
-      <c r="AO56" s="75" t="n"/>
-      <c r="AP56" s="74" t="n"/>
-      <c r="AQ56" s="75" t="n"/>
-      <c r="AR56" s="75" t="n"/>
-      <c r="AS56" s="74" t="n"/>
-      <c r="AT56" s="75" t="n"/>
-      <c r="AU56" s="75" t="n"/>
-      <c r="AV56" s="74" t="n"/>
-      <c r="AW56" s="75" t="n"/>
-      <c r="AX56" s="76" t="n"/>
-    </row>
+    <row r="54" hidden="1"/>
+    <row r="56" hidden="1"/>
   </sheetData>
-  <mergeCells count="187">
-    <mergeCell ref="I54:K54"/>
+  <mergeCells count="118">
     <mergeCell ref="AD28:AF28"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="C4:AX4"/>
     <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="I56:K56"/>
     <mergeCell ref="A32:A36"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="R3:W3"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="O56:Q56"/>
     <mergeCell ref="L9:N9"/>
     <mergeCell ref="AV9:AX9"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="A56:B56"/>
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="AD55:AF55"/>
     <mergeCell ref="X31:Z31"/>
     <mergeCell ref="U50:W50"/>
     <mergeCell ref="AO3:AU3"/>
     <mergeCell ref="AD9:AF9"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="AH3:AJ3"/>
-    <mergeCell ref="A53:B53"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="AH5:AJ5"/>
     <mergeCell ref="AS50:AU50"/>
@@ -11296,7 +10800,6 @@
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="AM9:AO9"/>
     <mergeCell ref="F50:H50"/>
-    <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="O50:Q50"/>
     <mergeCell ref="J7:L7"/>
@@ -11308,133 +10811,73 @@
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="U54:W54"/>
-    <mergeCell ref="U55:W55"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="AN7:AS7"/>
     <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="X9:Z9"/>
     <mergeCell ref="R9:T9"/>
-    <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="AT6:AV6"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="V5:X5"/>
-    <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="L28:N28"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP9:AR9"/>
     <mergeCell ref="AV3:AX3"/>
-    <mergeCell ref="AG56:AI56"/>
-    <mergeCell ref="AP54:AR54"/>
-    <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="R31:T31"/>
-    <mergeCell ref="F55:H55"/>
     <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AP55:AR55"/>
-    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="C50:E50"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AT5:AV5"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="I53:K53"/>
     <mergeCell ref="C1:Z1"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="AA53:AC53"/>
     <mergeCell ref="AH2:AN2"/>
     <mergeCell ref="AP31:AR31"/>
-    <mergeCell ref="L55:N55"/>
-    <mergeCell ref="U53:W53"/>
     <mergeCell ref="AH6:AJ6"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="X55:Z55"/>
-    <mergeCell ref="I55:K55"/>
     <mergeCell ref="U28:W28"/>
-    <mergeCell ref="L54:N54"/>
-    <mergeCell ref="AV53:AX53"/>
-    <mergeCell ref="AD54:AF54"/>
     <mergeCell ref="R50:T50"/>
     <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="AO2:AR2"/>
-    <mergeCell ref="R56:T56"/>
     <mergeCell ref="AA50:AC50"/>
     <mergeCell ref="V7:X7"/>
-    <mergeCell ref="L56:N56"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="AA55:AC55"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="AM50:AO50"/>
     <mergeCell ref="AH7:AJ7"/>
-    <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C52:AX52"/>
-    <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="K3:P3"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="AG55:AI55"/>
-    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="U31:W31"/>
     <mergeCell ref="Y3:AD3"/>
-    <mergeCell ref="O53:Q53"/>
     <mergeCell ref="R28:T28"/>
-    <mergeCell ref="L53:N53"/>
     <mergeCell ref="AS31:AU31"/>
-    <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="A44:A49"/>
-    <mergeCell ref="C54:E54"/>
     <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="O54:Q54"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="AD31:AF31"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="U56:W56"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="F2:T2"/>
     <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AA54:AC54"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="AJ53:AL53"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="U2:V2"/>
-    <mergeCell ref="AM54:AO54"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="AA56:AC56"/>
     <mergeCell ref="L31:N31"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AS1:AV1"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="C53:E53"/>
     <mergeCell ref="P5:U5"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="X56:Z56"/>
     <mergeCell ref="U9:W9"/>
     <mergeCell ref="AV31:AX31"/>
-    <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="AT7:AV7"/>
-    <mergeCell ref="AM53:AO53"/>
-    <mergeCell ref="F54:H54"/>
     <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="AN6:AS6"/>
-    <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="W2:AD2"/>
     <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="A31:B31"/>
@@ -11864,7 +11307,7 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="C14:AX14 C24:AX24 C35:AX35 C45:AX45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Probing depth" error="Enter PD in mm, 0 to 15." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>15</formula2>
@@ -11883,9 +11326,6 @@
     <dataValidation sqref="C11:AX11 C27:AX27 C32:AX32 C48:AX48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Plaque" error="Use / for plaque." type="list" errorStyle="stop">
       <formula1>"/"</formula1>
     </dataValidation>
-    <dataValidation sqref="C54:AX54 C56:AX56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Missing tooth or implant" error="Type X under a missing tooth, I under an implant, or leave it empty." type="list">
-      <formula1>"X,I"</formula1>
-    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -11901,7 +11341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BC56"/>
+  <dimension ref="A1:BC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -12120,7 +11560,7 @@
       <c r="G3" s="9" t="n"/>
       <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n"/>
-      <c r="J3" s="91" t="b">
+      <c r="J3" s="81" t="b">
         <v>0</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -12133,7 +11573,7 @@
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
       <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="91" t="b">
+      <c r="Q3" s="81" t="b">
         <v>0</v>
       </c>
       <c r="R3" s="10" t="inlineStr">
@@ -12146,7 +11586,7 @@
       <c r="U3" s="10" t="n"/>
       <c r="V3" s="10" t="n"/>
       <c r="W3" s="10" t="n"/>
-      <c r="X3" s="91" t="b">
+      <c r="X3" s="81" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="10" t="inlineStr">
@@ -12252,7 +11692,7 @@
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="n"/>
-      <c r="C5" s="91" t="b">
+      <c r="C5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -12270,7 +11710,7 @@
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="1" t="n"/>
       <c r="N5" s="1" t="n"/>
-      <c r="O5" s="91" t="b">
+      <c r="O5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="P5" s="13" t="inlineStr">
@@ -12288,7 +11728,7 @@
       <c r="X5" s="14" t="n"/>
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
-      <c r="AA5" s="91" t="b">
+      <c r="AA5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AB5" s="13" t="inlineStr">
@@ -12306,7 +11746,7 @@
       <c r="AJ5" s="14" t="n"/>
       <c r="AK5" s="1" t="n"/>
       <c r="AL5" s="1" t="n"/>
-      <c r="AM5" s="91" t="b">
+      <c r="AM5" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AN5" s="13" t="inlineStr">
@@ -12329,7 +11769,7 @@
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="n"/>
-      <c r="C6" s="91" t="b">
+      <c r="C6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -12347,7 +11787,7 @@
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="1" t="n"/>
       <c r="N6" s="1" t="n"/>
-      <c r="O6" s="91" t="b">
+      <c r="O6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="P6" s="13" t="inlineStr">
@@ -12365,7 +11805,7 @@
       <c r="X6" s="14" t="n"/>
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
-      <c r="AA6" s="91" t="b">
+      <c r="AA6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AB6" s="13" t="inlineStr">
@@ -12383,7 +11823,7 @@
       <c r="AJ6" s="14" t="n"/>
       <c r="AK6" s="1" t="n"/>
       <c r="AL6" s="1" t="n"/>
-      <c r="AM6" s="91" t="b">
+      <c r="AM6" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="13" t="inlineStr">
@@ -12406,7 +11846,7 @@
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
-      <c r="C7" s="91" t="b">
+      <c r="C7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -12424,7 +11864,7 @@
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="1" t="n"/>
       <c r="N7" s="1" t="n"/>
-      <c r="O7" s="91" t="b">
+      <c r="O7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="P7" s="13" t="inlineStr">
@@ -12442,7 +11882,7 @@
       <c r="X7" s="14" t="n"/>
       <c r="Y7" s="1" t="n"/>
       <c r="Z7" s="1" t="n"/>
-      <c r="AA7" s="91" t="b">
+      <c r="AA7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AB7" s="13" t="inlineStr">
@@ -12460,7 +11900,7 @@
       <c r="AJ7" s="14" t="n"/>
       <c r="AK7" s="1" t="n"/>
       <c r="AL7" s="1" t="n"/>
-      <c r="AM7" s="91" t="b">
+      <c r="AM7" s="81" t="b">
         <v>0</v>
       </c>
       <c r="AN7" s="13" t="inlineStr">
@@ -15820,380 +15260,32 @@
       <c r="AX50" s="64" t="n"/>
       <c r="AY50" s="66" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>MISSING TEETH AND IMPLANTS (not printed)  ·  X = missing, crosses the tooth out  ·  I = implant (to draw it, right-click the drawing &gt; Change Picture)</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="9" t="n"/>
-      <c r="T52" s="9" t="n"/>
-      <c r="U52" s="9" t="n"/>
-      <c r="V52" s="9" t="n"/>
-      <c r="W52" s="9" t="n"/>
-      <c r="X52" s="9" t="n"/>
-      <c r="Y52" s="9" t="n"/>
-      <c r="Z52" s="9" t="n"/>
-      <c r="AA52" s="9" t="n"/>
-      <c r="AB52" s="9" t="n"/>
-      <c r="AC52" s="9" t="n"/>
-      <c r="AD52" s="9" t="n"/>
-      <c r="AE52" s="9" t="n"/>
-      <c r="AF52" s="9" t="n"/>
-      <c r="AG52" s="9" t="n"/>
-      <c r="AH52" s="9" t="n"/>
-      <c r="AI52" s="9" t="n"/>
-      <c r="AJ52" s="9" t="n"/>
-      <c r="AK52" s="9" t="n"/>
-      <c r="AL52" s="9" t="n"/>
-      <c r="AM52" s="9" t="n"/>
-      <c r="AN52" s="9" t="n"/>
-      <c r="AO52" s="9" t="n"/>
-      <c r="AP52" s="9" t="n"/>
-      <c r="AQ52" s="9" t="n"/>
-      <c r="AR52" s="9" t="n"/>
-      <c r="AS52" s="9" t="n"/>
-      <c r="AT52" s="9" t="n"/>
-      <c r="AU52" s="9" t="n"/>
-      <c r="AV52" s="9" t="n"/>
-      <c r="AW52" s="9" t="n"/>
-      <c r="AX52" s="9" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="67" t="inlineStr">
-        <is>
-          <t>MAXILLA</t>
-        </is>
-      </c>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="69" t="n">
-        <v>18</v>
-      </c>
-      <c r="D53" s="70" t="n"/>
-      <c r="E53" s="70" t="n"/>
-      <c r="F53" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="G53" s="70" t="n"/>
-      <c r="H53" s="70" t="n"/>
-      <c r="I53" s="69" t="n">
-        <v>16</v>
-      </c>
-      <c r="J53" s="70" t="n"/>
-      <c r="K53" s="70" t="n"/>
-      <c r="L53" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="M53" s="70" t="n"/>
-      <c r="N53" s="70" t="n"/>
-      <c r="O53" s="69" t="n">
-        <v>14</v>
-      </c>
-      <c r="P53" s="70" t="n"/>
-      <c r="Q53" s="70" t="n"/>
-      <c r="R53" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="S53" s="70" t="n"/>
-      <c r="T53" s="70" t="n"/>
-      <c r="U53" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="V53" s="70" t="n"/>
-      <c r="W53" s="70" t="n"/>
-      <c r="X53" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y53" s="70" t="n"/>
-      <c r="Z53" s="70" t="n"/>
-      <c r="AA53" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB53" s="70" t="n"/>
-      <c r="AC53" s="70" t="n"/>
-      <c r="AD53" s="69" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE53" s="70" t="n"/>
-      <c r="AF53" s="70" t="n"/>
-      <c r="AG53" s="69" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH53" s="70" t="n"/>
-      <c r="AI53" s="70" t="n"/>
-      <c r="AJ53" s="69" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK53" s="70" t="n"/>
-      <c r="AL53" s="70" t="n"/>
-      <c r="AM53" s="69" t="n">
-        <v>25</v>
-      </c>
-      <c r="AN53" s="70" t="n"/>
-      <c r="AO53" s="70" t="n"/>
-      <c r="AP53" s="69" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ53" s="70" t="n"/>
-      <c r="AR53" s="70" t="n"/>
-      <c r="AS53" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT53" s="70" t="n"/>
-      <c r="AU53" s="70" t="n"/>
-      <c r="AV53" s="69" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW53" s="70" t="n"/>
-      <c r="AX53" s="71" t="n"/>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="72" t="inlineStr">
-        <is>
-          <t>X / I</t>
-        </is>
-      </c>
-      <c r="B54" s="73" t="n"/>
-      <c r="C54" s="74" t="n"/>
-      <c r="D54" s="75" t="n"/>
-      <c r="E54" s="75" t="n"/>
-      <c r="F54" s="74" t="n"/>
-      <c r="G54" s="75" t="n"/>
-      <c r="H54" s="75" t="n"/>
-      <c r="I54" s="74" t="n"/>
-      <c r="J54" s="75" t="n"/>
-      <c r="K54" s="75" t="n"/>
-      <c r="L54" s="74" t="n"/>
-      <c r="M54" s="75" t="n"/>
-      <c r="N54" s="75" t="n"/>
-      <c r="O54" s="74" t="n"/>
-      <c r="P54" s="75" t="n"/>
-      <c r="Q54" s="75" t="n"/>
-      <c r="R54" s="74" t="n"/>
-      <c r="S54" s="75" t="n"/>
-      <c r="T54" s="75" t="n"/>
-      <c r="U54" s="74" t="n"/>
-      <c r="V54" s="75" t="n"/>
-      <c r="W54" s="75" t="n"/>
-      <c r="X54" s="74" t="n"/>
-      <c r="Y54" s="75" t="n"/>
-      <c r="Z54" s="75" t="n"/>
-      <c r="AA54" s="74" t="n"/>
-      <c r="AB54" s="75" t="n"/>
-      <c r="AC54" s="75" t="n"/>
-      <c r="AD54" s="74" t="n"/>
-      <c r="AE54" s="75" t="n"/>
-      <c r="AF54" s="75" t="n"/>
-      <c r="AG54" s="74" t="n"/>
-      <c r="AH54" s="75" t="n"/>
-      <c r="AI54" s="75" t="n"/>
-      <c r="AJ54" s="74" t="n"/>
-      <c r="AK54" s="75" t="n"/>
-      <c r="AL54" s="75" t="n"/>
-      <c r="AM54" s="74" t="n"/>
-      <c r="AN54" s="75" t="n"/>
-      <c r="AO54" s="75" t="n"/>
-      <c r="AP54" s="74" t="n"/>
-      <c r="AQ54" s="75" t="n"/>
-      <c r="AR54" s="75" t="n"/>
-      <c r="AS54" s="74" t="n"/>
-      <c r="AT54" s="75" t="n"/>
-      <c r="AU54" s="75" t="n"/>
-      <c r="AV54" s="74" t="n"/>
-      <c r="AW54" s="75" t="n"/>
-      <c r="AX54" s="76" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="67" t="inlineStr">
-        <is>
-          <t>MANDIBLE</t>
-        </is>
-      </c>
-      <c r="B55" s="68" t="n"/>
-      <c r="C55" s="69" t="n">
-        <v>48</v>
-      </c>
-      <c r="D55" s="70" t="n"/>
-      <c r="E55" s="70" t="n"/>
-      <c r="F55" s="69" t="n">
-        <v>47</v>
-      </c>
-      <c r="G55" s="70" t="n"/>
-      <c r="H55" s="70" t="n"/>
-      <c r="I55" s="69" t="n">
-        <v>46</v>
-      </c>
-      <c r="J55" s="70" t="n"/>
-      <c r="K55" s="70" t="n"/>
-      <c r="L55" s="69" t="n">
-        <v>45</v>
-      </c>
-      <c r="M55" s="70" t="n"/>
-      <c r="N55" s="70" t="n"/>
-      <c r="O55" s="69" t="n">
-        <v>44</v>
-      </c>
-      <c r="P55" s="70" t="n"/>
-      <c r="Q55" s="70" t="n"/>
-      <c r="R55" s="69" t="n">
-        <v>43</v>
-      </c>
-      <c r="S55" s="70" t="n"/>
-      <c r="T55" s="70" t="n"/>
-      <c r="U55" s="69" t="n">
-        <v>42</v>
-      </c>
-      <c r="V55" s="70" t="n"/>
-      <c r="W55" s="70" t="n"/>
-      <c r="X55" s="69" t="n">
-        <v>41</v>
-      </c>
-      <c r="Y55" s="70" t="n"/>
-      <c r="Z55" s="70" t="n"/>
-      <c r="AA55" s="69" t="n">
-        <v>31</v>
-      </c>
-      <c r="AB55" s="70" t="n"/>
-      <c r="AC55" s="70" t="n"/>
-      <c r="AD55" s="69" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE55" s="70" t="n"/>
-      <c r="AF55" s="70" t="n"/>
-      <c r="AG55" s="69" t="n">
-        <v>33</v>
-      </c>
-      <c r="AH55" s="70" t="n"/>
-      <c r="AI55" s="70" t="n"/>
-      <c r="AJ55" s="69" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK55" s="70" t="n"/>
-      <c r="AL55" s="70" t="n"/>
-      <c r="AM55" s="69" t="n">
-        <v>35</v>
-      </c>
-      <c r="AN55" s="70" t="n"/>
-      <c r="AO55" s="70" t="n"/>
-      <c r="AP55" s="69" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ55" s="70" t="n"/>
-      <c r="AR55" s="70" t="n"/>
-      <c r="AS55" s="69" t="n">
-        <v>37</v>
-      </c>
-      <c r="AT55" s="70" t="n"/>
-      <c r="AU55" s="70" t="n"/>
-      <c r="AV55" s="69" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW55" s="70" t="n"/>
-      <c r="AX55" s="71" t="n"/>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="72" t="inlineStr">
-        <is>
-          <t>X / I</t>
-        </is>
-      </c>
-      <c r="B56" s="73" t="n"/>
-      <c r="C56" s="74" t="n"/>
-      <c r="D56" s="75" t="n"/>
-      <c r="E56" s="75" t="n"/>
-      <c r="F56" s="74" t="n"/>
-      <c r="G56" s="75" t="n"/>
-      <c r="H56" s="75" t="n"/>
-      <c r="I56" s="74" t="n"/>
-      <c r="J56" s="75" t="n"/>
-      <c r="K56" s="75" t="n"/>
-      <c r="L56" s="74" t="n"/>
-      <c r="M56" s="75" t="n"/>
-      <c r="N56" s="75" t="n"/>
-      <c r="O56" s="74" t="n"/>
-      <c r="P56" s="75" t="n"/>
-      <c r="Q56" s="75" t="n"/>
-      <c r="R56" s="74" t="n"/>
-      <c r="S56" s="75" t="n"/>
-      <c r="T56" s="75" t="n"/>
-      <c r="U56" s="74" t="n"/>
-      <c r="V56" s="75" t="n"/>
-      <c r="W56" s="75" t="n"/>
-      <c r="X56" s="74" t="n"/>
-      <c r="Y56" s="75" t="n"/>
-      <c r="Z56" s="75" t="n"/>
-      <c r="AA56" s="74" t="n"/>
-      <c r="AB56" s="75" t="n"/>
-      <c r="AC56" s="75" t="n"/>
-      <c r="AD56" s="74" t="n"/>
-      <c r="AE56" s="75" t="n"/>
-      <c r="AF56" s="75" t="n"/>
-      <c r="AG56" s="74" t="n"/>
-      <c r="AH56" s="75" t="n"/>
-      <c r="AI56" s="75" t="n"/>
-      <c r="AJ56" s="74" t="n"/>
-      <c r="AK56" s="75" t="n"/>
-      <c r="AL56" s="75" t="n"/>
-      <c r="AM56" s="74" t="n"/>
-      <c r="AN56" s="75" t="n"/>
-      <c r="AO56" s="75" t="n"/>
-      <c r="AP56" s="74" t="n"/>
-      <c r="AQ56" s="75" t="n"/>
-      <c r="AR56" s="75" t="n"/>
-      <c r="AS56" s="74" t="n"/>
-      <c r="AT56" s="75" t="n"/>
-      <c r="AU56" s="75" t="n"/>
-      <c r="AV56" s="74" t="n"/>
-      <c r="AW56" s="75" t="n"/>
-      <c r="AX56" s="76" t="n"/>
-    </row>
+    <row r="54" hidden="1"/>
+    <row r="56" hidden="1"/>
   </sheetData>
-  <mergeCells count="187">
-    <mergeCell ref="I54:K54"/>
+  <mergeCells count="118">
     <mergeCell ref="AD28:AF28"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="C4:AX4"/>
     <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="I56:K56"/>
     <mergeCell ref="A32:A36"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="R3:W3"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="O56:Q56"/>
     <mergeCell ref="L9:N9"/>
     <mergeCell ref="AV9:AX9"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="A56:B56"/>
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="AD55:AF55"/>
     <mergeCell ref="X31:Z31"/>
     <mergeCell ref="U50:W50"/>
     <mergeCell ref="AO3:AU3"/>
     <mergeCell ref="AD9:AF9"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="AH3:AJ3"/>
-    <mergeCell ref="A53:B53"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="AH5:AJ5"/>
     <mergeCell ref="AS50:AU50"/>
@@ -16209,7 +15301,6 @@
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="AM9:AO9"/>
     <mergeCell ref="F50:H50"/>
-    <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="O50:Q50"/>
     <mergeCell ref="J7:L7"/>
@@ -16221,133 +15312,73 @@
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="U54:W54"/>
-    <mergeCell ref="U55:W55"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="AN7:AS7"/>
     <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="X9:Z9"/>
     <mergeCell ref="R9:T9"/>
-    <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="AT6:AV6"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="V5:X5"/>
-    <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="L28:N28"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP9:AR9"/>
     <mergeCell ref="AV3:AX3"/>
-    <mergeCell ref="AG56:AI56"/>
-    <mergeCell ref="AP54:AR54"/>
-    <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="R31:T31"/>
-    <mergeCell ref="F55:H55"/>
     <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AP55:AR55"/>
-    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="C50:E50"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AT5:AV5"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="I53:K53"/>
     <mergeCell ref="C1:Z1"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="AA53:AC53"/>
     <mergeCell ref="AH2:AN2"/>
     <mergeCell ref="AP31:AR31"/>
-    <mergeCell ref="L55:N55"/>
-    <mergeCell ref="U53:W53"/>
     <mergeCell ref="AH6:AJ6"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="X55:Z55"/>
-    <mergeCell ref="I55:K55"/>
     <mergeCell ref="U28:W28"/>
-    <mergeCell ref="L54:N54"/>
-    <mergeCell ref="AV53:AX53"/>
-    <mergeCell ref="AD54:AF54"/>
     <mergeCell ref="R50:T50"/>
     <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="AO2:AR2"/>
-    <mergeCell ref="R56:T56"/>
     <mergeCell ref="AA50:AC50"/>
     <mergeCell ref="V7:X7"/>
-    <mergeCell ref="L56:N56"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="AA55:AC55"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="AM50:AO50"/>
     <mergeCell ref="AH7:AJ7"/>
-    <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C52:AX52"/>
-    <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="K3:P3"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="AG55:AI55"/>
-    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="U31:W31"/>
     <mergeCell ref="Y3:AD3"/>
-    <mergeCell ref="O53:Q53"/>
     <mergeCell ref="R28:T28"/>
-    <mergeCell ref="L53:N53"/>
     <mergeCell ref="AS31:AU31"/>
-    <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="A44:A49"/>
-    <mergeCell ref="C54:E54"/>
     <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="O54:Q54"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="AD31:AF31"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="U56:W56"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="F2:T2"/>
     <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AA54:AC54"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="AJ53:AL53"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="U2:V2"/>
-    <mergeCell ref="AM54:AO54"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="AA56:AC56"/>
     <mergeCell ref="L31:N31"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AS1:AV1"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="C53:E53"/>
     <mergeCell ref="P5:U5"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="X56:Z56"/>
     <mergeCell ref="U9:W9"/>
     <mergeCell ref="AV31:AX31"/>
-    <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="AT7:AV7"/>
-    <mergeCell ref="AM53:AO53"/>
-    <mergeCell ref="F54:H54"/>
     <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="AN6:AS6"/>
-    <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="W2:AD2"/>
     <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="A31:B31"/>
@@ -16777,7 +15808,7 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="C14:AX14 C24:AX24 C35:AX35 C45:AX45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Probing depth" error="Enter PD in mm, 0 to 15." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>15</formula2>
@@ -16795,9 +15826,6 @@
     </dataValidation>
     <dataValidation sqref="C11:AX11 C27:AX27 C32:AX32 C48:AX48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Plaque" error="Use / for plaque." type="list" errorStyle="stop">
       <formula1>"/"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C54:AX54 C56:AX56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Missing tooth or implant" error="Type X under a missing tooth, I under an implant, or leave it empty." type="list">
-      <formula1>"X,I"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -16902,34 +15930,34 @@
       <c r="X1" s="2" t="n"/>
       <c r="Y1" s="2" t="n"/>
       <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AA1" s="67" t="inlineStr">
         <is>
           <t>Re-evaluation minus pre-treatment</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="n"/>
-      <c r="AC1" s="77" t="n"/>
-      <c r="AD1" s="77" t="n"/>
-      <c r="AE1" s="77" t="n"/>
-      <c r="AF1" s="77" t="n"/>
-      <c r="AG1" s="77" t="n"/>
-      <c r="AH1" s="77" t="n"/>
-      <c r="AI1" s="77" t="n"/>
-      <c r="AJ1" s="77" t="n"/>
-      <c r="AK1" s="77" t="n"/>
-      <c r="AL1" s="77" t="n"/>
-      <c r="AM1" s="77" t="n"/>
-      <c r="AN1" s="77" t="n"/>
-      <c r="AO1" s="77" t="n"/>
-      <c r="AP1" s="77" t="n"/>
-      <c r="AQ1" s="77" t="n"/>
-      <c r="AR1" s="77" t="n"/>
-      <c r="AS1" s="77" t="n"/>
-      <c r="AT1" s="77" t="n"/>
-      <c r="AU1" s="77" t="n"/>
-      <c r="AV1" s="77" t="n"/>
-      <c r="AW1" s="77" t="n"/>
-      <c r="AX1" s="77" t="n"/>
+      <c r="AB1" s="67" t="n"/>
+      <c r="AC1" s="67" t="n"/>
+      <c r="AD1" s="67" t="n"/>
+      <c r="AE1" s="67" t="n"/>
+      <c r="AF1" s="67" t="n"/>
+      <c r="AG1" s="67" t="n"/>
+      <c r="AH1" s="67" t="n"/>
+      <c r="AI1" s="67" t="n"/>
+      <c r="AJ1" s="67" t="n"/>
+      <c r="AK1" s="67" t="n"/>
+      <c r="AL1" s="67" t="n"/>
+      <c r="AM1" s="67" t="n"/>
+      <c r="AN1" s="67" t="n"/>
+      <c r="AO1" s="67" t="n"/>
+      <c r="AP1" s="67" t="n"/>
+      <c r="AQ1" s="67" t="n"/>
+      <c r="AR1" s="67" t="n"/>
+      <c r="AS1" s="67" t="n"/>
+      <c r="AT1" s="67" t="n"/>
+      <c r="AU1" s="67" t="n"/>
+      <c r="AV1" s="67" t="n"/>
+      <c r="AW1" s="67" t="n"/>
+      <c r="AX1" s="67" t="n"/>
       <c r="AY1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
@@ -17016,58 +16044,58 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
-      <c r="C3" s="78" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>Green: improvement (PD or CAL reduced). Red: worse. Plaque and BOP rows show the re-evaluation marks.</t>
         </is>
       </c>
-      <c r="D3" s="78" t="n"/>
-      <c r="E3" s="78" t="n"/>
-      <c r="F3" s="78" t="n"/>
-      <c r="G3" s="78" t="n"/>
-      <c r="H3" s="78" t="n"/>
-      <c r="I3" s="78" t="n"/>
-      <c r="J3" s="78" t="n"/>
-      <c r="K3" s="78" t="n"/>
-      <c r="L3" s="78" t="n"/>
-      <c r="M3" s="78" t="n"/>
-      <c r="N3" s="78" t="n"/>
-      <c r="O3" s="78" t="n"/>
-      <c r="P3" s="78" t="n"/>
-      <c r="Q3" s="78" t="n"/>
-      <c r="R3" s="78" t="n"/>
-      <c r="S3" s="78" t="n"/>
-      <c r="T3" s="78" t="n"/>
-      <c r="U3" s="78" t="n"/>
-      <c r="V3" s="78" t="n"/>
-      <c r="W3" s="78" t="n"/>
-      <c r="X3" s="78" t="n"/>
-      <c r="Y3" s="78" t="n"/>
-      <c r="Z3" s="78" t="n"/>
-      <c r="AA3" s="78" t="n"/>
-      <c r="AB3" s="78" t="n"/>
-      <c r="AC3" s="78" t="n"/>
-      <c r="AD3" s="78" t="n"/>
-      <c r="AE3" s="78" t="n"/>
-      <c r="AF3" s="78" t="n"/>
-      <c r="AG3" s="78" t="n"/>
-      <c r="AH3" s="78" t="n"/>
-      <c r="AI3" s="78" t="n"/>
-      <c r="AJ3" s="78" t="n"/>
-      <c r="AK3" s="78" t="n"/>
-      <c r="AL3" s="78" t="n"/>
-      <c r="AM3" s="78" t="n"/>
-      <c r="AN3" s="78" t="n"/>
-      <c r="AO3" s="78" t="n"/>
-      <c r="AP3" s="78" t="n"/>
-      <c r="AQ3" s="78" t="n"/>
-      <c r="AR3" s="78" t="n"/>
-      <c r="AS3" s="78" t="n"/>
-      <c r="AT3" s="78" t="n"/>
-      <c r="AU3" s="78" t="n"/>
-      <c r="AV3" s="78" t="n"/>
-      <c r="AW3" s="78" t="n"/>
-      <c r="AX3" s="78" t="n"/>
+      <c r="D3" s="68" t="n"/>
+      <c r="E3" s="68" t="n"/>
+      <c r="F3" s="68" t="n"/>
+      <c r="G3" s="68" t="n"/>
+      <c r="H3" s="68" t="n"/>
+      <c r="I3" s="68" t="n"/>
+      <c r="J3" s="68" t="n"/>
+      <c r="K3" s="68" t="n"/>
+      <c r="L3" s="68" t="n"/>
+      <c r="M3" s="68" t="n"/>
+      <c r="N3" s="68" t="n"/>
+      <c r="O3" s="68" t="n"/>
+      <c r="P3" s="68" t="n"/>
+      <c r="Q3" s="68" t="n"/>
+      <c r="R3" s="68" t="n"/>
+      <c r="S3" s="68" t="n"/>
+      <c r="T3" s="68" t="n"/>
+      <c r="U3" s="68" t="n"/>
+      <c r="V3" s="68" t="n"/>
+      <c r="W3" s="68" t="n"/>
+      <c r="X3" s="68" t="n"/>
+      <c r="Y3" s="68" t="n"/>
+      <c r="Z3" s="68" t="n"/>
+      <c r="AA3" s="68" t="n"/>
+      <c r="AB3" s="68" t="n"/>
+      <c r="AC3" s="68" t="n"/>
+      <c r="AD3" s="68" t="n"/>
+      <c r="AE3" s="68" t="n"/>
+      <c r="AF3" s="68" t="n"/>
+      <c r="AG3" s="68" t="n"/>
+      <c r="AH3" s="68" t="n"/>
+      <c r="AI3" s="68" t="n"/>
+      <c r="AJ3" s="68" t="n"/>
+      <c r="AK3" s="68" t="n"/>
+      <c r="AL3" s="68" t="n"/>
+      <c r="AM3" s="68" t="n"/>
+      <c r="AN3" s="68" t="n"/>
+      <c r="AO3" s="68" t="n"/>
+      <c r="AP3" s="68" t="n"/>
+      <c r="AQ3" s="68" t="n"/>
+      <c r="AR3" s="68" t="n"/>
+      <c r="AS3" s="68" t="n"/>
+      <c r="AT3" s="68" t="n"/>
+      <c r="AU3" s="68" t="n"/>
+      <c r="AV3" s="68" t="n"/>
+      <c r="AW3" s="68" t="n"/>
+      <c r="AX3" s="68" t="n"/>
       <c r="AY3" s="1" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -17435,195 +16463,195 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="69">
         <f>IF(OR(Eva!C10="",'Pre-Tx'!C10=""),"",Eva!C10-'Pre-Tx'!C10)</f>
         <v/>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="70">
         <f>IF(OR(Eva!D10="",'Pre-Tx'!D10=""),"",Eva!D10-'Pre-Tx'!D10)</f>
         <v/>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="70">
         <f>IF(OR(Eva!E10="",'Pre-Tx'!E10=""),"",Eva!E10-'Pre-Tx'!E10)</f>
         <v/>
       </c>
-      <c r="F10" s="79">
+      <c r="F10" s="69">
         <f>IF(OR(Eva!F10="",'Pre-Tx'!F10=""),"",Eva!F10-'Pre-Tx'!F10)</f>
         <v/>
       </c>
-      <c r="G10" s="80">
+      <c r="G10" s="70">
         <f>IF(OR(Eva!G10="",'Pre-Tx'!G10=""),"",Eva!G10-'Pre-Tx'!G10)</f>
         <v/>
       </c>
-      <c r="H10" s="80">
+      <c r="H10" s="70">
         <f>IF(OR(Eva!H10="",'Pre-Tx'!H10=""),"",Eva!H10-'Pre-Tx'!H10)</f>
         <v/>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="69">
         <f>IF(OR(Eva!I10="",'Pre-Tx'!I10=""),"",Eva!I10-'Pre-Tx'!I10)</f>
         <v/>
       </c>
-      <c r="J10" s="80">
+      <c r="J10" s="70">
         <f>IF(OR(Eva!J10="",'Pre-Tx'!J10=""),"",Eva!J10-'Pre-Tx'!J10)</f>
         <v/>
       </c>
-      <c r="K10" s="80">
+      <c r="K10" s="70">
         <f>IF(OR(Eva!K10="",'Pre-Tx'!K10=""),"",Eva!K10-'Pre-Tx'!K10)</f>
         <v/>
       </c>
-      <c r="L10" s="79">
+      <c r="L10" s="69">
         <f>IF(OR(Eva!L10="",'Pre-Tx'!L10=""),"",Eva!L10-'Pre-Tx'!L10)</f>
         <v/>
       </c>
-      <c r="M10" s="80">
+      <c r="M10" s="70">
         <f>IF(OR(Eva!M10="",'Pre-Tx'!M10=""),"",Eva!M10-'Pre-Tx'!M10)</f>
         <v/>
       </c>
-      <c r="N10" s="80">
+      <c r="N10" s="70">
         <f>IF(OR(Eva!N10="",'Pre-Tx'!N10=""),"",Eva!N10-'Pre-Tx'!N10)</f>
         <v/>
       </c>
-      <c r="O10" s="79">
+      <c r="O10" s="69">
         <f>IF(OR(Eva!O10="",'Pre-Tx'!O10=""),"",Eva!O10-'Pre-Tx'!O10)</f>
         <v/>
       </c>
-      <c r="P10" s="80">
+      <c r="P10" s="70">
         <f>IF(OR(Eva!P10="",'Pre-Tx'!P10=""),"",Eva!P10-'Pre-Tx'!P10)</f>
         <v/>
       </c>
-      <c r="Q10" s="80">
+      <c r="Q10" s="70">
         <f>IF(OR(Eva!Q10="",'Pre-Tx'!Q10=""),"",Eva!Q10-'Pre-Tx'!Q10)</f>
         <v/>
       </c>
-      <c r="R10" s="79">
+      <c r="R10" s="69">
         <f>IF(OR(Eva!R10="",'Pre-Tx'!R10=""),"",Eva!R10-'Pre-Tx'!R10)</f>
         <v/>
       </c>
-      <c r="S10" s="80">
+      <c r="S10" s="70">
         <f>IF(OR(Eva!S10="",'Pre-Tx'!S10=""),"",Eva!S10-'Pre-Tx'!S10)</f>
         <v/>
       </c>
-      <c r="T10" s="80">
+      <c r="T10" s="70">
         <f>IF(OR(Eva!T10="",'Pre-Tx'!T10=""),"",Eva!T10-'Pre-Tx'!T10)</f>
         <v/>
       </c>
-      <c r="U10" s="79">
+      <c r="U10" s="69">
         <f>IF(OR(Eva!U10="",'Pre-Tx'!U10=""),"",Eva!U10-'Pre-Tx'!U10)</f>
         <v/>
       </c>
-      <c r="V10" s="80">
+      <c r="V10" s="70">
         <f>IF(OR(Eva!V10="",'Pre-Tx'!V10=""),"",Eva!V10-'Pre-Tx'!V10)</f>
         <v/>
       </c>
-      <c r="W10" s="80">
+      <c r="W10" s="70">
         <f>IF(OR(Eva!W10="",'Pre-Tx'!W10=""),"",Eva!W10-'Pre-Tx'!W10)</f>
         <v/>
       </c>
-      <c r="X10" s="79">
+      <c r="X10" s="69">
         <f>IF(OR(Eva!X10="",'Pre-Tx'!X10=""),"",Eva!X10-'Pre-Tx'!X10)</f>
         <v/>
       </c>
-      <c r="Y10" s="80">
+      <c r="Y10" s="70">
         <f>IF(OR(Eva!Y10="",'Pre-Tx'!Y10=""),"",Eva!Y10-'Pre-Tx'!Y10)</f>
         <v/>
       </c>
-      <c r="Z10" s="80">
+      <c r="Z10" s="70">
         <f>IF(OR(Eva!Z10="",'Pre-Tx'!Z10=""),"",Eva!Z10-'Pre-Tx'!Z10)</f>
         <v/>
       </c>
-      <c r="AA10" s="81">
+      <c r="AA10" s="71">
         <f>IF(OR(Eva!AA10="",'Pre-Tx'!AA10=""),"",Eva!AA10-'Pre-Tx'!AA10)</f>
         <v/>
       </c>
-      <c r="AB10" s="80">
+      <c r="AB10" s="70">
         <f>IF(OR(Eva!AB10="",'Pre-Tx'!AB10=""),"",Eva!AB10-'Pre-Tx'!AB10)</f>
         <v/>
       </c>
-      <c r="AC10" s="80">
+      <c r="AC10" s="70">
         <f>IF(OR(Eva!AC10="",'Pre-Tx'!AC10=""),"",Eva!AC10-'Pre-Tx'!AC10)</f>
         <v/>
       </c>
-      <c r="AD10" s="79">
+      <c r="AD10" s="69">
         <f>IF(OR(Eva!AD10="",'Pre-Tx'!AD10=""),"",Eva!AD10-'Pre-Tx'!AD10)</f>
         <v/>
       </c>
-      <c r="AE10" s="80">
+      <c r="AE10" s="70">
         <f>IF(OR(Eva!AE10="",'Pre-Tx'!AE10=""),"",Eva!AE10-'Pre-Tx'!AE10)</f>
         <v/>
       </c>
-      <c r="AF10" s="80">
+      <c r="AF10" s="70">
         <f>IF(OR(Eva!AF10="",'Pre-Tx'!AF10=""),"",Eva!AF10-'Pre-Tx'!AF10)</f>
         <v/>
       </c>
-      <c r="AG10" s="79">
+      <c r="AG10" s="69">
         <f>IF(OR(Eva!AG10="",'Pre-Tx'!AG10=""),"",Eva!AG10-'Pre-Tx'!AG10)</f>
         <v/>
       </c>
-      <c r="AH10" s="80">
+      <c r="AH10" s="70">
         <f>IF(OR(Eva!AH10="",'Pre-Tx'!AH10=""),"",Eva!AH10-'Pre-Tx'!AH10)</f>
         <v/>
       </c>
-      <c r="AI10" s="80">
+      <c r="AI10" s="70">
         <f>IF(OR(Eva!AI10="",'Pre-Tx'!AI10=""),"",Eva!AI10-'Pre-Tx'!AI10)</f>
         <v/>
       </c>
-      <c r="AJ10" s="79">
+      <c r="AJ10" s="69">
         <f>IF(OR(Eva!AJ10="",'Pre-Tx'!AJ10=""),"",Eva!AJ10-'Pre-Tx'!AJ10)</f>
         <v/>
       </c>
-      <c r="AK10" s="80">
+      <c r="AK10" s="70">
         <f>IF(OR(Eva!AK10="",'Pre-Tx'!AK10=""),"",Eva!AK10-'Pre-Tx'!AK10)</f>
         <v/>
       </c>
-      <c r="AL10" s="80">
+      <c r="AL10" s="70">
         <f>IF(OR(Eva!AL10="",'Pre-Tx'!AL10=""),"",Eva!AL10-'Pre-Tx'!AL10)</f>
         <v/>
       </c>
-      <c r="AM10" s="79">
+      <c r="AM10" s="69">
         <f>IF(OR(Eva!AM10="",'Pre-Tx'!AM10=""),"",Eva!AM10-'Pre-Tx'!AM10)</f>
         <v/>
       </c>
-      <c r="AN10" s="80">
+      <c r="AN10" s="70">
         <f>IF(OR(Eva!AN10="",'Pre-Tx'!AN10=""),"",Eva!AN10-'Pre-Tx'!AN10)</f>
         <v/>
       </c>
-      <c r="AO10" s="80">
+      <c r="AO10" s="70">
         <f>IF(OR(Eva!AO10="",'Pre-Tx'!AO10=""),"",Eva!AO10-'Pre-Tx'!AO10)</f>
         <v/>
       </c>
-      <c r="AP10" s="79">
+      <c r="AP10" s="69">
         <f>IF(OR(Eva!AP10="",'Pre-Tx'!AP10=""),"",Eva!AP10-'Pre-Tx'!AP10)</f>
         <v/>
       </c>
-      <c r="AQ10" s="80">
+      <c r="AQ10" s="70">
         <f>IF(OR(Eva!AQ10="",'Pre-Tx'!AQ10=""),"",Eva!AQ10-'Pre-Tx'!AQ10)</f>
         <v/>
       </c>
-      <c r="AR10" s="80">
+      <c r="AR10" s="70">
         <f>IF(OR(Eva!AR10="",'Pre-Tx'!AR10=""),"",Eva!AR10-'Pre-Tx'!AR10)</f>
         <v/>
       </c>
-      <c r="AS10" s="79">
+      <c r="AS10" s="69">
         <f>IF(OR(Eva!AS10="",'Pre-Tx'!AS10=""),"",Eva!AS10-'Pre-Tx'!AS10)</f>
         <v/>
       </c>
-      <c r="AT10" s="80">
+      <c r="AT10" s="70">
         <f>IF(OR(Eva!AT10="",'Pre-Tx'!AT10=""),"",Eva!AT10-'Pre-Tx'!AT10)</f>
         <v/>
       </c>
-      <c r="AU10" s="80">
+      <c r="AU10" s="70">
         <f>IF(OR(Eva!AU10="",'Pre-Tx'!AU10=""),"",Eva!AU10-'Pre-Tx'!AU10)</f>
         <v/>
       </c>
-      <c r="AV10" s="79">
+      <c r="AV10" s="69">
         <f>IF(OR(Eva!AV10="",'Pre-Tx'!AV10=""),"",Eva!AV10-'Pre-Tx'!AV10)</f>
         <v/>
       </c>
-      <c r="AW10" s="80">
+      <c r="AW10" s="70">
         <f>IF(OR(Eva!AW10="",'Pre-Tx'!AW10=""),"",Eva!AW10-'Pre-Tx'!AW10)</f>
         <v/>
       </c>
-      <c r="AX10" s="80">
+      <c r="AX10" s="70">
         <f>IF(OR(Eva!AX10="",'Pre-Tx'!AX10=""),"",Eva!AX10-'Pre-Tx'!AX10)</f>
         <v/>
       </c>
@@ -18050,195 +17078,195 @@
           <t>CEJ-GM</t>
         </is>
       </c>
-      <c r="C13" s="79">
+      <c r="C13" s="69">
         <f>IF(OR(Eva!C13="",'Pre-Tx'!C13=""),"",Eva!C13-'Pre-Tx'!C13)</f>
         <v/>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="70">
         <f>IF(OR(Eva!D13="",'Pre-Tx'!D13=""),"",Eva!D13-'Pre-Tx'!D13)</f>
         <v/>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="70">
         <f>IF(OR(Eva!E13="",'Pre-Tx'!E13=""),"",Eva!E13-'Pre-Tx'!E13)</f>
         <v/>
       </c>
-      <c r="F13" s="79">
+      <c r="F13" s="69">
         <f>IF(OR(Eva!F13="",'Pre-Tx'!F13=""),"",Eva!F13-'Pre-Tx'!F13)</f>
         <v/>
       </c>
-      <c r="G13" s="80">
+      <c r="G13" s="70">
         <f>IF(OR(Eva!G13="",'Pre-Tx'!G13=""),"",Eva!G13-'Pre-Tx'!G13)</f>
         <v/>
       </c>
-      <c r="H13" s="80">
+      <c r="H13" s="70">
         <f>IF(OR(Eva!H13="",'Pre-Tx'!H13=""),"",Eva!H13-'Pre-Tx'!H13)</f>
         <v/>
       </c>
-      <c r="I13" s="79">
+      <c r="I13" s="69">
         <f>IF(OR(Eva!I13="",'Pre-Tx'!I13=""),"",Eva!I13-'Pre-Tx'!I13)</f>
         <v/>
       </c>
-      <c r="J13" s="80">
+      <c r="J13" s="70">
         <f>IF(OR(Eva!J13="",'Pre-Tx'!J13=""),"",Eva!J13-'Pre-Tx'!J13)</f>
         <v/>
       </c>
-      <c r="K13" s="80">
+      <c r="K13" s="70">
         <f>IF(OR(Eva!K13="",'Pre-Tx'!K13=""),"",Eva!K13-'Pre-Tx'!K13)</f>
         <v/>
       </c>
-      <c r="L13" s="79">
+      <c r="L13" s="69">
         <f>IF(OR(Eva!L13="",'Pre-Tx'!L13=""),"",Eva!L13-'Pre-Tx'!L13)</f>
         <v/>
       </c>
-      <c r="M13" s="80">
+      <c r="M13" s="70">
         <f>IF(OR(Eva!M13="",'Pre-Tx'!M13=""),"",Eva!M13-'Pre-Tx'!M13)</f>
         <v/>
       </c>
-      <c r="N13" s="80">
+      <c r="N13" s="70">
         <f>IF(OR(Eva!N13="",'Pre-Tx'!N13=""),"",Eva!N13-'Pre-Tx'!N13)</f>
         <v/>
       </c>
-      <c r="O13" s="79">
+      <c r="O13" s="69">
         <f>IF(OR(Eva!O13="",'Pre-Tx'!O13=""),"",Eva!O13-'Pre-Tx'!O13)</f>
         <v/>
       </c>
-      <c r="P13" s="80">
+      <c r="P13" s="70">
         <f>IF(OR(Eva!P13="",'Pre-Tx'!P13=""),"",Eva!P13-'Pre-Tx'!P13)</f>
         <v/>
       </c>
-      <c r="Q13" s="80">
+      <c r="Q13" s="70">
         <f>IF(OR(Eva!Q13="",'Pre-Tx'!Q13=""),"",Eva!Q13-'Pre-Tx'!Q13)</f>
         <v/>
       </c>
-      <c r="R13" s="79">
+      <c r="R13" s="69">
         <f>IF(OR(Eva!R13="",'Pre-Tx'!R13=""),"",Eva!R13-'Pre-Tx'!R13)</f>
         <v/>
       </c>
-      <c r="S13" s="80">
+      <c r="S13" s="70">
         <f>IF(OR(Eva!S13="",'Pre-Tx'!S13=""),"",Eva!S13-'Pre-Tx'!S13)</f>
         <v/>
       </c>
-      <c r="T13" s="80">
+      <c r="T13" s="70">
         <f>IF(OR(Eva!T13="",'Pre-Tx'!T13=""),"",Eva!T13-'Pre-Tx'!T13)</f>
         <v/>
       </c>
-      <c r="U13" s="79">
+      <c r="U13" s="69">
         <f>IF(OR(Eva!U13="",'Pre-Tx'!U13=""),"",Eva!U13-'Pre-Tx'!U13)</f>
         <v/>
       </c>
-      <c r="V13" s="80">
+      <c r="V13" s="70">
         <f>IF(OR(Eva!V13="",'Pre-Tx'!V13=""),"",Eva!V13-'Pre-Tx'!V13)</f>
         <v/>
       </c>
-      <c r="W13" s="80">
+      <c r="W13" s="70">
         <f>IF(OR(Eva!W13="",'Pre-Tx'!W13=""),"",Eva!W13-'Pre-Tx'!W13)</f>
         <v/>
       </c>
-      <c r="X13" s="79">
+      <c r="X13" s="69">
         <f>IF(OR(Eva!X13="",'Pre-Tx'!X13=""),"",Eva!X13-'Pre-Tx'!X13)</f>
         <v/>
       </c>
-      <c r="Y13" s="80">
+      <c r="Y13" s="70">
         <f>IF(OR(Eva!Y13="",'Pre-Tx'!Y13=""),"",Eva!Y13-'Pre-Tx'!Y13)</f>
         <v/>
       </c>
-      <c r="Z13" s="80">
+      <c r="Z13" s="70">
         <f>IF(OR(Eva!Z13="",'Pre-Tx'!Z13=""),"",Eva!Z13-'Pre-Tx'!Z13)</f>
         <v/>
       </c>
-      <c r="AA13" s="81">
+      <c r="AA13" s="71">
         <f>IF(OR(Eva!AA13="",'Pre-Tx'!AA13=""),"",Eva!AA13-'Pre-Tx'!AA13)</f>
         <v/>
       </c>
-      <c r="AB13" s="80">
+      <c r="AB13" s="70">
         <f>IF(OR(Eva!AB13="",'Pre-Tx'!AB13=""),"",Eva!AB13-'Pre-Tx'!AB13)</f>
         <v/>
       </c>
-      <c r="AC13" s="80">
+      <c r="AC13" s="70">
         <f>IF(OR(Eva!AC13="",'Pre-Tx'!AC13=""),"",Eva!AC13-'Pre-Tx'!AC13)</f>
         <v/>
       </c>
-      <c r="AD13" s="79">
+      <c r="AD13" s="69">
         <f>IF(OR(Eva!AD13="",'Pre-Tx'!AD13=""),"",Eva!AD13-'Pre-Tx'!AD13)</f>
         <v/>
       </c>
-      <c r="AE13" s="80">
+      <c r="AE13" s="70">
         <f>IF(OR(Eva!AE13="",'Pre-Tx'!AE13=""),"",Eva!AE13-'Pre-Tx'!AE13)</f>
         <v/>
       </c>
-      <c r="AF13" s="80">
+      <c r="AF13" s="70">
         <f>IF(OR(Eva!AF13="",'Pre-Tx'!AF13=""),"",Eva!AF13-'Pre-Tx'!AF13)</f>
         <v/>
       </c>
-      <c r="AG13" s="79">
+      <c r="AG13" s="69">
         <f>IF(OR(Eva!AG13="",'Pre-Tx'!AG13=""),"",Eva!AG13-'Pre-Tx'!AG13)</f>
         <v/>
       </c>
-      <c r="AH13" s="80">
+      <c r="AH13" s="70">
         <f>IF(OR(Eva!AH13="",'Pre-Tx'!AH13=""),"",Eva!AH13-'Pre-Tx'!AH13)</f>
         <v/>
       </c>
-      <c r="AI13" s="80">
+      <c r="AI13" s="70">
         <f>IF(OR(Eva!AI13="",'Pre-Tx'!AI13=""),"",Eva!AI13-'Pre-Tx'!AI13)</f>
         <v/>
       </c>
-      <c r="AJ13" s="79">
+      <c r="AJ13" s="69">
         <f>IF(OR(Eva!AJ13="",'Pre-Tx'!AJ13=""),"",Eva!AJ13-'Pre-Tx'!AJ13)</f>
         <v/>
       </c>
-      <c r="AK13" s="80">
+      <c r="AK13" s="70">
         <f>IF(OR(Eva!AK13="",'Pre-Tx'!AK13=""),"",Eva!AK13-'Pre-Tx'!AK13)</f>
         <v/>
       </c>
-      <c r="AL13" s="80">
+      <c r="AL13" s="70">
         <f>IF(OR(Eva!AL13="",'Pre-Tx'!AL13=""),"",Eva!AL13-'Pre-Tx'!AL13)</f>
         <v/>
       </c>
-      <c r="AM13" s="79">
+      <c r="AM13" s="69">
         <f>IF(OR(Eva!AM13="",'Pre-Tx'!AM13=""),"",Eva!AM13-'Pre-Tx'!AM13)</f>
         <v/>
       </c>
-      <c r="AN13" s="80">
+      <c r="AN13" s="70">
         <f>IF(OR(Eva!AN13="",'Pre-Tx'!AN13=""),"",Eva!AN13-'Pre-Tx'!AN13)</f>
         <v/>
       </c>
-      <c r="AO13" s="80">
+      <c r="AO13" s="70">
         <f>IF(OR(Eva!AO13="",'Pre-Tx'!AO13=""),"",Eva!AO13-'Pre-Tx'!AO13)</f>
         <v/>
       </c>
-      <c r="AP13" s="79">
+      <c r="AP13" s="69">
         <f>IF(OR(Eva!AP13="",'Pre-Tx'!AP13=""),"",Eva!AP13-'Pre-Tx'!AP13)</f>
         <v/>
       </c>
-      <c r="AQ13" s="80">
+      <c r="AQ13" s="70">
         <f>IF(OR(Eva!AQ13="",'Pre-Tx'!AQ13=""),"",Eva!AQ13-'Pre-Tx'!AQ13)</f>
         <v/>
       </c>
-      <c r="AR13" s="80">
+      <c r="AR13" s="70">
         <f>IF(OR(Eva!AR13="",'Pre-Tx'!AR13=""),"",Eva!AR13-'Pre-Tx'!AR13)</f>
         <v/>
       </c>
-      <c r="AS13" s="79">
+      <c r="AS13" s="69">
         <f>IF(OR(Eva!AS13="",'Pre-Tx'!AS13=""),"",Eva!AS13-'Pre-Tx'!AS13)</f>
         <v/>
       </c>
-      <c r="AT13" s="80">
+      <c r="AT13" s="70">
         <f>IF(OR(Eva!AT13="",'Pre-Tx'!AT13=""),"",Eva!AT13-'Pre-Tx'!AT13)</f>
         <v/>
       </c>
-      <c r="AU13" s="80">
+      <c r="AU13" s="70">
         <f>IF(OR(Eva!AU13="",'Pre-Tx'!AU13=""),"",Eva!AU13-'Pre-Tx'!AU13)</f>
         <v/>
       </c>
-      <c r="AV13" s="79">
+      <c r="AV13" s="69">
         <f>IF(OR(Eva!AV13="",'Pre-Tx'!AV13=""),"",Eva!AV13-'Pre-Tx'!AV13)</f>
         <v/>
       </c>
-      <c r="AW13" s="80">
+      <c r="AW13" s="70">
         <f>IF(OR(Eva!AW13="",'Pre-Tx'!AW13=""),"",Eva!AW13-'Pre-Tx'!AW13)</f>
         <v/>
       </c>
-      <c r="AX13" s="80">
+      <c r="AX13" s="70">
         <f>IF(OR(Eva!AX13="",'Pre-Tx'!AX13=""),"",Eva!AX13-'Pre-Tx'!AX13)</f>
         <v/>
       </c>
@@ -18255,195 +17283,195 @@
           <t>PD</t>
         </is>
       </c>
-      <c r="C14" s="82">
+      <c r="C14" s="72">
         <f>IF(OR(Eva!C14="",'Pre-Tx'!C14=""),"",Eva!C14-'Pre-Tx'!C14)</f>
         <v/>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="73">
         <f>IF(OR(Eva!D14="",'Pre-Tx'!D14=""),"",Eva!D14-'Pre-Tx'!D14)</f>
         <v/>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="73">
         <f>IF(OR(Eva!E14="",'Pre-Tx'!E14=""),"",Eva!E14-'Pre-Tx'!E14)</f>
         <v/>
       </c>
-      <c r="F14" s="82">
+      <c r="F14" s="72">
         <f>IF(OR(Eva!F14="",'Pre-Tx'!F14=""),"",Eva!F14-'Pre-Tx'!F14)</f>
         <v/>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="73">
         <f>IF(OR(Eva!G14="",'Pre-Tx'!G14=""),"",Eva!G14-'Pre-Tx'!G14)</f>
         <v/>
       </c>
-      <c r="H14" s="83">
+      <c r="H14" s="73">
         <f>IF(OR(Eva!H14="",'Pre-Tx'!H14=""),"",Eva!H14-'Pre-Tx'!H14)</f>
         <v/>
       </c>
-      <c r="I14" s="82">
+      <c r="I14" s="72">
         <f>IF(OR(Eva!I14="",'Pre-Tx'!I14=""),"",Eva!I14-'Pre-Tx'!I14)</f>
         <v/>
       </c>
-      <c r="J14" s="83">
+      <c r="J14" s="73">
         <f>IF(OR(Eva!J14="",'Pre-Tx'!J14=""),"",Eva!J14-'Pre-Tx'!J14)</f>
         <v/>
       </c>
-      <c r="K14" s="83">
+      <c r="K14" s="73">
         <f>IF(OR(Eva!K14="",'Pre-Tx'!K14=""),"",Eva!K14-'Pre-Tx'!K14)</f>
         <v/>
       </c>
-      <c r="L14" s="82">
+      <c r="L14" s="72">
         <f>IF(OR(Eva!L14="",'Pre-Tx'!L14=""),"",Eva!L14-'Pre-Tx'!L14)</f>
         <v/>
       </c>
-      <c r="M14" s="83">
+      <c r="M14" s="73">
         <f>IF(OR(Eva!M14="",'Pre-Tx'!M14=""),"",Eva!M14-'Pre-Tx'!M14)</f>
         <v/>
       </c>
-      <c r="N14" s="83">
+      <c r="N14" s="73">
         <f>IF(OR(Eva!N14="",'Pre-Tx'!N14=""),"",Eva!N14-'Pre-Tx'!N14)</f>
         <v/>
       </c>
-      <c r="O14" s="82">
+      <c r="O14" s="72">
         <f>IF(OR(Eva!O14="",'Pre-Tx'!O14=""),"",Eva!O14-'Pre-Tx'!O14)</f>
         <v/>
       </c>
-      <c r="P14" s="83">
+      <c r="P14" s="73">
         <f>IF(OR(Eva!P14="",'Pre-Tx'!P14=""),"",Eva!P14-'Pre-Tx'!P14)</f>
         <v/>
       </c>
-      <c r="Q14" s="83">
+      <c r="Q14" s="73">
         <f>IF(OR(Eva!Q14="",'Pre-Tx'!Q14=""),"",Eva!Q14-'Pre-Tx'!Q14)</f>
         <v/>
       </c>
-      <c r="R14" s="82">
+      <c r="R14" s="72">
         <f>IF(OR(Eva!R14="",'Pre-Tx'!R14=""),"",Eva!R14-'Pre-Tx'!R14)</f>
         <v/>
       </c>
-      <c r="S14" s="83">
+      <c r="S14" s="73">
         <f>IF(OR(Eva!S14="",'Pre-Tx'!S14=""),"",Eva!S14-'Pre-Tx'!S14)</f>
         <v/>
       </c>
-      <c r="T14" s="83">
+      <c r="T14" s="73">
         <f>IF(OR(Eva!T14="",'Pre-Tx'!T14=""),"",Eva!T14-'Pre-Tx'!T14)</f>
         <v/>
       </c>
-      <c r="U14" s="82">
+      <c r="U14" s="72">
         <f>IF(OR(Eva!U14="",'Pre-Tx'!U14=""),"",Eva!U14-'Pre-Tx'!U14)</f>
         <v/>
       </c>
-      <c r="V14" s="83">
+      <c r="V14" s="73">
         <f>IF(OR(Eva!V14="",'Pre-Tx'!V14=""),"",Eva!V14-'Pre-Tx'!V14)</f>
         <v/>
       </c>
-      <c r="W14" s="83">
+      <c r="W14" s="73">
         <f>IF(OR(Eva!W14="",'Pre-Tx'!W14=""),"",Eva!W14-'Pre-Tx'!W14)</f>
         <v/>
       </c>
-      <c r="X14" s="82">
+      <c r="X14" s="72">
         <f>IF(OR(Eva!X14="",'Pre-Tx'!X14=""),"",Eva!X14-'Pre-Tx'!X14)</f>
         <v/>
       </c>
-      <c r="Y14" s="83">
+      <c r="Y14" s="73">
         <f>IF(OR(Eva!Y14="",'Pre-Tx'!Y14=""),"",Eva!Y14-'Pre-Tx'!Y14)</f>
         <v/>
       </c>
-      <c r="Z14" s="83">
+      <c r="Z14" s="73">
         <f>IF(OR(Eva!Z14="",'Pre-Tx'!Z14=""),"",Eva!Z14-'Pre-Tx'!Z14)</f>
         <v/>
       </c>
-      <c r="AA14" s="84">
+      <c r="AA14" s="74">
         <f>IF(OR(Eva!AA14="",'Pre-Tx'!AA14=""),"",Eva!AA14-'Pre-Tx'!AA14)</f>
         <v/>
       </c>
-      <c r="AB14" s="83">
+      <c r="AB14" s="73">
         <f>IF(OR(Eva!AB14="",'Pre-Tx'!AB14=""),"",Eva!AB14-'Pre-Tx'!AB14)</f>
         <v/>
       </c>
-      <c r="AC14" s="83">
+      <c r="AC14" s="73">
         <f>IF(OR(Eva!AC14="",'Pre-Tx'!AC14=""),"",Eva!AC14-'Pre-Tx'!AC14)</f>
         <v/>
       </c>
-      <c r="AD14" s="82">
+      <c r="AD14" s="72">
         <f>IF(OR(Eva!AD14="",'Pre-Tx'!AD14=""),"",Eva!AD14-'Pre-Tx'!AD14)</f>
         <v/>
       </c>
-      <c r="AE14" s="83">
+      <c r="AE14" s="73">
         <f>IF(OR(Eva!AE14="",'Pre-Tx'!AE14=""),"",Eva!AE14-'Pre-Tx'!AE14)</f>
         <v/>
       </c>
-      <c r="AF14" s="83">
+      <c r="AF14" s="73">
         <f>IF(OR(Eva!AF14="",'Pre-Tx'!AF14=""),"",Eva!AF14-'Pre-Tx'!AF14)</f>
         <v/>
       </c>
-      <c r="AG14" s="82">
+      <c r="AG14" s="72">
         <f>IF(OR(Eva!AG14="",'Pre-Tx'!AG14=""),"",Eva!AG14-'Pre-Tx'!AG14)</f>
         <v/>
       </c>
-      <c r="AH14" s="83">
+      <c r="AH14" s="73">
         <f>IF(OR(Eva!AH14="",'Pre-Tx'!AH14=""),"",Eva!AH14-'Pre-Tx'!AH14)</f>
         <v/>
       </c>
-      <c r="AI14" s="83">
+      <c r="AI14" s="73">
         <f>IF(OR(Eva!AI14="",'Pre-Tx'!AI14=""),"",Eva!AI14-'Pre-Tx'!AI14)</f>
         <v/>
       </c>
-      <c r="AJ14" s="82">
+      <c r="AJ14" s="72">
         <f>IF(OR(Eva!AJ14="",'Pre-Tx'!AJ14=""),"",Eva!AJ14-'Pre-Tx'!AJ14)</f>
         <v/>
       </c>
-      <c r="AK14" s="83">
+      <c r="AK14" s="73">
         <f>IF(OR(Eva!AK14="",'Pre-Tx'!AK14=""),"",Eva!AK14-'Pre-Tx'!AK14)</f>
         <v/>
       </c>
-      <c r="AL14" s="83">
+      <c r="AL14" s="73">
         <f>IF(OR(Eva!AL14="",'Pre-Tx'!AL14=""),"",Eva!AL14-'Pre-Tx'!AL14)</f>
         <v/>
       </c>
-      <c r="AM14" s="82">
+      <c r="AM14" s="72">
         <f>IF(OR(Eva!AM14="",'Pre-Tx'!AM14=""),"",Eva!AM14-'Pre-Tx'!AM14)</f>
         <v/>
       </c>
-      <c r="AN14" s="83">
+      <c r="AN14" s="73">
         <f>IF(OR(Eva!AN14="",'Pre-Tx'!AN14=""),"",Eva!AN14-'Pre-Tx'!AN14)</f>
         <v/>
       </c>
-      <c r="AO14" s="83">
+      <c r="AO14" s="73">
         <f>IF(OR(Eva!AO14="",'Pre-Tx'!AO14=""),"",Eva!AO14-'Pre-Tx'!AO14)</f>
         <v/>
       </c>
-      <c r="AP14" s="82">
+      <c r="AP14" s="72">
         <f>IF(OR(Eva!AP14="",'Pre-Tx'!AP14=""),"",Eva!AP14-'Pre-Tx'!AP14)</f>
         <v/>
       </c>
-      <c r="AQ14" s="83">
+      <c r="AQ14" s="73">
         <f>IF(OR(Eva!AQ14="",'Pre-Tx'!AQ14=""),"",Eva!AQ14-'Pre-Tx'!AQ14)</f>
         <v/>
       </c>
-      <c r="AR14" s="83">
+      <c r="AR14" s="73">
         <f>IF(OR(Eva!AR14="",'Pre-Tx'!AR14=""),"",Eva!AR14-'Pre-Tx'!AR14)</f>
         <v/>
       </c>
-      <c r="AS14" s="82">
+      <c r="AS14" s="72">
         <f>IF(OR(Eva!AS14="",'Pre-Tx'!AS14=""),"",Eva!AS14-'Pre-Tx'!AS14)</f>
         <v/>
       </c>
-      <c r="AT14" s="83">
+      <c r="AT14" s="73">
         <f>IF(OR(Eva!AT14="",'Pre-Tx'!AT14=""),"",Eva!AT14-'Pre-Tx'!AT14)</f>
         <v/>
       </c>
-      <c r="AU14" s="83">
+      <c r="AU14" s="73">
         <f>IF(OR(Eva!AU14="",'Pre-Tx'!AU14=""),"",Eva!AU14-'Pre-Tx'!AU14)</f>
         <v/>
       </c>
-      <c r="AV14" s="82">
+      <c r="AV14" s="72">
         <f>IF(OR(Eva!AV14="",'Pre-Tx'!AV14=""),"",Eva!AV14-'Pre-Tx'!AV14)</f>
         <v/>
       </c>
-      <c r="AW14" s="83">
+      <c r="AW14" s="73">
         <f>IF(OR(Eva!AW14="",'Pre-Tx'!AW14=""),"",Eva!AW14-'Pre-Tx'!AW14)</f>
         <v/>
       </c>
-      <c r="AX14" s="83">
+      <c r="AX14" s="73">
         <f>IF(OR(Eva!AX14="",'Pre-Tx'!AX14=""),"",Eva!AX14-'Pre-Tx'!AX14)</f>
         <v/>
       </c>
@@ -18460,195 +17488,195 @@
           <t>CAL</t>
         </is>
       </c>
-      <c r="C15" s="85">
+      <c r="C15" s="75">
         <f>IF(OR(Eva!C15="",'Pre-Tx'!C15=""),"",Eva!C15-'Pre-Tx'!C15)</f>
         <v/>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="76">
         <f>IF(OR(Eva!D15="",'Pre-Tx'!D15=""),"",Eva!D15-'Pre-Tx'!D15)</f>
         <v/>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="76">
         <f>IF(OR(Eva!E15="",'Pre-Tx'!E15=""),"",Eva!E15-'Pre-Tx'!E15)</f>
         <v/>
       </c>
-      <c r="F15" s="85">
+      <c r="F15" s="75">
         <f>IF(OR(Eva!F15="",'Pre-Tx'!F15=""),"",Eva!F15-'Pre-Tx'!F15)</f>
         <v/>
       </c>
-      <c r="G15" s="86">
+      <c r="G15" s="76">
         <f>IF(OR(Eva!G15="",'Pre-Tx'!G15=""),"",Eva!G15-'Pre-Tx'!G15)</f>
         <v/>
       </c>
-      <c r="H15" s="86">
+      <c r="H15" s="76">
         <f>IF(OR(Eva!H15="",'Pre-Tx'!H15=""),"",Eva!H15-'Pre-Tx'!H15)</f>
         <v/>
       </c>
-      <c r="I15" s="85">
+      <c r="I15" s="75">
         <f>IF(OR(Eva!I15="",'Pre-Tx'!I15=""),"",Eva!I15-'Pre-Tx'!I15)</f>
         <v/>
       </c>
-      <c r="J15" s="86">
+      <c r="J15" s="76">
         <f>IF(OR(Eva!J15="",'Pre-Tx'!J15=""),"",Eva!J15-'Pre-Tx'!J15)</f>
         <v/>
       </c>
-      <c r="K15" s="86">
+      <c r="K15" s="76">
         <f>IF(OR(Eva!K15="",'Pre-Tx'!K15=""),"",Eva!K15-'Pre-Tx'!K15)</f>
         <v/>
       </c>
-      <c r="L15" s="85">
+      <c r="L15" s="75">
         <f>IF(OR(Eva!L15="",'Pre-Tx'!L15=""),"",Eva!L15-'Pre-Tx'!L15)</f>
         <v/>
       </c>
-      <c r="M15" s="86">
+      <c r="M15" s="76">
         <f>IF(OR(Eva!M15="",'Pre-Tx'!M15=""),"",Eva!M15-'Pre-Tx'!M15)</f>
         <v/>
       </c>
-      <c r="N15" s="86">
+      <c r="N15" s="76">
         <f>IF(OR(Eva!N15="",'Pre-Tx'!N15=""),"",Eva!N15-'Pre-Tx'!N15)</f>
         <v/>
       </c>
-      <c r="O15" s="85">
+      <c r="O15" s="75">
         <f>IF(OR(Eva!O15="",'Pre-Tx'!O15=""),"",Eva!O15-'Pre-Tx'!O15)</f>
         <v/>
       </c>
-      <c r="P15" s="86">
+      <c r="P15" s="76">
         <f>IF(OR(Eva!P15="",'Pre-Tx'!P15=""),"",Eva!P15-'Pre-Tx'!P15)</f>
         <v/>
       </c>
-      <c r="Q15" s="86">
+      <c r="Q15" s="76">
         <f>IF(OR(Eva!Q15="",'Pre-Tx'!Q15=""),"",Eva!Q15-'Pre-Tx'!Q15)</f>
         <v/>
       </c>
-      <c r="R15" s="85">
+      <c r="R15" s="75">
         <f>IF(OR(Eva!R15="",'Pre-Tx'!R15=""),"",Eva!R15-'Pre-Tx'!R15)</f>
         <v/>
       </c>
-      <c r="S15" s="86">
+      <c r="S15" s="76">
         <f>IF(OR(Eva!S15="",'Pre-Tx'!S15=""),"",Eva!S15-'Pre-Tx'!S15)</f>
         <v/>
       </c>
-      <c r="T15" s="86">
+      <c r="T15" s="76">
         <f>IF(OR(Eva!T15="",'Pre-Tx'!T15=""),"",Eva!T15-'Pre-Tx'!T15)</f>
         <v/>
       </c>
-      <c r="U15" s="85">
+      <c r="U15" s="75">
         <f>IF(OR(Eva!U15="",'Pre-Tx'!U15=""),"",Eva!U15-'Pre-Tx'!U15)</f>
         <v/>
       </c>
-      <c r="V15" s="86">
+      <c r="V15" s="76">
         <f>IF(OR(Eva!V15="",'Pre-Tx'!V15=""),"",Eva!V15-'Pre-Tx'!V15)</f>
         <v/>
       </c>
-      <c r="W15" s="86">
+      <c r="W15" s="76">
         <f>IF(OR(Eva!W15="",'Pre-Tx'!W15=""),"",Eva!W15-'Pre-Tx'!W15)</f>
         <v/>
       </c>
-      <c r="X15" s="85">
+      <c r="X15" s="75">
         <f>IF(OR(Eva!X15="",'Pre-Tx'!X15=""),"",Eva!X15-'Pre-Tx'!X15)</f>
         <v/>
       </c>
-      <c r="Y15" s="86">
+      <c r="Y15" s="76">
         <f>IF(OR(Eva!Y15="",'Pre-Tx'!Y15=""),"",Eva!Y15-'Pre-Tx'!Y15)</f>
         <v/>
       </c>
-      <c r="Z15" s="86">
+      <c r="Z15" s="76">
         <f>IF(OR(Eva!Z15="",'Pre-Tx'!Z15=""),"",Eva!Z15-'Pre-Tx'!Z15)</f>
         <v/>
       </c>
-      <c r="AA15" s="87">
+      <c r="AA15" s="77">
         <f>IF(OR(Eva!AA15="",'Pre-Tx'!AA15=""),"",Eva!AA15-'Pre-Tx'!AA15)</f>
         <v/>
       </c>
-      <c r="AB15" s="86">
+      <c r="AB15" s="76">
         <f>IF(OR(Eva!AB15="",'Pre-Tx'!AB15=""),"",Eva!AB15-'Pre-Tx'!AB15)</f>
         <v/>
       </c>
-      <c r="AC15" s="86">
+      <c r="AC15" s="76">
         <f>IF(OR(Eva!AC15="",'Pre-Tx'!AC15=""),"",Eva!AC15-'Pre-Tx'!AC15)</f>
         <v/>
       </c>
-      <c r="AD15" s="85">
+      <c r="AD15" s="75">
         <f>IF(OR(Eva!AD15="",'Pre-Tx'!AD15=""),"",Eva!AD15-'Pre-Tx'!AD15)</f>
         <v/>
       </c>
-      <c r="AE15" s="86">
+      <c r="AE15" s="76">
         <f>IF(OR(Eva!AE15="",'Pre-Tx'!AE15=""),"",Eva!AE15-'Pre-Tx'!AE15)</f>
         <v/>
       </c>
-      <c r="AF15" s="86">
+      <c r="AF15" s="76">
         <f>IF(OR(Eva!AF15="",'Pre-Tx'!AF15=""),"",Eva!AF15-'Pre-Tx'!AF15)</f>
         <v/>
       </c>
-      <c r="AG15" s="85">
+      <c r="AG15" s="75">
         <f>IF(OR(Eva!AG15="",'Pre-Tx'!AG15=""),"",Eva!AG15-'Pre-Tx'!AG15)</f>
         <v/>
       </c>
-      <c r="AH15" s="86">
+      <c r="AH15" s="76">
         <f>IF(OR(Eva!AH15="",'Pre-Tx'!AH15=""),"",Eva!AH15-'Pre-Tx'!AH15)</f>
         <v/>
       </c>
-      <c r="AI15" s="86">
+      <c r="AI15" s="76">
         <f>IF(OR(Eva!AI15="",'Pre-Tx'!AI15=""),"",Eva!AI15-'Pre-Tx'!AI15)</f>
         <v/>
       </c>
-      <c r="AJ15" s="85">
+      <c r="AJ15" s="75">
         <f>IF(OR(Eva!AJ15="",'Pre-Tx'!AJ15=""),"",Eva!AJ15-'Pre-Tx'!AJ15)</f>
         <v/>
       </c>
-      <c r="AK15" s="86">
+      <c r="AK15" s="76">
         <f>IF(OR(Eva!AK15="",'Pre-Tx'!AK15=""),"",Eva!AK15-'Pre-Tx'!AK15)</f>
         <v/>
       </c>
-      <c r="AL15" s="86">
+      <c r="AL15" s="76">
         <f>IF(OR(Eva!AL15="",'Pre-Tx'!AL15=""),"",Eva!AL15-'Pre-Tx'!AL15)</f>
         <v/>
       </c>
-      <c r="AM15" s="85">
+      <c r="AM15" s="75">
         <f>IF(OR(Eva!AM15="",'Pre-Tx'!AM15=""),"",Eva!AM15-'Pre-Tx'!AM15)</f>
         <v/>
       </c>
-      <c r="AN15" s="86">
+      <c r="AN15" s="76">
         <f>IF(OR(Eva!AN15="",'Pre-Tx'!AN15=""),"",Eva!AN15-'Pre-Tx'!AN15)</f>
         <v/>
       </c>
-      <c r="AO15" s="86">
+      <c r="AO15" s="76">
         <f>IF(OR(Eva!AO15="",'Pre-Tx'!AO15=""),"",Eva!AO15-'Pre-Tx'!AO15)</f>
         <v/>
       </c>
-      <c r="AP15" s="85">
+      <c r="AP15" s="75">
         <f>IF(OR(Eva!AP15="",'Pre-Tx'!AP15=""),"",Eva!AP15-'Pre-Tx'!AP15)</f>
         <v/>
       </c>
-      <c r="AQ15" s="86">
+      <c r="AQ15" s="76">
         <f>IF(OR(Eva!AQ15="",'Pre-Tx'!AQ15=""),"",Eva!AQ15-'Pre-Tx'!AQ15)</f>
         <v/>
       </c>
-      <c r="AR15" s="86">
+      <c r="AR15" s="76">
         <f>IF(OR(Eva!AR15="",'Pre-Tx'!AR15=""),"",Eva!AR15-'Pre-Tx'!AR15)</f>
         <v/>
       </c>
-      <c r="AS15" s="85">
+      <c r="AS15" s="75">
         <f>IF(OR(Eva!AS15="",'Pre-Tx'!AS15=""),"",Eva!AS15-'Pre-Tx'!AS15)</f>
         <v/>
       </c>
-      <c r="AT15" s="86">
+      <c r="AT15" s="76">
         <f>IF(OR(Eva!AT15="",'Pre-Tx'!AT15=""),"",Eva!AT15-'Pre-Tx'!AT15)</f>
         <v/>
       </c>
-      <c r="AU15" s="86">
+      <c r="AU15" s="76">
         <f>IF(OR(Eva!AU15="",'Pre-Tx'!AU15=""),"",Eva!AU15-'Pre-Tx'!AU15)</f>
         <v/>
       </c>
-      <c r="AV15" s="85">
+      <c r="AV15" s="75">
         <f>IF(OR(Eva!AV15="",'Pre-Tx'!AV15=""),"",Eva!AV15-'Pre-Tx'!AV15)</f>
         <v/>
       </c>
-      <c r="AW15" s="86">
+      <c r="AW15" s="76">
         <f>IF(OR(Eva!AW15="",'Pre-Tx'!AW15=""),"",Eva!AW15-'Pre-Tx'!AW15)</f>
         <v/>
       </c>
-      <c r="AX15" s="86">
+      <c r="AX15" s="76">
         <f>IF(OR(Eva!AX15="",'Pre-Tx'!AX15=""),"",Eva!AX15-'Pre-Tx'!AX15)</f>
         <v/>
       </c>
@@ -19040,195 +18068,195 @@
           <t>CAL</t>
         </is>
       </c>
-      <c r="C23" s="88">
+      <c r="C23" s="78">
         <f>IF(OR(Eva!C23="",'Pre-Tx'!C23=""),"",Eva!C23-'Pre-Tx'!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="89">
+      <c r="D23" s="79">
         <f>IF(OR(Eva!D23="",'Pre-Tx'!D23=""),"",Eva!D23-'Pre-Tx'!D23)</f>
         <v/>
       </c>
-      <c r="E23" s="89">
+      <c r="E23" s="79">
         <f>IF(OR(Eva!E23="",'Pre-Tx'!E23=""),"",Eva!E23-'Pre-Tx'!E23)</f>
         <v/>
       </c>
-      <c r="F23" s="88">
+      <c r="F23" s="78">
         <f>IF(OR(Eva!F23="",'Pre-Tx'!F23=""),"",Eva!F23-'Pre-Tx'!F23)</f>
         <v/>
       </c>
-      <c r="G23" s="89">
+      <c r="G23" s="79">
         <f>IF(OR(Eva!G23="",'Pre-Tx'!G23=""),"",Eva!G23-'Pre-Tx'!G23)</f>
         <v/>
       </c>
-      <c r="H23" s="89">
+      <c r="H23" s="79">
         <f>IF(OR(Eva!H23="",'Pre-Tx'!H23=""),"",Eva!H23-'Pre-Tx'!H23)</f>
         <v/>
       </c>
-      <c r="I23" s="88">
+      <c r="I23" s="78">
         <f>IF(OR(Eva!I23="",'Pre-Tx'!I23=""),"",Eva!I23-'Pre-Tx'!I23)</f>
         <v/>
       </c>
-      <c r="J23" s="89">
+      <c r="J23" s="79">
         <f>IF(OR(Eva!J23="",'Pre-Tx'!J23=""),"",Eva!J23-'Pre-Tx'!J23)</f>
         <v/>
       </c>
-      <c r="K23" s="89">
+      <c r="K23" s="79">
         <f>IF(OR(Eva!K23="",'Pre-Tx'!K23=""),"",Eva!K23-'Pre-Tx'!K23)</f>
         <v/>
       </c>
-      <c r="L23" s="88">
+      <c r="L23" s="78">
         <f>IF(OR(Eva!L23="",'Pre-Tx'!L23=""),"",Eva!L23-'Pre-Tx'!L23)</f>
         <v/>
       </c>
-      <c r="M23" s="89">
+      <c r="M23" s="79">
         <f>IF(OR(Eva!M23="",'Pre-Tx'!M23=""),"",Eva!M23-'Pre-Tx'!M23)</f>
         <v/>
       </c>
-      <c r="N23" s="89">
+      <c r="N23" s="79">
         <f>IF(OR(Eva!N23="",'Pre-Tx'!N23=""),"",Eva!N23-'Pre-Tx'!N23)</f>
         <v/>
       </c>
-      <c r="O23" s="88">
+      <c r="O23" s="78">
         <f>IF(OR(Eva!O23="",'Pre-Tx'!O23=""),"",Eva!O23-'Pre-Tx'!O23)</f>
         <v/>
       </c>
-      <c r="P23" s="89">
+      <c r="P23" s="79">
         <f>IF(OR(Eva!P23="",'Pre-Tx'!P23=""),"",Eva!P23-'Pre-Tx'!P23)</f>
         <v/>
       </c>
-      <c r="Q23" s="89">
+      <c r="Q23" s="79">
         <f>IF(OR(Eva!Q23="",'Pre-Tx'!Q23=""),"",Eva!Q23-'Pre-Tx'!Q23)</f>
         <v/>
       </c>
-      <c r="R23" s="88">
+      <c r="R23" s="78">
         <f>IF(OR(Eva!R23="",'Pre-Tx'!R23=""),"",Eva!R23-'Pre-Tx'!R23)</f>
         <v/>
       </c>
-      <c r="S23" s="89">
+      <c r="S23" s="79">
         <f>IF(OR(Eva!S23="",'Pre-Tx'!S23=""),"",Eva!S23-'Pre-Tx'!S23)</f>
         <v/>
       </c>
-      <c r="T23" s="89">
+      <c r="T23" s="79">
         <f>IF(OR(Eva!T23="",'Pre-Tx'!T23=""),"",Eva!T23-'Pre-Tx'!T23)</f>
         <v/>
       </c>
-      <c r="U23" s="88">
+      <c r="U23" s="78">
         <f>IF(OR(Eva!U23="",'Pre-Tx'!U23=""),"",Eva!U23-'Pre-Tx'!U23)</f>
         <v/>
       </c>
-      <c r="V23" s="89">
+      <c r="V23" s="79">
         <f>IF(OR(Eva!V23="",'Pre-Tx'!V23=""),"",Eva!V23-'Pre-Tx'!V23)</f>
         <v/>
       </c>
-      <c r="W23" s="89">
+      <c r="W23" s="79">
         <f>IF(OR(Eva!W23="",'Pre-Tx'!W23=""),"",Eva!W23-'Pre-Tx'!W23)</f>
         <v/>
       </c>
-      <c r="X23" s="88">
+      <c r="X23" s="78">
         <f>IF(OR(Eva!X23="",'Pre-Tx'!X23=""),"",Eva!X23-'Pre-Tx'!X23)</f>
         <v/>
       </c>
-      <c r="Y23" s="89">
+      <c r="Y23" s="79">
         <f>IF(OR(Eva!Y23="",'Pre-Tx'!Y23=""),"",Eva!Y23-'Pre-Tx'!Y23)</f>
         <v/>
       </c>
-      <c r="Z23" s="89">
+      <c r="Z23" s="79">
         <f>IF(OR(Eva!Z23="",'Pre-Tx'!Z23=""),"",Eva!Z23-'Pre-Tx'!Z23)</f>
         <v/>
       </c>
-      <c r="AA23" s="90">
+      <c r="AA23" s="80">
         <f>IF(OR(Eva!AA23="",'Pre-Tx'!AA23=""),"",Eva!AA23-'Pre-Tx'!AA23)</f>
         <v/>
       </c>
-      <c r="AB23" s="89">
+      <c r="AB23" s="79">
         <f>IF(OR(Eva!AB23="",'Pre-Tx'!AB23=""),"",Eva!AB23-'Pre-Tx'!AB23)</f>
         <v/>
       </c>
-      <c r="AC23" s="89">
+      <c r="AC23" s="79">
         <f>IF(OR(Eva!AC23="",'Pre-Tx'!AC23=""),"",Eva!AC23-'Pre-Tx'!AC23)</f>
         <v/>
       </c>
-      <c r="AD23" s="88">
+      <c r="AD23" s="78">
         <f>IF(OR(Eva!AD23="",'Pre-Tx'!AD23=""),"",Eva!AD23-'Pre-Tx'!AD23)</f>
         <v/>
       </c>
-      <c r="AE23" s="89">
+      <c r="AE23" s="79">
         <f>IF(OR(Eva!AE23="",'Pre-Tx'!AE23=""),"",Eva!AE23-'Pre-Tx'!AE23)</f>
         <v/>
       </c>
-      <c r="AF23" s="89">
+      <c r="AF23" s="79">
         <f>IF(OR(Eva!AF23="",'Pre-Tx'!AF23=""),"",Eva!AF23-'Pre-Tx'!AF23)</f>
         <v/>
       </c>
-      <c r="AG23" s="88">
+      <c r="AG23" s="78">
         <f>IF(OR(Eva!AG23="",'Pre-Tx'!AG23=""),"",Eva!AG23-'Pre-Tx'!AG23)</f>
         <v/>
       </c>
-      <c r="AH23" s="89">
+      <c r="AH23" s="79">
         <f>IF(OR(Eva!AH23="",'Pre-Tx'!AH23=""),"",Eva!AH23-'Pre-Tx'!AH23)</f>
         <v/>
       </c>
-      <c r="AI23" s="89">
+      <c r="AI23" s="79">
         <f>IF(OR(Eva!AI23="",'Pre-Tx'!AI23=""),"",Eva!AI23-'Pre-Tx'!AI23)</f>
         <v/>
       </c>
-      <c r="AJ23" s="88">
+      <c r="AJ23" s="78">
         <f>IF(OR(Eva!AJ23="",'Pre-Tx'!AJ23=""),"",Eva!AJ23-'Pre-Tx'!AJ23)</f>
         <v/>
       </c>
-      <c r="AK23" s="89">
+      <c r="AK23" s="79">
         <f>IF(OR(Eva!AK23="",'Pre-Tx'!AK23=""),"",Eva!AK23-'Pre-Tx'!AK23)</f>
         <v/>
       </c>
-      <c r="AL23" s="89">
+      <c r="AL23" s="79">
         <f>IF(OR(Eva!AL23="",'Pre-Tx'!AL23=""),"",Eva!AL23-'Pre-Tx'!AL23)</f>
         <v/>
       </c>
-      <c r="AM23" s="88">
+      <c r="AM23" s="78">
         <f>IF(OR(Eva!AM23="",'Pre-Tx'!AM23=""),"",Eva!AM23-'Pre-Tx'!AM23)</f>
         <v/>
       </c>
-      <c r="AN23" s="89">
+      <c r="AN23" s="79">
         <f>IF(OR(Eva!AN23="",'Pre-Tx'!AN23=""),"",Eva!AN23-'Pre-Tx'!AN23)</f>
         <v/>
       </c>
-      <c r="AO23" s="89">
+      <c r="AO23" s="79">
         <f>IF(OR(Eva!AO23="",'Pre-Tx'!AO23=""),"",Eva!AO23-'Pre-Tx'!AO23)</f>
         <v/>
       </c>
-      <c r="AP23" s="88">
+      <c r="AP23" s="78">
         <f>IF(OR(Eva!AP23="",'Pre-Tx'!AP23=""),"",Eva!AP23-'Pre-Tx'!AP23)</f>
         <v/>
       </c>
-      <c r="AQ23" s="89">
+      <c r="AQ23" s="79">
         <f>IF(OR(Eva!AQ23="",'Pre-Tx'!AQ23=""),"",Eva!AQ23-'Pre-Tx'!AQ23)</f>
         <v/>
       </c>
-      <c r="AR23" s="89">
+      <c r="AR23" s="79">
         <f>IF(OR(Eva!AR23="",'Pre-Tx'!AR23=""),"",Eva!AR23-'Pre-Tx'!AR23)</f>
         <v/>
       </c>
-      <c r="AS23" s="88">
+      <c r="AS23" s="78">
         <f>IF(OR(Eva!AS23="",'Pre-Tx'!AS23=""),"",Eva!AS23-'Pre-Tx'!AS23)</f>
         <v/>
       </c>
-      <c r="AT23" s="89">
+      <c r="AT23" s="79">
         <f>IF(OR(Eva!AT23="",'Pre-Tx'!AT23=""),"",Eva!AT23-'Pre-Tx'!AT23)</f>
         <v/>
       </c>
-      <c r="AU23" s="89">
+      <c r="AU23" s="79">
         <f>IF(OR(Eva!AU23="",'Pre-Tx'!AU23=""),"",Eva!AU23-'Pre-Tx'!AU23)</f>
         <v/>
       </c>
-      <c r="AV23" s="88">
+      <c r="AV23" s="78">
         <f>IF(OR(Eva!AV23="",'Pre-Tx'!AV23=""),"",Eva!AV23-'Pre-Tx'!AV23)</f>
         <v/>
       </c>
-      <c r="AW23" s="89">
+      <c r="AW23" s="79">
         <f>IF(OR(Eva!AW23="",'Pre-Tx'!AW23=""),"",Eva!AW23-'Pre-Tx'!AW23)</f>
         <v/>
       </c>
-      <c r="AX23" s="89">
+      <c r="AX23" s="79">
         <f>IF(OR(Eva!AX23="",'Pre-Tx'!AX23=""),"",Eva!AX23-'Pre-Tx'!AX23)</f>
         <v/>
       </c>
@@ -19245,195 +18273,195 @@
           <t>PD</t>
         </is>
       </c>
-      <c r="C24" s="82">
+      <c r="C24" s="72">
         <f>IF(OR(Eva!C24="",'Pre-Tx'!C24=""),"",Eva!C24-'Pre-Tx'!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="83">
+      <c r="D24" s="73">
         <f>IF(OR(Eva!D24="",'Pre-Tx'!D24=""),"",Eva!D24-'Pre-Tx'!D24)</f>
         <v/>
       </c>
-      <c r="E24" s="83">
+      <c r="E24" s="73">
         <f>IF(OR(Eva!E24="",'Pre-Tx'!E24=""),"",Eva!E24-'Pre-Tx'!E24)</f>
         <v/>
       </c>
-      <c r="F24" s="82">
+      <c r="F24" s="72">
         <f>IF(OR(Eva!F24="",'Pre-Tx'!F24=""),"",Eva!F24-'Pre-Tx'!F24)</f>
         <v/>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="73">
         <f>IF(OR(Eva!G24="",'Pre-Tx'!G24=""),"",Eva!G24-'Pre-Tx'!G24)</f>
         <v/>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="73">
         <f>IF(OR(Eva!H24="",'Pre-Tx'!H24=""),"",Eva!H24-'Pre-Tx'!H24)</f>
         <v/>
       </c>
-      <c r="I24" s="82">
+      <c r="I24" s="72">
         <f>IF(OR(Eva!I24="",'Pre-Tx'!I24=""),"",Eva!I24-'Pre-Tx'!I24)</f>
         <v/>
       </c>
-      <c r="J24" s="83">
+      <c r="J24" s="73">
         <f>IF(OR(Eva!J24="",'Pre-Tx'!J24=""),"",Eva!J24-'Pre-Tx'!J24)</f>
         <v/>
       </c>
-      <c r="K24" s="83">
+      <c r="K24" s="73">
         <f>IF(OR(Eva!K24="",'Pre-Tx'!K24=""),"",Eva!K24-'Pre-Tx'!K24)</f>
         <v/>
       </c>
-      <c r="L24" s="82">
+      <c r="L24" s="72">
         <f>IF(OR(Eva!L24="",'Pre-Tx'!L24=""),"",Eva!L24-'Pre-Tx'!L24)</f>
         <v/>
       </c>
-      <c r="M24" s="83">
+      <c r="M24" s="73">
         <f>IF(OR(Eva!M24="",'Pre-Tx'!M24=""),"",Eva!M24-'Pre-Tx'!M24)</f>
         <v/>
       </c>
-      <c r="N24" s="83">
+      <c r="N24" s="73">
         <f>IF(OR(Eva!N24="",'Pre-Tx'!N24=""),"",Eva!N24-'Pre-Tx'!N24)</f>
         <v/>
       </c>
-      <c r="O24" s="82">
+      <c r="O24" s="72">
         <f>IF(OR(Eva!O24="",'Pre-Tx'!O24=""),"",Eva!O24-'Pre-Tx'!O24)</f>
         <v/>
       </c>
-      <c r="P24" s="83">
+      <c r="P24" s="73">
         <f>IF(OR(Eva!P24="",'Pre-Tx'!P24=""),"",Eva!P24-'Pre-Tx'!P24)</f>
         <v/>
       </c>
-      <c r="Q24" s="83">
+      <c r="Q24" s="73">
         <f>IF(OR(Eva!Q24="",'Pre-Tx'!Q24=""),"",Eva!Q24-'Pre-Tx'!Q24)</f>
         <v/>
       </c>
-      <c r="R24" s="82">
+      <c r="R24" s="72">
         <f>IF(OR(Eva!R24="",'Pre-Tx'!R24=""),"",Eva!R24-'Pre-Tx'!R24)</f>
         <v/>
       </c>
-      <c r="S24" s="83">
+      <c r="S24" s="73">
         <f>IF(OR(Eva!S24="",'Pre-Tx'!S24=""),"",Eva!S24-'Pre-Tx'!S24)</f>
         <v/>
       </c>
-      <c r="T24" s="83">
+      <c r="T24" s="73">
         <f>IF(OR(Eva!T24="",'Pre-Tx'!T24=""),"",Eva!T24-'Pre-Tx'!T24)</f>
         <v/>
       </c>
-      <c r="U24" s="82">
+      <c r="U24" s="72">
         <f>IF(OR(Eva!U24="",'Pre-Tx'!U24=""),"",Eva!U24-'Pre-Tx'!U24)</f>
         <v/>
       </c>
-      <c r="V24" s="83">
+      <c r="V24" s="73">
         <f>IF(OR(Eva!V24="",'Pre-Tx'!V24=""),"",Eva!V24-'Pre-Tx'!V24)</f>
         <v/>
       </c>
-      <c r="W24" s="83">
+      <c r="W24" s="73">
         <f>IF(OR(Eva!W24="",'Pre-Tx'!W24=""),"",Eva!W24-'Pre-Tx'!W24)</f>
         <v/>
       </c>
-      <c r="X24" s="82">
+      <c r="X24" s="72">
         <f>IF(OR(Eva!X24="",'Pre-Tx'!X24=""),"",Eva!X24-'Pre-Tx'!X24)</f>
         <v/>
       </c>
-      <c r="Y24" s="83">
+      <c r="Y24" s="73">
         <f>IF(OR(Eva!Y24="",'Pre-Tx'!Y24=""),"",Eva!Y24-'Pre-Tx'!Y24)</f>
         <v/>
       </c>
-      <c r="Z24" s="83">
+      <c r="Z24" s="73">
         <f>IF(OR(Eva!Z24="",'Pre-Tx'!Z24=""),"",Eva!Z24-'Pre-Tx'!Z24)</f>
         <v/>
       </c>
-      <c r="AA24" s="84">
+      <c r="AA24" s="74">
         <f>IF(OR(Eva!AA24="",'Pre-Tx'!AA24=""),"",Eva!AA24-'Pre-Tx'!AA24)</f>
         <v/>
       </c>
-      <c r="AB24" s="83">
+      <c r="AB24" s="73">
         <f>IF(OR(Eva!AB24="",'Pre-Tx'!AB24=""),"",Eva!AB24-'Pre-Tx'!AB24)</f>
         <v/>
       </c>
-      <c r="AC24" s="83">
+      <c r="AC24" s="73">
         <f>IF(OR(Eva!AC24="",'Pre-Tx'!AC24=""),"",Eva!AC24-'Pre-Tx'!AC24)</f>
         <v/>
       </c>
-      <c r="AD24" s="82">
+      <c r="AD24" s="72">
         <f>IF(OR(Eva!AD24="",'Pre-Tx'!AD24=""),"",Eva!AD24-'Pre-Tx'!AD24)</f>
         <v/>
       </c>
-      <c r="AE24" s="83">
+      <c r="AE24" s="73">
         <f>IF(OR(Eva!AE24="",'Pre-Tx'!AE24=""),"",Eva!AE24-'Pre-Tx'!AE24)</f>
         <v/>
       </c>
-      <c r="AF24" s="83">
+      <c r="AF24" s="73">
         <f>IF(OR(Eva!AF24="",'Pre-Tx'!AF24=""),"",Eva!AF24-'Pre-Tx'!AF24)</f>
         <v/>
       </c>
-      <c r="AG24" s="82">
+      <c r="AG24" s="72">
         <f>IF(OR(Eva!AG24="",'Pre-Tx'!AG24=""),"",Eva!AG24-'Pre-Tx'!AG24)</f>
         <v/>
       </c>
-      <c r="AH24" s="83">
+      <c r="AH24" s="73">
         <f>IF(OR(Eva!AH24="",'Pre-Tx'!AH24=""),"",Eva!AH24-'Pre-Tx'!AH24)</f>
         <v/>
       </c>
-      <c r="AI24" s="83">
+      <c r="AI24" s="73">
         <f>IF(OR(Eva!AI24="",'Pre-Tx'!AI24=""),"",Eva!AI24-'Pre-Tx'!AI24)</f>
         <v/>
       </c>
-      <c r="AJ24" s="82">
+      <c r="AJ24" s="72">
         <f>IF(OR(Eva!AJ24="",'Pre-Tx'!AJ24=""),"",Eva!AJ24-'Pre-Tx'!AJ24)</f>
         <v/>
       </c>
-      <c r="AK24" s="83">
+      <c r="AK24" s="73">
         <f>IF(OR(Eva!AK24="",'Pre-Tx'!AK24=""),"",Eva!AK24-'Pre-Tx'!AK24)</f>
         <v/>
       </c>
-      <c r="AL24" s="83">
+      <c r="AL24" s="73">
         <f>IF(OR(Eva!AL24="",'Pre-Tx'!AL24=""),"",Eva!AL24-'Pre-Tx'!AL24)</f>
         <v/>
       </c>
-      <c r="AM24" s="82">
+      <c r="AM24" s="72">
         <f>IF(OR(Eva!AM24="",'Pre-Tx'!AM24=""),"",Eva!AM24-'Pre-Tx'!AM24)</f>
         <v/>
       </c>
-      <c r="AN24" s="83">
+      <c r="AN24" s="73">
         <f>IF(OR(Eva!AN24="",'Pre-Tx'!AN24=""),"",Eva!AN24-'Pre-Tx'!AN24)</f>
         <v/>
       </c>
-      <c r="AO24" s="83">
+      <c r="AO24" s="73">
         <f>IF(OR(Eva!AO24="",'Pre-Tx'!AO24=""),"",Eva!AO24-'Pre-Tx'!AO24)</f>
         <v/>
       </c>
-      <c r="AP24" s="82">
+      <c r="AP24" s="72">
         <f>IF(OR(Eva!AP24="",'Pre-Tx'!AP24=""),"",Eva!AP24-'Pre-Tx'!AP24)</f>
         <v/>
       </c>
-      <c r="AQ24" s="83">
+      <c r="AQ24" s="73">
         <f>IF(OR(Eva!AQ24="",'Pre-Tx'!AQ24=""),"",Eva!AQ24-'Pre-Tx'!AQ24)</f>
         <v/>
       </c>
-      <c r="AR24" s="83">
+      <c r="AR24" s="73">
         <f>IF(OR(Eva!AR24="",'Pre-Tx'!AR24=""),"",Eva!AR24-'Pre-Tx'!AR24)</f>
         <v/>
       </c>
-      <c r="AS24" s="82">
+      <c r="AS24" s="72">
         <f>IF(OR(Eva!AS24="",'Pre-Tx'!AS24=""),"",Eva!AS24-'Pre-Tx'!AS24)</f>
         <v/>
       </c>
-      <c r="AT24" s="83">
+      <c r="AT24" s="73">
         <f>IF(OR(Eva!AT24="",'Pre-Tx'!AT24=""),"",Eva!AT24-'Pre-Tx'!AT24)</f>
         <v/>
       </c>
-      <c r="AU24" s="83">
+      <c r="AU24" s="73">
         <f>IF(OR(Eva!AU24="",'Pre-Tx'!AU24=""),"",Eva!AU24-'Pre-Tx'!AU24)</f>
         <v/>
       </c>
-      <c r="AV24" s="82">
+      <c r="AV24" s="72">
         <f>IF(OR(Eva!AV24="",'Pre-Tx'!AV24=""),"",Eva!AV24-'Pre-Tx'!AV24)</f>
         <v/>
       </c>
-      <c r="AW24" s="83">
+      <c r="AW24" s="73">
         <f>IF(OR(Eva!AW24="",'Pre-Tx'!AW24=""),"",Eva!AW24-'Pre-Tx'!AW24)</f>
         <v/>
       </c>
-      <c r="AX24" s="83">
+      <c r="AX24" s="73">
         <f>IF(OR(Eva!AX24="",'Pre-Tx'!AX24=""),"",Eva!AX24-'Pre-Tx'!AX24)</f>
         <v/>
       </c>
@@ -19450,195 +18478,195 @@
           <t>CEJ-GM</t>
         </is>
       </c>
-      <c r="C25" s="79">
+      <c r="C25" s="69">
         <f>IF(OR(Eva!C25="",'Pre-Tx'!C25=""),"",Eva!C25-'Pre-Tx'!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="80">
+      <c r="D25" s="70">
         <f>IF(OR(Eva!D25="",'Pre-Tx'!D25=""),"",Eva!D25-'Pre-Tx'!D25)</f>
         <v/>
       </c>
-      <c r="E25" s="80">
+      <c r="E25" s="70">
         <f>IF(OR(Eva!E25="",'Pre-Tx'!E25=""),"",Eva!E25-'Pre-Tx'!E25)</f>
         <v/>
       </c>
-      <c r="F25" s="79">
+      <c r="F25" s="69">
         <f>IF(OR(Eva!F25="",'Pre-Tx'!F25=""),"",Eva!F25-'Pre-Tx'!F25)</f>
         <v/>
       </c>
-      <c r="G25" s="80">
+      <c r="G25" s="70">
         <f>IF(OR(Eva!G25="",'Pre-Tx'!G25=""),"",Eva!G25-'Pre-Tx'!G25)</f>
         <v/>
       </c>
-      <c r="H25" s="80">
+      <c r="H25" s="70">
         <f>IF(OR(Eva!H25="",'Pre-Tx'!H25=""),"",Eva!H25-'Pre-Tx'!H25)</f>
         <v/>
       </c>
-      <c r="I25" s="79">
+      <c r="I25" s="69">
         <f>IF(OR(Eva!I25="",'Pre-Tx'!I25=""),"",Eva!I25-'Pre-Tx'!I25)</f>
         <v/>
       </c>
-      <c r="J25" s="80">
+      <c r="J25" s="70">
         <f>IF(OR(Eva!J25="",'Pre-Tx'!J25=""),"",Eva!J25-'Pre-Tx'!J25)</f>
         <v/>
       </c>
-      <c r="K25" s="80">
+      <c r="K25" s="70">
         <f>IF(OR(Eva!K25="",'Pre-Tx'!K25=""),"",Eva!K25-'Pre-Tx'!K25)</f>
         <v/>
       </c>
-      <c r="L25" s="79">
+      <c r="L25" s="69">
         <f>IF(OR(Eva!L25="",'Pre-Tx'!L25=""),"",Eva!L25-'Pre-Tx'!L25)</f>
         <v/>
       </c>
-      <c r="M25" s="80">
+      <c r="M25" s="70">
         <f>IF(OR(Eva!M25="",'Pre-Tx'!M25=""),"",Eva!M25-'Pre-Tx'!M25)</f>
         <v/>
       </c>
-      <c r="N25" s="80">
+      <c r="N25" s="70">
         <f>IF(OR(Eva!N25="",'Pre-Tx'!N25=""),"",Eva!N25-'Pre-Tx'!N25)</f>
         <v/>
       </c>
-      <c r="O25" s="79">
+      <c r="O25" s="69">
         <f>IF(OR(Eva!O25="",'Pre-Tx'!O25=""),"",Eva!O25-'Pre-Tx'!O25)</f>
         <v/>
       </c>
-      <c r="P25" s="80">
+      <c r="P25" s="70">
         <f>IF(OR(Eva!P25="",'Pre-Tx'!P25=""),"",Eva!P25-'Pre-Tx'!P25)</f>
         <v/>
       </c>
-      <c r="Q25" s="80">
+      <c r="Q25" s="70">
         <f>IF(OR(Eva!Q25="",'Pre-Tx'!Q25=""),"",Eva!Q25-'Pre-Tx'!Q25)</f>
         <v/>
       </c>
-      <c r="R25" s="79">
+      <c r="R25" s="69">
         <f>IF(OR(Eva!R25="",'Pre-Tx'!R25=""),"",Eva!R25-'Pre-Tx'!R25)</f>
         <v/>
       </c>
-      <c r="S25" s="80">
+      <c r="S25" s="70">
         <f>IF(OR(Eva!S25="",'Pre-Tx'!S25=""),"",Eva!S25-'Pre-Tx'!S25)</f>
         <v/>
       </c>
-      <c r="T25" s="80">
+      <c r="T25" s="70">
         <f>IF(OR(Eva!T25="",'Pre-Tx'!T25=""),"",Eva!T25-'Pre-Tx'!T25)</f>
         <v/>
       </c>
-      <c r="U25" s="79">
+      <c r="U25" s="69">
         <f>IF(OR(Eva!U25="",'Pre-Tx'!U25=""),"",Eva!U25-'Pre-Tx'!U25)</f>
         <v/>
       </c>
-      <c r="V25" s="80">
+      <c r="V25" s="70">
         <f>IF(OR(Eva!V25="",'Pre-Tx'!V25=""),"",Eva!V25-'Pre-Tx'!V25)</f>
         <v/>
       </c>
-      <c r="W25" s="80">
+      <c r="W25" s="70">
         <f>IF(OR(Eva!W25="",'Pre-Tx'!W25=""),"",Eva!W25-'Pre-Tx'!W25)</f>
         <v/>
       </c>
-      <c r="X25" s="79">
+      <c r="X25" s="69">
         <f>IF(OR(Eva!X25="",'Pre-Tx'!X25=""),"",Eva!X25-'Pre-Tx'!X25)</f>
         <v/>
       </c>
-      <c r="Y25" s="80">
+      <c r="Y25" s="70">
         <f>IF(OR(Eva!Y25="",'Pre-Tx'!Y25=""),"",Eva!Y25-'Pre-Tx'!Y25)</f>
         <v/>
       </c>
-      <c r="Z25" s="80">
+      <c r="Z25" s="70">
         <f>IF(OR(Eva!Z25="",'Pre-Tx'!Z25=""),"",Eva!Z25-'Pre-Tx'!Z25)</f>
         <v/>
       </c>
-      <c r="AA25" s="81">
+      <c r="AA25" s="71">
         <f>IF(OR(Eva!AA25="",'Pre-Tx'!AA25=""),"",Eva!AA25-'Pre-Tx'!AA25)</f>
         <v/>
       </c>
-      <c r="AB25" s="80">
+      <c r="AB25" s="70">
         <f>IF(OR(Eva!AB25="",'Pre-Tx'!AB25=""),"",Eva!AB25-'Pre-Tx'!AB25)</f>
         <v/>
       </c>
-      <c r="AC25" s="80">
+      <c r="AC25" s="70">
         <f>IF(OR(Eva!AC25="",'Pre-Tx'!AC25=""),"",Eva!AC25-'Pre-Tx'!AC25)</f>
         <v/>
       </c>
-      <c r="AD25" s="79">
+      <c r="AD25" s="69">
         <f>IF(OR(Eva!AD25="",'Pre-Tx'!AD25=""),"",Eva!AD25-'Pre-Tx'!AD25)</f>
         <v/>
       </c>
-      <c r="AE25" s="80">
+      <c r="AE25" s="70">
         <f>IF(OR(Eva!AE25="",'Pre-Tx'!AE25=""),"",Eva!AE25-'Pre-Tx'!AE25)</f>
         <v/>
       </c>
-      <c r="AF25" s="80">
+      <c r="AF25" s="70">
         <f>IF(OR(Eva!AF25="",'Pre-Tx'!AF25=""),"",Eva!AF25-'Pre-Tx'!AF25)</f>
         <v/>
       </c>
-      <c r="AG25" s="79">
+      <c r="AG25" s="69">
         <f>IF(OR(Eva!AG25="",'Pre-Tx'!AG25=""),"",Eva!AG25-'Pre-Tx'!AG25)</f>
         <v/>
       </c>
-      <c r="AH25" s="80">
+      <c r="AH25" s="70">
         <f>IF(OR(Eva!AH25="",'Pre-Tx'!AH25=""),"",Eva!AH25-'Pre-Tx'!AH25)</f>
         <v/>
       </c>
-      <c r="AI25" s="80">
+      <c r="AI25" s="70">
         <f>IF(OR(Eva!AI25="",'Pre-Tx'!AI25=""),"",Eva!AI25-'Pre-Tx'!AI25)</f>
         <v/>
       </c>
-      <c r="AJ25" s="79">
+      <c r="AJ25" s="69">
         <f>IF(OR(Eva!AJ25="",'Pre-Tx'!AJ25=""),"",Eva!AJ25-'Pre-Tx'!AJ25)</f>
         <v/>
       </c>
-      <c r="AK25" s="80">
+      <c r="AK25" s="70">
         <f>IF(OR(Eva!AK25="",'Pre-Tx'!AK25=""),"",Eva!AK25-'Pre-Tx'!AK25)</f>
         <v/>
       </c>
-      <c r="AL25" s="80">
+      <c r="AL25" s="70">
         <f>IF(OR(Eva!AL25="",'Pre-Tx'!AL25=""),"",Eva!AL25-'Pre-Tx'!AL25)</f>
         <v/>
       </c>
-      <c r="AM25" s="79">
+      <c r="AM25" s="69">
         <f>IF(OR(Eva!AM25="",'Pre-Tx'!AM25=""),"",Eva!AM25-'Pre-Tx'!AM25)</f>
         <v/>
       </c>
-      <c r="AN25" s="80">
+      <c r="AN25" s="70">
         <f>IF(OR(Eva!AN25="",'Pre-Tx'!AN25=""),"",Eva!AN25-'Pre-Tx'!AN25)</f>
         <v/>
       </c>
-      <c r="AO25" s="80">
+      <c r="AO25" s="70">
         <f>IF(OR(Eva!AO25="",'Pre-Tx'!AO25=""),"",Eva!AO25-'Pre-Tx'!AO25)</f>
         <v/>
       </c>
-      <c r="AP25" s="79">
+      <c r="AP25" s="69">
         <f>IF(OR(Eva!AP25="",'Pre-Tx'!AP25=""),"",Eva!AP25-'Pre-Tx'!AP25)</f>
         <v/>
       </c>
-      <c r="AQ25" s="80">
+      <c r="AQ25" s="70">
         <f>IF(OR(Eva!AQ25="",'Pre-Tx'!AQ25=""),"",Eva!AQ25-'Pre-Tx'!AQ25)</f>
         <v/>
       </c>
-      <c r="AR25" s="80">
+      <c r="AR25" s="70">
         <f>IF(OR(Eva!AR25="",'Pre-Tx'!AR25=""),"",Eva!AR25-'Pre-Tx'!AR25)</f>
         <v/>
       </c>
-      <c r="AS25" s="79">
+      <c r="AS25" s="69">
         <f>IF(OR(Eva!AS25="",'Pre-Tx'!AS25=""),"",Eva!AS25-'Pre-Tx'!AS25)</f>
         <v/>
       </c>
-      <c r="AT25" s="80">
+      <c r="AT25" s="70">
         <f>IF(OR(Eva!AT25="",'Pre-Tx'!AT25=""),"",Eva!AT25-'Pre-Tx'!AT25)</f>
         <v/>
       </c>
-      <c r="AU25" s="80">
+      <c r="AU25" s="70">
         <f>IF(OR(Eva!AU25="",'Pre-Tx'!AU25=""),"",Eva!AU25-'Pre-Tx'!AU25)</f>
         <v/>
       </c>
-      <c r="AV25" s="79">
+      <c r="AV25" s="69">
         <f>IF(OR(Eva!AV25="",'Pre-Tx'!AV25=""),"",Eva!AV25-'Pre-Tx'!AV25)</f>
         <v/>
       </c>
-      <c r="AW25" s="80">
+      <c r="AW25" s="70">
         <f>IF(OR(Eva!AW25="",'Pre-Tx'!AW25=""),"",Eva!AW25-'Pre-Tx'!AW25)</f>
         <v/>
       </c>
-      <c r="AX25" s="80">
+      <c r="AX25" s="70">
         <f>IF(OR(Eva!AX25="",'Pre-Tx'!AX25=""),"",Eva!AX25-'Pre-Tx'!AX25)</f>
         <v/>
       </c>
@@ -20763,195 +19791,195 @@
           <t>CEJ-GM</t>
         </is>
       </c>
-      <c r="C34" s="79">
+      <c r="C34" s="69">
         <f>IF(OR(Eva!C34="",'Pre-Tx'!C34=""),"",Eva!C34-'Pre-Tx'!C34)</f>
         <v/>
       </c>
-      <c r="D34" s="80">
+      <c r="D34" s="70">
         <f>IF(OR(Eva!D34="",'Pre-Tx'!D34=""),"",Eva!D34-'Pre-Tx'!D34)</f>
         <v/>
       </c>
-      <c r="E34" s="80">
+      <c r="E34" s="70">
         <f>IF(OR(Eva!E34="",'Pre-Tx'!E34=""),"",Eva!E34-'Pre-Tx'!E34)</f>
         <v/>
       </c>
-      <c r="F34" s="79">
+      <c r="F34" s="69">
         <f>IF(OR(Eva!F34="",'Pre-Tx'!F34=""),"",Eva!F34-'Pre-Tx'!F34)</f>
         <v/>
       </c>
-      <c r="G34" s="80">
+      <c r="G34" s="70">
         <f>IF(OR(Eva!G34="",'Pre-Tx'!G34=""),"",Eva!G34-'Pre-Tx'!G34)</f>
         <v/>
       </c>
-      <c r="H34" s="80">
+      <c r="H34" s="70">
         <f>IF(OR(Eva!H34="",'Pre-Tx'!H34=""),"",Eva!H34-'Pre-Tx'!H34)</f>
         <v/>
       </c>
-      <c r="I34" s="79">
+      <c r="I34" s="69">
         <f>IF(OR(Eva!I34="",'Pre-Tx'!I34=""),"",Eva!I34-'Pre-Tx'!I34)</f>
         <v/>
       </c>
-      <c r="J34" s="80">
+      <c r="J34" s="70">
         <f>IF(OR(Eva!J34="",'Pre-Tx'!J34=""),"",Eva!J34-'Pre-Tx'!J34)</f>
         <v/>
       </c>
-      <c r="K34" s="80">
+      <c r="K34" s="70">
         <f>IF(OR(Eva!K34="",'Pre-Tx'!K34=""),"",Eva!K34-'Pre-Tx'!K34)</f>
         <v/>
       </c>
-      <c r="L34" s="79">
+      <c r="L34" s="69">
         <f>IF(OR(Eva!L34="",'Pre-Tx'!L34=""),"",Eva!L34-'Pre-Tx'!L34)</f>
         <v/>
       </c>
-      <c r="M34" s="80">
+      <c r="M34" s="70">
         <f>IF(OR(Eva!M34="",'Pre-Tx'!M34=""),"",Eva!M34-'Pre-Tx'!M34)</f>
         <v/>
       </c>
-      <c r="N34" s="80">
+      <c r="N34" s="70">
         <f>IF(OR(Eva!N34="",'Pre-Tx'!N34=""),"",Eva!N34-'Pre-Tx'!N34)</f>
         <v/>
       </c>
-      <c r="O34" s="79">
+      <c r="O34" s="69">
         <f>IF(OR(Eva!O34="",'Pre-Tx'!O34=""),"",Eva!O34-'Pre-Tx'!O34)</f>
         <v/>
       </c>
-      <c r="P34" s="80">
+      <c r="P34" s="70">
         <f>IF(OR(Eva!P34="",'Pre-Tx'!P34=""),"",Eva!P34-'Pre-Tx'!P34)</f>
         <v/>
       </c>
-      <c r="Q34" s="80">
+      <c r="Q34" s="70">
         <f>IF(OR(Eva!Q34="",'Pre-Tx'!Q34=""),"",Eva!Q34-'Pre-Tx'!Q34)</f>
         <v/>
       </c>
-      <c r="R34" s="79">
+      <c r="R34" s="69">
         <f>IF(OR(Eva!R34="",'Pre-Tx'!R34=""),"",Eva!R34-'Pre-Tx'!R34)</f>
         <v/>
       </c>
-      <c r="S34" s="80">
+      <c r="S34" s="70">
         <f>IF(OR(Eva!S34="",'Pre-Tx'!S34=""),"",Eva!S34-'Pre-Tx'!S34)</f>
         <v/>
       </c>
-      <c r="T34" s="80">
+      <c r="T34" s="70">
         <f>IF(OR(Eva!T34="",'Pre-Tx'!T34=""),"",Eva!T34-'Pre-Tx'!T34)</f>
         <v/>
       </c>
-      <c r="U34" s="79">
+      <c r="U34" s="69">
         <f>IF(OR(Eva!U34="",'Pre-Tx'!U34=""),"",Eva!U34-'Pre-Tx'!U34)</f>
         <v/>
       </c>
-      <c r="V34" s="80">
+      <c r="V34" s="70">
         <f>IF(OR(Eva!V34="",'Pre-Tx'!V34=""),"",Eva!V34-'Pre-Tx'!V34)</f>
         <v/>
       </c>
-      <c r="W34" s="80">
+      <c r="W34" s="70">
         <f>IF(OR(Eva!W34="",'Pre-Tx'!W34=""),"",Eva!W34-'Pre-Tx'!W34)</f>
         <v/>
       </c>
-      <c r="X34" s="79">
+      <c r="X34" s="69">
         <f>IF(OR(Eva!X34="",'Pre-Tx'!X34=""),"",Eva!X34-'Pre-Tx'!X34)</f>
         <v/>
       </c>
-      <c r="Y34" s="80">
+      <c r="Y34" s="70">
         <f>IF(OR(Eva!Y34="",'Pre-Tx'!Y34=""),"",Eva!Y34-'Pre-Tx'!Y34)</f>
         <v/>
       </c>
-      <c r="Z34" s="80">
+      <c r="Z34" s="70">
         <f>IF(OR(Eva!Z34="",'Pre-Tx'!Z34=""),"",Eva!Z34-'Pre-Tx'!Z34)</f>
         <v/>
       </c>
-      <c r="AA34" s="81">
+      <c r="AA34" s="71">
         <f>IF(OR(Eva!AA34="",'Pre-Tx'!AA34=""),"",Eva!AA34-'Pre-Tx'!AA34)</f>
         <v/>
       </c>
-      <c r="AB34" s="80">
+      <c r="AB34" s="70">
         <f>IF(OR(Eva!AB34="",'Pre-Tx'!AB34=""),"",Eva!AB34-'Pre-Tx'!AB34)</f>
         <v/>
       </c>
-      <c r="AC34" s="80">
+      <c r="AC34" s="70">
         <f>IF(OR(Eva!AC34="",'Pre-Tx'!AC34=""),"",Eva!AC34-'Pre-Tx'!AC34)</f>
         <v/>
       </c>
-      <c r="AD34" s="79">
+      <c r="AD34" s="69">
         <f>IF(OR(Eva!AD34="",'Pre-Tx'!AD34=""),"",Eva!AD34-'Pre-Tx'!AD34)</f>
         <v/>
       </c>
-      <c r="AE34" s="80">
+      <c r="AE34" s="70">
         <f>IF(OR(Eva!AE34="",'Pre-Tx'!AE34=""),"",Eva!AE34-'Pre-Tx'!AE34)</f>
         <v/>
       </c>
-      <c r="AF34" s="80">
+      <c r="AF34" s="70">
         <f>IF(OR(Eva!AF34="",'Pre-Tx'!AF34=""),"",Eva!AF34-'Pre-Tx'!AF34)</f>
         <v/>
       </c>
-      <c r="AG34" s="79">
+      <c r="AG34" s="69">
         <f>IF(OR(Eva!AG34="",'Pre-Tx'!AG34=""),"",Eva!AG34-'Pre-Tx'!AG34)</f>
         <v/>
       </c>
-      <c r="AH34" s="80">
+      <c r="AH34" s="70">
         <f>IF(OR(Eva!AH34="",'Pre-Tx'!AH34=""),"",Eva!AH34-'Pre-Tx'!AH34)</f>
         <v/>
       </c>
-      <c r="AI34" s="80">
+      <c r="AI34" s="70">
         <f>IF(OR(Eva!AI34="",'Pre-Tx'!AI34=""),"",Eva!AI34-'Pre-Tx'!AI34)</f>
         <v/>
       </c>
-      <c r="AJ34" s="79">
+      <c r="AJ34" s="69">
         <f>IF(OR(Eva!AJ34="",'Pre-Tx'!AJ34=""),"",Eva!AJ34-'Pre-Tx'!AJ34)</f>
         <v/>
       </c>
-      <c r="AK34" s="80">
+      <c r="AK34" s="70">
         <f>IF(OR(Eva!AK34="",'Pre-Tx'!AK34=""),"",Eva!AK34-'Pre-Tx'!AK34)</f>
         <v/>
       </c>
-      <c r="AL34" s="80">
+      <c r="AL34" s="70">
         <f>IF(OR(Eva!AL34="",'Pre-Tx'!AL34=""),"",Eva!AL34-'Pre-Tx'!AL34)</f>
         <v/>
       </c>
-      <c r="AM34" s="79">
+      <c r="AM34" s="69">
         <f>IF(OR(Eva!AM34="",'Pre-Tx'!AM34=""),"",Eva!AM34-'Pre-Tx'!AM34)</f>
         <v/>
       </c>
-      <c r="AN34" s="80">
+      <c r="AN34" s="70">
         <f>IF(OR(Eva!AN34="",'Pre-Tx'!AN34=""),"",Eva!AN34-'Pre-Tx'!AN34)</f>
         <v/>
       </c>
-      <c r="AO34" s="80">
+      <c r="AO34" s="70">
         <f>IF(OR(Eva!AO34="",'Pre-Tx'!AO34=""),"",Eva!AO34-'Pre-Tx'!AO34)</f>
         <v/>
       </c>
-      <c r="AP34" s="79">
+      <c r="AP34" s="69">
         <f>IF(OR(Eva!AP34="",'Pre-Tx'!AP34=""),"",Eva!AP34-'Pre-Tx'!AP34)</f>
         <v/>
       </c>
-      <c r="AQ34" s="80">
+      <c r="AQ34" s="70">
         <f>IF(OR(Eva!AQ34="",'Pre-Tx'!AQ34=""),"",Eva!AQ34-'Pre-Tx'!AQ34)</f>
         <v/>
       </c>
-      <c r="AR34" s="80">
+      <c r="AR34" s="70">
         <f>IF(OR(Eva!AR34="",'Pre-Tx'!AR34=""),"",Eva!AR34-'Pre-Tx'!AR34)</f>
         <v/>
       </c>
-      <c r="AS34" s="79">
+      <c r="AS34" s="69">
         <f>IF(OR(Eva!AS34="",'Pre-Tx'!AS34=""),"",Eva!AS34-'Pre-Tx'!AS34)</f>
         <v/>
       </c>
-      <c r="AT34" s="80">
+      <c r="AT34" s="70">
         <f>IF(OR(Eva!AT34="",'Pre-Tx'!AT34=""),"",Eva!AT34-'Pre-Tx'!AT34)</f>
         <v/>
       </c>
-      <c r="AU34" s="80">
+      <c r="AU34" s="70">
         <f>IF(OR(Eva!AU34="",'Pre-Tx'!AU34=""),"",Eva!AU34-'Pre-Tx'!AU34)</f>
         <v/>
       </c>
-      <c r="AV34" s="79">
+      <c r="AV34" s="69">
         <f>IF(OR(Eva!AV34="",'Pre-Tx'!AV34=""),"",Eva!AV34-'Pre-Tx'!AV34)</f>
         <v/>
       </c>
-      <c r="AW34" s="80">
+      <c r="AW34" s="70">
         <f>IF(OR(Eva!AW34="",'Pre-Tx'!AW34=""),"",Eva!AW34-'Pre-Tx'!AW34)</f>
         <v/>
       </c>
-      <c r="AX34" s="80">
+      <c r="AX34" s="70">
         <f>IF(OR(Eva!AX34="",'Pre-Tx'!AX34=""),"",Eva!AX34-'Pre-Tx'!AX34)</f>
         <v/>
       </c>
@@ -20968,195 +19996,195 @@
           <t>PD</t>
         </is>
       </c>
-      <c r="C35" s="82">
+      <c r="C35" s="72">
         <f>IF(OR(Eva!C35="",'Pre-Tx'!C35=""),"",Eva!C35-'Pre-Tx'!C35)</f>
         <v/>
       </c>
-      <c r="D35" s="83">
+      <c r="D35" s="73">
         <f>IF(OR(Eva!D35="",'Pre-Tx'!D35=""),"",Eva!D35-'Pre-Tx'!D35)</f>
         <v/>
       </c>
-      <c r="E35" s="83">
+      <c r="E35" s="73">
         <f>IF(OR(Eva!E35="",'Pre-Tx'!E35=""),"",Eva!E35-'Pre-Tx'!E35)</f>
         <v/>
       </c>
-      <c r="F35" s="82">
+      <c r="F35" s="72">
         <f>IF(OR(Eva!F35="",'Pre-Tx'!F35=""),"",Eva!F35-'Pre-Tx'!F35)</f>
         <v/>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="73">
         <f>IF(OR(Eva!G35="",'Pre-Tx'!G35=""),"",Eva!G35-'Pre-Tx'!G35)</f>
         <v/>
       </c>
-      <c r="H35" s="83">
+      <c r="H35" s="73">
         <f>IF(OR(Eva!H35="",'Pre-Tx'!H35=""),"",Eva!H35-'Pre-Tx'!H35)</f>
         <v/>
       </c>
-      <c r="I35" s="82">
+      <c r="I35" s="72">
         <f>IF(OR(Eva!I35="",'Pre-Tx'!I35=""),"",Eva!I35-'Pre-Tx'!I35)</f>
         <v/>
       </c>
-      <c r="J35" s="83">
+      <c r="J35" s="73">
         <f>IF(OR(Eva!J35="",'Pre-Tx'!J35=""),"",Eva!J35-'Pre-Tx'!J35)</f>
         <v/>
       </c>
-      <c r="K35" s="83">
+      <c r="K35" s="73">
         <f>IF(OR(Eva!K35="",'Pre-Tx'!K35=""),"",Eva!K35-'Pre-Tx'!K35)</f>
         <v/>
       </c>
-      <c r="L35" s="82">
+      <c r="L35" s="72">
         <f>IF(OR(Eva!L35="",'Pre-Tx'!L35=""),"",Eva!L35-'Pre-Tx'!L35)</f>
         <v/>
       </c>
-      <c r="M35" s="83">
+      <c r="M35" s="73">
         <f>IF(OR(Eva!M35="",'Pre-Tx'!M35=""),"",Eva!M35-'Pre-Tx'!M35)</f>
         <v/>
       </c>
-      <c r="N35" s="83">
+      <c r="N35" s="73">
         <f>IF(OR(Eva!N35="",'Pre-Tx'!N35=""),"",Eva!N35-'Pre-Tx'!N35)</f>
         <v/>
       </c>
-      <c r="O35" s="82">
+      <c r="O35" s="72">
         <f>IF(OR(Eva!O35="",'Pre-Tx'!O35=""),"",Eva!O35-'Pre-Tx'!O35)</f>
         <v/>
       </c>
-      <c r="P35" s="83">
+      <c r="P35" s="73">
         <f>IF(OR(Eva!P35="",'Pre-Tx'!P35=""),"",Eva!P35-'Pre-Tx'!P35)</f>
         <v/>
       </c>
-      <c r="Q35" s="83">
+      <c r="Q35" s="73">
         <f>IF(OR(Eva!Q35="",'Pre-Tx'!Q35=""),"",Eva!Q35-'Pre-Tx'!Q35)</f>
         <v/>
       </c>
-      <c r="R35" s="82">
+      <c r="R35" s="72">
         <f>IF(OR(Eva!R35="",'Pre-Tx'!R35=""),"",Eva!R35-'Pre-Tx'!R35)</f>
         <v/>
       </c>
-      <c r="S35" s="83">
+      <c r="S35" s="73">
         <f>IF(OR(Eva!S35="",'Pre-Tx'!S35=""),"",Eva!S35-'Pre-Tx'!S35)</f>
         <v/>
       </c>
-      <c r="T35" s="83">
+      <c r="T35" s="73">
         <f>IF(OR(Eva!T35="",'Pre-Tx'!T35=""),"",Eva!T35-'Pre-Tx'!T35)</f>
         <v/>
       </c>
-      <c r="U35" s="82">
+      <c r="U35" s="72">
         <f>IF(OR(Eva!U35="",'Pre-Tx'!U35=""),"",Eva!U35-'Pre-Tx'!U35)</f>
         <v/>
       </c>
-      <c r="V35" s="83">
+      <c r="V35" s="73">
         <f>IF(OR(Eva!V35="",'Pre-Tx'!V35=""),"",Eva!V35-'Pre-Tx'!V35)</f>
         <v/>
       </c>
-      <c r="W35" s="83">
+      <c r="W35" s="73">
         <f>IF(OR(Eva!W35="",'Pre-Tx'!W35=""),"",Eva!W35-'Pre-Tx'!W35)</f>
         <v/>
       </c>
-      <c r="X35" s="82">
+      <c r="X35" s="72">
         <f>IF(OR(Eva!X35="",'Pre-Tx'!X35=""),"",Eva!X35-'Pre-Tx'!X35)</f>
         <v/>
       </c>
-      <c r="Y35" s="83">
+      <c r="Y35" s="73">
         <f>IF(OR(Eva!Y35="",'Pre-Tx'!Y35=""),"",Eva!Y35-'Pre-Tx'!Y35)</f>
         <v/>
       </c>
-      <c r="Z35" s="83">
+      <c r="Z35" s="73">
         <f>IF(OR(Eva!Z35="",'Pre-Tx'!Z35=""),"",Eva!Z35-'Pre-Tx'!Z35)</f>
         <v/>
       </c>
-      <c r="AA35" s="84">
+      <c r="AA35" s="74">
         <f>IF(OR(Eva!AA35="",'Pre-Tx'!AA35=""),"",Eva!AA35-'Pre-Tx'!AA35)</f>
         <v/>
       </c>
-      <c r="AB35" s="83">
+      <c r="AB35" s="73">
         <f>IF(OR(Eva!AB35="",'Pre-Tx'!AB35=""),"",Eva!AB35-'Pre-Tx'!AB35)</f>
         <v/>
       </c>
-      <c r="AC35" s="83">
+      <c r="AC35" s="73">
         <f>IF(OR(Eva!AC35="",'Pre-Tx'!AC35=""),"",Eva!AC35-'Pre-Tx'!AC35)</f>
         <v/>
       </c>
-      <c r="AD35" s="82">
+      <c r="AD35" s="72">
         <f>IF(OR(Eva!AD35="",'Pre-Tx'!AD35=""),"",Eva!AD35-'Pre-Tx'!AD35)</f>
         <v/>
       </c>
-      <c r="AE35" s="83">
+      <c r="AE35" s="73">
         <f>IF(OR(Eva!AE35="",'Pre-Tx'!AE35=""),"",Eva!AE35-'Pre-Tx'!AE35)</f>
         <v/>
       </c>
-      <c r="AF35" s="83">
+      <c r="AF35" s="73">
         <f>IF(OR(Eva!AF35="",'Pre-Tx'!AF35=""),"",Eva!AF35-'Pre-Tx'!AF35)</f>
         <v/>
       </c>
-      <c r="AG35" s="82">
+      <c r="AG35" s="72">
         <f>IF(OR(Eva!AG35="",'Pre-Tx'!AG35=""),"",Eva!AG35-'Pre-Tx'!AG35)</f>
         <v/>
       </c>
-      <c r="AH35" s="83">
+      <c r="AH35" s="73">
         <f>IF(OR(Eva!AH35="",'Pre-Tx'!AH35=""),"",Eva!AH35-'Pre-Tx'!AH35)</f>
         <v/>
       </c>
-      <c r="AI35" s="83">
+      <c r="AI35" s="73">
         <f>IF(OR(Eva!AI35="",'Pre-Tx'!AI35=""),"",Eva!AI35-'Pre-Tx'!AI35)</f>
         <v/>
       </c>
-      <c r="AJ35" s="82">
+      <c r="AJ35" s="72">
         <f>IF(OR(Eva!AJ35="",'Pre-Tx'!AJ35=""),"",Eva!AJ35-'Pre-Tx'!AJ35)</f>
         <v/>
       </c>
-      <c r="AK35" s="83">
+      <c r="AK35" s="73">
         <f>IF(OR(Eva!AK35="",'Pre-Tx'!AK35=""),"",Eva!AK35-'Pre-Tx'!AK35)</f>
         <v/>
       </c>
-      <c r="AL35" s="83">
+      <c r="AL35" s="73">
         <f>IF(OR(Eva!AL35="",'Pre-Tx'!AL35=""),"",Eva!AL35-'Pre-Tx'!AL35)</f>
         <v/>
       </c>
-      <c r="AM35" s="82">
+      <c r="AM35" s="72">
         <f>IF(OR(Eva!AM35="",'Pre-Tx'!AM35=""),"",Eva!AM35-'Pre-Tx'!AM35)</f>
         <v/>
       </c>
-      <c r="AN35" s="83">
+      <c r="AN35" s="73">
         <f>IF(OR(Eva!AN35="",'Pre-Tx'!AN35=""),"",Eva!AN35-'Pre-Tx'!AN35)</f>
         <v/>
       </c>
-      <c r="AO35" s="83">
+      <c r="AO35" s="73">
         <f>IF(OR(Eva!AO35="",'Pre-Tx'!AO35=""),"",Eva!AO35-'Pre-Tx'!AO35)</f>
         <v/>
       </c>
-      <c r="AP35" s="82">
+      <c r="AP35" s="72">
         <f>IF(OR(Eva!AP35="",'Pre-Tx'!AP35=""),"",Eva!AP35-'Pre-Tx'!AP35)</f>
         <v/>
       </c>
-      <c r="AQ35" s="83">
+      <c r="AQ35" s="73">
         <f>IF(OR(Eva!AQ35="",'Pre-Tx'!AQ35=""),"",Eva!AQ35-'Pre-Tx'!AQ35)</f>
         <v/>
       </c>
-      <c r="AR35" s="83">
+      <c r="AR35" s="73">
         <f>IF(OR(Eva!AR35="",'Pre-Tx'!AR35=""),"",Eva!AR35-'Pre-Tx'!AR35)</f>
         <v/>
       </c>
-      <c r="AS35" s="82">
+      <c r="AS35" s="72">
         <f>IF(OR(Eva!AS35="",'Pre-Tx'!AS35=""),"",Eva!AS35-'Pre-Tx'!AS35)</f>
         <v/>
       </c>
-      <c r="AT35" s="83">
+      <c r="AT35" s="73">
         <f>IF(OR(Eva!AT35="",'Pre-Tx'!AT35=""),"",Eva!AT35-'Pre-Tx'!AT35)</f>
         <v/>
       </c>
-      <c r="AU35" s="83">
+      <c r="AU35" s="73">
         <f>IF(OR(Eva!AU35="",'Pre-Tx'!AU35=""),"",Eva!AU35-'Pre-Tx'!AU35)</f>
         <v/>
       </c>
-      <c r="AV35" s="82">
+      <c r="AV35" s="72">
         <f>IF(OR(Eva!AV35="",'Pre-Tx'!AV35=""),"",Eva!AV35-'Pre-Tx'!AV35)</f>
         <v/>
       </c>
-      <c r="AW35" s="83">
+      <c r="AW35" s="73">
         <f>IF(OR(Eva!AW35="",'Pre-Tx'!AW35=""),"",Eva!AW35-'Pre-Tx'!AW35)</f>
         <v/>
       </c>
-      <c r="AX35" s="83">
+      <c r="AX35" s="73">
         <f>IF(OR(Eva!AX35="",'Pre-Tx'!AX35=""),"",Eva!AX35-'Pre-Tx'!AX35)</f>
         <v/>
       </c>
@@ -21173,195 +20201,195 @@
           <t>CAL</t>
         </is>
       </c>
-      <c r="C36" s="85">
+      <c r="C36" s="75">
         <f>IF(OR(Eva!C36="",'Pre-Tx'!C36=""),"",Eva!C36-'Pre-Tx'!C36)</f>
         <v/>
       </c>
-      <c r="D36" s="86">
+      <c r="D36" s="76">
         <f>IF(OR(Eva!D36="",'Pre-Tx'!D36=""),"",Eva!D36-'Pre-Tx'!D36)</f>
         <v/>
       </c>
-      <c r="E36" s="86">
+      <c r="E36" s="76">
         <f>IF(OR(Eva!E36="",'Pre-Tx'!E36=""),"",Eva!E36-'Pre-Tx'!E36)</f>
         <v/>
       </c>
-      <c r="F36" s="85">
+      <c r="F36" s="75">
         <f>IF(OR(Eva!F36="",'Pre-Tx'!F36=""),"",Eva!F36-'Pre-Tx'!F36)</f>
         <v/>
       </c>
-      <c r="G36" s="86">
+      <c r="G36" s="76">
         <f>IF(OR(Eva!G36="",'Pre-Tx'!G36=""),"",Eva!G36-'Pre-Tx'!G36)</f>
         <v/>
       </c>
-      <c r="H36" s="86">
+      <c r="H36" s="76">
         <f>IF(OR(Eva!H36="",'Pre-Tx'!H36=""),"",Eva!H36-'Pre-Tx'!H36)</f>
         <v/>
       </c>
-      <c r="I36" s="85">
+      <c r="I36" s="75">
         <f>IF(OR(Eva!I36="",'Pre-Tx'!I36=""),"",Eva!I36-'Pre-Tx'!I36)</f>
         <v/>
       </c>
-      <c r="J36" s="86">
+      <c r="J36" s="76">
         <f>IF(OR(Eva!J36="",'Pre-Tx'!J36=""),"",Eva!J36-'Pre-Tx'!J36)</f>
         <v/>
       </c>
-      <c r="K36" s="86">
+      <c r="K36" s="76">
         <f>IF(OR(Eva!K36="",'Pre-Tx'!K36=""),"",Eva!K36-'Pre-Tx'!K36)</f>
         <v/>
       </c>
-      <c r="L36" s="85">
+      <c r="L36" s="75">
         <f>IF(OR(Eva!L36="",'Pre-Tx'!L36=""),"",Eva!L36-'Pre-Tx'!L36)</f>
         <v/>
       </c>
-      <c r="M36" s="86">
+      <c r="M36" s="76">
         <f>IF(OR(Eva!M36="",'Pre-Tx'!M36=""),"",Eva!M36-'Pre-Tx'!M36)</f>
         <v/>
       </c>
-      <c r="N36" s="86">
+      <c r="N36" s="76">
         <f>IF(OR(Eva!N36="",'Pre-Tx'!N36=""),"",Eva!N36-'Pre-Tx'!N36)</f>
         <v/>
       </c>
-      <c r="O36" s="85">
+      <c r="O36" s="75">
         <f>IF(OR(Eva!O36="",'Pre-Tx'!O36=""),"",Eva!O36-'Pre-Tx'!O36)</f>
         <v/>
       </c>
-      <c r="P36" s="86">
+      <c r="P36" s="76">
         <f>IF(OR(Eva!P36="",'Pre-Tx'!P36=""),"",Eva!P36-'Pre-Tx'!P36)</f>
         <v/>
       </c>
-      <c r="Q36" s="86">
+      <c r="Q36" s="76">
         <f>IF(OR(Eva!Q36="",'Pre-Tx'!Q36=""),"",Eva!Q36-'Pre-Tx'!Q36)</f>
         <v/>
       </c>
-      <c r="R36" s="85">
+      <c r="R36" s="75">
         <f>IF(OR(Eva!R36="",'Pre-Tx'!R36=""),"",Eva!R36-'Pre-Tx'!R36)</f>
         <v/>
       </c>
-      <c r="S36" s="86">
+      <c r="S36" s="76">
         <f>IF(OR(Eva!S36="",'Pre-Tx'!S36=""),"",Eva!S36-'Pre-Tx'!S36)</f>
         <v/>
       </c>
-      <c r="T36" s="86">
+      <c r="T36" s="76">
         <f>IF(OR(Eva!T36="",'Pre-Tx'!T36=""),"",Eva!T36-'Pre-Tx'!T36)</f>
         <v/>
       </c>
-      <c r="U36" s="85">
+      <c r="U36" s="75">
         <f>IF(OR(Eva!U36="",'Pre-Tx'!U36=""),"",Eva!U36-'Pre-Tx'!U36)</f>
         <v/>
       </c>
-      <c r="V36" s="86">
+      <c r="V36" s="76">
         <f>IF(OR(Eva!V36="",'Pre-Tx'!V36=""),"",Eva!V36-'Pre-Tx'!V36)</f>
         <v/>
       </c>
-      <c r="W36" s="86">
+      <c r="W36" s="76">
         <f>IF(OR(Eva!W36="",'Pre-Tx'!W36=""),"",Eva!W36-'Pre-Tx'!W36)</f>
         <v/>
       </c>
-      <c r="X36" s="85">
+      <c r="X36" s="75">
         <f>IF(OR(Eva!X36="",'Pre-Tx'!X36=""),"",Eva!X36-'Pre-Tx'!X36)</f>
         <v/>
       </c>
-      <c r="Y36" s="86">
+      <c r="Y36" s="76">
         <f>IF(OR(Eva!Y36="",'Pre-Tx'!Y36=""),"",Eva!Y36-'Pre-Tx'!Y36)</f>
         <v/>
       </c>
-      <c r="Z36" s="86">
+      <c r="Z36" s="76">
         <f>IF(OR(Eva!Z36="",'Pre-Tx'!Z36=""),"",Eva!Z36-'Pre-Tx'!Z36)</f>
         <v/>
       </c>
-      <c r="AA36" s="87">
+      <c r="AA36" s="77">
         <f>IF(OR(Eva!AA36="",'Pre-Tx'!AA36=""),"",Eva!AA36-'Pre-Tx'!AA36)</f>
         <v/>
       </c>
-      <c r="AB36" s="86">
+      <c r="AB36" s="76">
         <f>IF(OR(Eva!AB36="",'Pre-Tx'!AB36=""),"",Eva!AB36-'Pre-Tx'!AB36)</f>
         <v/>
       </c>
-      <c r="AC36" s="86">
+      <c r="AC36" s="76">
         <f>IF(OR(Eva!AC36="",'Pre-Tx'!AC36=""),"",Eva!AC36-'Pre-Tx'!AC36)</f>
         <v/>
       </c>
-      <c r="AD36" s="85">
+      <c r="AD36" s="75">
         <f>IF(OR(Eva!AD36="",'Pre-Tx'!AD36=""),"",Eva!AD36-'Pre-Tx'!AD36)</f>
         <v/>
       </c>
-      <c r="AE36" s="86">
+      <c r="AE36" s="76">
         <f>IF(OR(Eva!AE36="",'Pre-Tx'!AE36=""),"",Eva!AE36-'Pre-Tx'!AE36)</f>
         <v/>
       </c>
-      <c r="AF36" s="86">
+      <c r="AF36" s="76">
         <f>IF(OR(Eva!AF36="",'Pre-Tx'!AF36=""),"",Eva!AF36-'Pre-Tx'!AF36)</f>
         <v/>
       </c>
-      <c r="AG36" s="85">
+      <c r="AG36" s="75">
         <f>IF(OR(Eva!AG36="",'Pre-Tx'!AG36=""),"",Eva!AG36-'Pre-Tx'!AG36)</f>
         <v/>
       </c>
-      <c r="AH36" s="86">
+      <c r="AH36" s="76">
         <f>IF(OR(Eva!AH36="",'Pre-Tx'!AH36=""),"",Eva!AH36-'Pre-Tx'!AH36)</f>
         <v/>
       </c>
-      <c r="AI36" s="86">
+      <c r="AI36" s="76">
         <f>IF(OR(Eva!AI36="",'Pre-Tx'!AI36=""),"",Eva!AI36-'Pre-Tx'!AI36)</f>
         <v/>
       </c>
-      <c r="AJ36" s="85">
+      <c r="AJ36" s="75">
         <f>IF(OR(Eva!AJ36="",'Pre-Tx'!AJ36=""),"",Eva!AJ36-'Pre-Tx'!AJ36)</f>
         <v/>
       </c>
-      <c r="AK36" s="86">
+      <c r="AK36" s="76">
         <f>IF(OR(Eva!AK36="",'Pre-Tx'!AK36=""),"",Eva!AK36-'Pre-Tx'!AK36)</f>
         <v/>
       </c>
-      <c r="AL36" s="86">
+      <c r="AL36" s="76">
         <f>IF(OR(Eva!AL36="",'Pre-Tx'!AL36=""),"",Eva!AL36-'Pre-Tx'!AL36)</f>
         <v/>
       </c>
-      <c r="AM36" s="85">
+      <c r="AM36" s="75">
         <f>IF(OR(Eva!AM36="",'Pre-Tx'!AM36=""),"",Eva!AM36-'Pre-Tx'!AM36)</f>
         <v/>
       </c>
-      <c r="AN36" s="86">
+      <c r="AN36" s="76">
         <f>IF(OR(Eva!AN36="",'Pre-Tx'!AN36=""),"",Eva!AN36-'Pre-Tx'!AN36)</f>
         <v/>
       </c>
-      <c r="AO36" s="86">
+      <c r="AO36" s="76">
         <f>IF(OR(Eva!AO36="",'Pre-Tx'!AO36=""),"",Eva!AO36-'Pre-Tx'!AO36)</f>
         <v/>
       </c>
-      <c r="AP36" s="85">
+      <c r="AP36" s="75">
         <f>IF(OR(Eva!AP36="",'Pre-Tx'!AP36=""),"",Eva!AP36-'Pre-Tx'!AP36)</f>
         <v/>
       </c>
-      <c r="AQ36" s="86">
+      <c r="AQ36" s="76">
         <f>IF(OR(Eva!AQ36="",'Pre-Tx'!AQ36=""),"",Eva!AQ36-'Pre-Tx'!AQ36)</f>
         <v/>
       </c>
-      <c r="AR36" s="86">
+      <c r="AR36" s="76">
         <f>IF(OR(Eva!AR36="",'Pre-Tx'!AR36=""),"",Eva!AR36-'Pre-Tx'!AR36)</f>
         <v/>
       </c>
-      <c r="AS36" s="85">
+      <c r="AS36" s="75">
         <f>IF(OR(Eva!AS36="",'Pre-Tx'!AS36=""),"",Eva!AS36-'Pre-Tx'!AS36)</f>
         <v/>
       </c>
-      <c r="AT36" s="86">
+      <c r="AT36" s="76">
         <f>IF(OR(Eva!AT36="",'Pre-Tx'!AT36=""),"",Eva!AT36-'Pre-Tx'!AT36)</f>
         <v/>
       </c>
-      <c r="AU36" s="86">
+      <c r="AU36" s="76">
         <f>IF(OR(Eva!AU36="",'Pre-Tx'!AU36=""),"",Eva!AU36-'Pre-Tx'!AU36)</f>
         <v/>
       </c>
-      <c r="AV36" s="85">
+      <c r="AV36" s="75">
         <f>IF(OR(Eva!AV36="",'Pre-Tx'!AV36=""),"",Eva!AV36-'Pre-Tx'!AV36)</f>
         <v/>
       </c>
-      <c r="AW36" s="86">
+      <c r="AW36" s="76">
         <f>IF(OR(Eva!AW36="",'Pre-Tx'!AW36=""),"",Eva!AW36-'Pre-Tx'!AW36)</f>
         <v/>
       </c>
-      <c r="AX36" s="86">
+      <c r="AX36" s="76">
         <f>IF(OR(Eva!AX36="",'Pre-Tx'!AX36=""),"",Eva!AX36-'Pre-Tx'!AX36)</f>
         <v/>
       </c>
@@ -21753,195 +20781,195 @@
           <t>CAL</t>
         </is>
       </c>
-      <c r="C44" s="88">
+      <c r="C44" s="78">
         <f>IF(OR(Eva!C44="",'Pre-Tx'!C44=""),"",Eva!C44-'Pre-Tx'!C44)</f>
         <v/>
       </c>
-      <c r="D44" s="89">
+      <c r="D44" s="79">
         <f>IF(OR(Eva!D44="",'Pre-Tx'!D44=""),"",Eva!D44-'Pre-Tx'!D44)</f>
         <v/>
       </c>
-      <c r="E44" s="89">
+      <c r="E44" s="79">
         <f>IF(OR(Eva!E44="",'Pre-Tx'!E44=""),"",Eva!E44-'Pre-Tx'!E44)</f>
         <v/>
       </c>
-      <c r="F44" s="88">
+      <c r="F44" s="78">
         <f>IF(OR(Eva!F44="",'Pre-Tx'!F44=""),"",Eva!F44-'Pre-Tx'!F44)</f>
         <v/>
       </c>
-      <c r="G44" s="89">
+      <c r="G44" s="79">
         <f>IF(OR(Eva!G44="",'Pre-Tx'!G44=""),"",Eva!G44-'Pre-Tx'!G44)</f>
         <v/>
       </c>
-      <c r="H44" s="89">
+      <c r="H44" s="79">
         <f>IF(OR(Eva!H44="",'Pre-Tx'!H44=""),"",Eva!H44-'Pre-Tx'!H44)</f>
         <v/>
       </c>
-      <c r="I44" s="88">
+      <c r="I44" s="78">
         <f>IF(OR(Eva!I44="",'Pre-Tx'!I44=""),"",Eva!I44-'Pre-Tx'!I44)</f>
         <v/>
       </c>
-      <c r="J44" s="89">
+      <c r="J44" s="79">
         <f>IF(OR(Eva!J44="",'Pre-Tx'!J44=""),"",Eva!J44-'Pre-Tx'!J44)</f>
         <v/>
       </c>
-      <c r="K44" s="89">
+      <c r="K44" s="79">
         <f>IF(OR(Eva!K44="",'Pre-Tx'!K44=""),"",Eva!K44-'Pre-Tx'!K44)</f>
         <v/>
       </c>
-      <c r="L44" s="88">
+      <c r="L44" s="78">
         <f>IF(OR(Eva!L44="",'Pre-Tx'!L44=""),"",Eva!L44-'Pre-Tx'!L44)</f>
         <v/>
       </c>
-      <c r="M44" s="89">
+      <c r="M44" s="79">
         <f>IF(OR(Eva!M44="",'Pre-Tx'!M44=""),"",Eva!M44-'Pre-Tx'!M44)</f>
         <v/>
       </c>
-      <c r="N44" s="89">
+      <c r="N44" s="79">
         <f>IF(OR(Eva!N44="",'Pre-Tx'!N44=""),"",Eva!N44-'Pre-Tx'!N44)</f>
         <v/>
       </c>
-      <c r="O44" s="88">
+      <c r="O44" s="78">
         <f>IF(OR(Eva!O44="",'Pre-Tx'!O44=""),"",Eva!O44-'Pre-Tx'!O44)</f>
         <v/>
       </c>
-      <c r="P44" s="89">
+      <c r="P44" s="79">
         <f>IF(OR(Eva!P44="",'Pre-Tx'!P44=""),"",Eva!P44-'Pre-Tx'!P44)</f>
         <v/>
       </c>
-      <c r="Q44" s="89">
+      <c r="Q44" s="79">
         <f>IF(OR(Eva!Q44="",'Pre-Tx'!Q44=""),"",Eva!Q44-'Pre-Tx'!Q44)</f>
         <v/>
       </c>
-      <c r="R44" s="88">
+      <c r="R44" s="78">
         <f>IF(OR(Eva!R44="",'Pre-Tx'!R44=""),"",Eva!R44-'Pre-Tx'!R44)</f>
         <v/>
       </c>
-      <c r="S44" s="89">
+      <c r="S44" s="79">
         <f>IF(OR(Eva!S44="",'Pre-Tx'!S44=""),"",Eva!S44-'Pre-Tx'!S44)</f>
         <v/>
       </c>
-      <c r="T44" s="89">
+      <c r="T44" s="79">
         <f>IF(OR(Eva!T44="",'Pre-Tx'!T44=""),"",Eva!T44-'Pre-Tx'!T44)</f>
         <v/>
       </c>
-      <c r="U44" s="88">
+      <c r="U44" s="78">
         <f>IF(OR(Eva!U44="",'Pre-Tx'!U44=""),"",Eva!U44-'Pre-Tx'!U44)</f>
         <v/>
       </c>
-      <c r="V44" s="89">
+      <c r="V44" s="79">
         <f>IF(OR(Eva!V44="",'Pre-Tx'!V44=""),"",Eva!V44-'Pre-Tx'!V44)</f>
         <v/>
       </c>
-      <c r="W44" s="89">
+      <c r="W44" s="79">
         <f>IF(OR(Eva!W44="",'Pre-Tx'!W44=""),"",Eva!W44-'Pre-Tx'!W44)</f>
         <v/>
       </c>
-      <c r="X44" s="88">
+      <c r="X44" s="78">
         <f>IF(OR(Eva!X44="",'Pre-Tx'!X44=""),"",Eva!X44-'Pre-Tx'!X44)</f>
         <v/>
       </c>
-      <c r="Y44" s="89">
+      <c r="Y44" s="79">
         <f>IF(OR(Eva!Y44="",'Pre-Tx'!Y44=""),"",Eva!Y44-'Pre-Tx'!Y44)</f>
         <v/>
       </c>
-      <c r="Z44" s="89">
+      <c r="Z44" s="79">
         <f>IF(OR(Eva!Z44="",'Pre-Tx'!Z44=""),"",Eva!Z44-'Pre-Tx'!Z44)</f>
         <v/>
       </c>
-      <c r="AA44" s="90">
+      <c r="AA44" s="80">
         <f>IF(OR(Eva!AA44="",'Pre-Tx'!AA44=""),"",Eva!AA44-'Pre-Tx'!AA44)</f>
         <v/>
       </c>
-      <c r="AB44" s="89">
+      <c r="AB44" s="79">
         <f>IF(OR(Eva!AB44="",'Pre-Tx'!AB44=""),"",Eva!AB44-'Pre-Tx'!AB44)</f>
         <v/>
       </c>
-      <c r="AC44" s="89">
+      <c r="AC44" s="79">
         <f>IF(OR(Eva!AC44="",'Pre-Tx'!AC44=""),"",Eva!AC44-'Pre-Tx'!AC44)</f>
         <v/>
       </c>
-      <c r="AD44" s="88">
+      <c r="AD44" s="78">
         <f>IF(OR(Eva!AD44="",'Pre-Tx'!AD44=""),"",Eva!AD44-'Pre-Tx'!AD44)</f>
         <v/>
       </c>
-      <c r="AE44" s="89">
+      <c r="AE44" s="79">
         <f>IF(OR(Eva!AE44="",'Pre-Tx'!AE44=""),"",Eva!AE44-'Pre-Tx'!AE44)</f>
         <v/>
       </c>
-      <c r="AF44" s="89">
+      <c r="AF44" s="79">
         <f>IF(OR(Eva!AF44="",'Pre-Tx'!AF44=""),"",Eva!AF44-'Pre-Tx'!AF44)</f>
         <v/>
       </c>
-      <c r="AG44" s="88">
+      <c r="AG44" s="78">
         <f>IF(OR(Eva!AG44="",'Pre-Tx'!AG44=""),"",Eva!AG44-'Pre-Tx'!AG44)</f>
         <v/>
       </c>
-      <c r="AH44" s="89">
+      <c r="AH44" s="79">
         <f>IF(OR(Eva!AH44="",'Pre-Tx'!AH44=""),"",Eva!AH44-'Pre-Tx'!AH44)</f>
         <v/>
       </c>
-      <c r="AI44" s="89">
+      <c r="AI44" s="79">
         <f>IF(OR(Eva!AI44="",'Pre-Tx'!AI44=""),"",Eva!AI44-'Pre-Tx'!AI44)</f>
         <v/>
       </c>
-      <c r="AJ44" s="88">
+      <c r="AJ44" s="78">
         <f>IF(OR(Eva!AJ44="",'Pre-Tx'!AJ44=""),"",Eva!AJ44-'Pre-Tx'!AJ44)</f>
         <v/>
       </c>
-      <c r="AK44" s="89">
+      <c r="AK44" s="79">
         <f>IF(OR(Eva!AK44="",'Pre-Tx'!AK44=""),"",Eva!AK44-'Pre-Tx'!AK44)</f>
         <v/>
       </c>
-      <c r="AL44" s="89">
+      <c r="AL44" s="79">
         <f>IF(OR(Eva!AL44="",'Pre-Tx'!AL44=""),"",Eva!AL44-'Pre-Tx'!AL44)</f>
         <v/>
       </c>
-      <c r="AM44" s="88">
+      <c r="AM44" s="78">
         <f>IF(OR(Eva!AM44="",'Pre-Tx'!AM44=""),"",Eva!AM44-'Pre-Tx'!AM44)</f>
         <v/>
       </c>
-      <c r="AN44" s="89">
+      <c r="AN44" s="79">
         <f>IF(OR(Eva!AN44="",'Pre-Tx'!AN44=""),"",Eva!AN44-'Pre-Tx'!AN44)</f>
         <v/>
       </c>
-      <c r="AO44" s="89">
+      <c r="AO44" s="79">
         <f>IF(OR(Eva!AO44="",'Pre-Tx'!AO44=""),"",Eva!AO44-'Pre-Tx'!AO44)</f>
         <v/>
       </c>
-      <c r="AP44" s="88">
+      <c r="AP44" s="78">
         <f>IF(OR(Eva!AP44="",'Pre-Tx'!AP44=""),"",Eva!AP44-'Pre-Tx'!AP44)</f>
         <v/>
       </c>
-      <c r="AQ44" s="89">
+      <c r="AQ44" s="79">
         <f>IF(OR(Eva!AQ44="",'Pre-Tx'!AQ44=""),"",Eva!AQ44-'Pre-Tx'!AQ44)</f>
         <v/>
       </c>
-      <c r="AR44" s="89">
+      <c r="AR44" s="79">
         <f>IF(OR(Eva!AR44="",'Pre-Tx'!AR44=""),"",Eva!AR44-'Pre-Tx'!AR44)</f>
         <v/>
       </c>
-      <c r="AS44" s="88">
+      <c r="AS44" s="78">
         <f>IF(OR(Eva!AS44="",'Pre-Tx'!AS44=""),"",Eva!AS44-'Pre-Tx'!AS44)</f>
         <v/>
       </c>
-      <c r="AT44" s="89">
+      <c r="AT44" s="79">
         <f>IF(OR(Eva!AT44="",'Pre-Tx'!AT44=""),"",Eva!AT44-'Pre-Tx'!AT44)</f>
         <v/>
       </c>
-      <c r="AU44" s="89">
+      <c r="AU44" s="79">
         <f>IF(OR(Eva!AU44="",'Pre-Tx'!AU44=""),"",Eva!AU44-'Pre-Tx'!AU44)</f>
         <v/>
       </c>
-      <c r="AV44" s="88">
+      <c r="AV44" s="78">
         <f>IF(OR(Eva!AV44="",'Pre-Tx'!AV44=""),"",Eva!AV44-'Pre-Tx'!AV44)</f>
         <v/>
       </c>
-      <c r="AW44" s="89">
+      <c r="AW44" s="79">
         <f>IF(OR(Eva!AW44="",'Pre-Tx'!AW44=""),"",Eva!AW44-'Pre-Tx'!AW44)</f>
         <v/>
       </c>
-      <c r="AX44" s="89">
+      <c r="AX44" s="79">
         <f>IF(OR(Eva!AX44="",'Pre-Tx'!AX44=""),"",Eva!AX44-'Pre-Tx'!AX44)</f>
         <v/>
       </c>
@@ -21958,195 +20986,195 @@
           <t>PD</t>
         </is>
       </c>
-      <c r="C45" s="82">
+      <c r="C45" s="72">
         <f>IF(OR(Eva!C45="",'Pre-Tx'!C45=""),"",Eva!C45-'Pre-Tx'!C45)</f>
         <v/>
       </c>
-      <c r="D45" s="83">
+      <c r="D45" s="73">
         <f>IF(OR(Eva!D45="",'Pre-Tx'!D45=""),"",Eva!D45-'Pre-Tx'!D45)</f>
         <v/>
       </c>
-      <c r="E45" s="83">
+      <c r="E45" s="73">
         <f>IF(OR(Eva!E45="",'Pre-Tx'!E45=""),"",Eva!E45-'Pre-Tx'!E45)</f>
         <v/>
       </c>
-      <c r="F45" s="82">
+      <c r="F45" s="72">
         <f>IF(OR(Eva!F45="",'Pre-Tx'!F45=""),"",Eva!F45-'Pre-Tx'!F45)</f>
         <v/>
       </c>
-      <c r="G45" s="83">
+      <c r="G45" s="73">
         <f>IF(OR(Eva!G45="",'Pre-Tx'!G45=""),"",Eva!G45-'Pre-Tx'!G45)</f>
         <v/>
       </c>
-      <c r="H45" s="83">
+      <c r="H45" s="73">
         <f>IF(OR(Eva!H45="",'Pre-Tx'!H45=""),"",Eva!H45-'Pre-Tx'!H45)</f>
         <v/>
       </c>
-      <c r="I45" s="82">
+      <c r="I45" s="72">
         <f>IF(OR(Eva!I45="",'Pre-Tx'!I45=""),"",Eva!I45-'Pre-Tx'!I45)</f>
         <v/>
       </c>
-      <c r="J45" s="83">
+      <c r="J45" s="73">
         <f>IF(OR(Eva!J45="",'Pre-Tx'!J45=""),"",Eva!J45-'Pre-Tx'!J45)</f>
         <v/>
       </c>
-      <c r="K45" s="83">
+      <c r="K45" s="73">
         <f>IF(OR(Eva!K45="",'Pre-Tx'!K45=""),"",Eva!K45-'Pre-Tx'!K45)</f>
         <v/>
       </c>
-      <c r="L45" s="82">
+      <c r="L45" s="72">
         <f>IF(OR(Eva!L45="",'Pre-Tx'!L45=""),"",Eva!L45-'Pre-Tx'!L45)</f>
         <v/>
       </c>
-      <c r="M45" s="83">
+      <c r="M45" s="73">
         <f>IF(OR(Eva!M45="",'Pre-Tx'!M45=""),"",Eva!M45-'Pre-Tx'!M45)</f>
         <v/>
       </c>
-      <c r="N45" s="83">
+      <c r="N45" s="73">
         <f>IF(OR(Eva!N45="",'Pre-Tx'!N45=""),"",Eva!N45-'Pre-Tx'!N45)</f>
         <v/>
       </c>
-      <c r="O45" s="82">
+      <c r="O45" s="72">
         <f>IF(OR(Eva!O45="",'Pre-Tx'!O45=""),"",Eva!O45-'Pre-Tx'!O45)</f>
         <v/>
       </c>
-      <c r="P45" s="83">
+      <c r="P45" s="73">
         <f>IF(OR(Eva!P45="",'Pre-Tx'!P45=""),"",Eva!P45-'Pre-Tx'!P45)</f>
         <v/>
       </c>
-      <c r="Q45" s="83">
+      <c r="Q45" s="73">
         <f>IF(OR(Eva!Q45="",'Pre-Tx'!Q45=""),"",Eva!Q45-'Pre-Tx'!Q45)</f>
         <v/>
       </c>
-      <c r="R45" s="82">
+      <c r="R45" s="72">
         <f>IF(OR(Eva!R45="",'Pre-Tx'!R45=""),"",Eva!R45-'Pre-Tx'!R45)</f>
         <v/>
       </c>
-      <c r="S45" s="83">
+      <c r="S45" s="73">
         <f>IF(OR(Eva!S45="",'Pre-Tx'!S45=""),"",Eva!S45-'Pre-Tx'!S45)</f>
         <v/>
       </c>
-      <c r="T45" s="83">
+      <c r="T45" s="73">
         <f>IF(OR(Eva!T45="",'Pre-Tx'!T45=""),"",Eva!T45-'Pre-Tx'!T45)</f>
         <v/>
       </c>
-      <c r="U45" s="82">
+      <c r="U45" s="72">
         <f>IF(OR(Eva!U45="",'Pre-Tx'!U45=""),"",Eva!U45-'Pre-Tx'!U45)</f>
         <v/>
       </c>
-      <c r="V45" s="83">
+      <c r="V45" s="73">
         <f>IF(OR(Eva!V45="",'Pre-Tx'!V45=""),"",Eva!V45-'Pre-Tx'!V45)</f>
         <v/>
       </c>
-      <c r="W45" s="83">
+      <c r="W45" s="73">
         <f>IF(OR(Eva!W45="",'Pre-Tx'!W45=""),"",Eva!W45-'Pre-Tx'!W45)</f>
         <v/>
       </c>
-      <c r="X45" s="82">
+      <c r="X45" s="72">
         <f>IF(OR(Eva!X45="",'Pre-Tx'!X45=""),"",Eva!X45-'Pre-Tx'!X45)</f>
         <v/>
       </c>
-      <c r="Y45" s="83">
+      <c r="Y45" s="73">
         <f>IF(OR(Eva!Y45="",'Pre-Tx'!Y45=""),"",Eva!Y45-'Pre-Tx'!Y45)</f>
         <v/>
       </c>
-      <c r="Z45" s="83">
+      <c r="Z45" s="73">
         <f>IF(OR(Eva!Z45="",'Pre-Tx'!Z45=""),"",Eva!Z45-'Pre-Tx'!Z45)</f>
         <v/>
       </c>
-      <c r="AA45" s="84">
+      <c r="AA45" s="74">
         <f>IF(OR(Eva!AA45="",'Pre-Tx'!AA45=""),"",Eva!AA45-'Pre-Tx'!AA45)</f>
         <v/>
       </c>
-      <c r="AB45" s="83">
+      <c r="AB45" s="73">
         <f>IF(OR(Eva!AB45="",'Pre-Tx'!AB45=""),"",Eva!AB45-'Pre-Tx'!AB45)</f>
         <v/>
       </c>
-      <c r="AC45" s="83">
+      <c r="AC45" s="73">
         <f>IF(OR(Eva!AC45="",'Pre-Tx'!AC45=""),"",Eva!AC45-'Pre-Tx'!AC45)</f>
         <v/>
       </c>
-      <c r="AD45" s="82">
+      <c r="AD45" s="72">
         <f>IF(OR(Eva!AD45="",'Pre-Tx'!AD45=""),"",Eva!AD45-'Pre-Tx'!AD45)</f>
         <v/>
       </c>
-      <c r="AE45" s="83">
+      <c r="AE45" s="73">
         <f>IF(OR(Eva!AE45="",'Pre-Tx'!AE45=""),"",Eva!AE45-'Pre-Tx'!AE45)</f>
         <v/>
       </c>
-      <c r="AF45" s="83">
+      <c r="AF45" s="73">
         <f>IF(OR(Eva!AF45="",'Pre-Tx'!AF45=""),"",Eva!AF45-'Pre-Tx'!AF45)</f>
         <v/>
       </c>
-      <c r="AG45" s="82">
+      <c r="AG45" s="72">
         <f>IF(OR(Eva!AG45="",'Pre-Tx'!AG45=""),"",Eva!AG45-'Pre-Tx'!AG45)</f>
         <v/>
       </c>
-      <c r="AH45" s="83">
+      <c r="AH45" s="73">
         <f>IF(OR(Eva!AH45="",'Pre-Tx'!AH45=""),"",Eva!AH45-'Pre-Tx'!AH45)</f>
         <v/>
       </c>
-      <c r="AI45" s="83">
+      <c r="AI45" s="73">
         <f>IF(OR(Eva!AI45="",'Pre-Tx'!AI45=""),"",Eva!AI45-'Pre-Tx'!AI45)</f>
         <v/>
       </c>
-      <c r="AJ45" s="82">
+      <c r="AJ45" s="72">
         <f>IF(OR(Eva!AJ45="",'Pre-Tx'!AJ45=""),"",Eva!AJ45-'Pre-Tx'!AJ45)</f>
         <v/>
       </c>
-      <c r="AK45" s="83">
+      <c r="AK45" s="73">
         <f>IF(OR(Eva!AK45="",'Pre-Tx'!AK45=""),"",Eva!AK45-'Pre-Tx'!AK45)</f>
         <v/>
       </c>
-      <c r="AL45" s="83">
+      <c r="AL45" s="73">
         <f>IF(OR(Eva!AL45="",'Pre-Tx'!AL45=""),"",Eva!AL45-'Pre-Tx'!AL45)</f>
         <v/>
       </c>
-      <c r="AM45" s="82">
+      <c r="AM45" s="72">
         <f>IF(OR(Eva!AM45="",'Pre-Tx'!AM45=""),"",Eva!AM45-'Pre-Tx'!AM45)</f>
         <v/>
       </c>
-      <c r="AN45" s="83">
+      <c r="AN45" s="73">
         <f>IF(OR(Eva!AN45="",'Pre-Tx'!AN45=""),"",Eva!AN45-'Pre-Tx'!AN45)</f>
         <v/>
       </c>
-      <c r="AO45" s="83">
+      <c r="AO45" s="73">
         <f>IF(OR(Eva!AO45="",'Pre-Tx'!AO45=""),"",Eva!AO45-'Pre-Tx'!AO45)</f>
         <v/>
       </c>
-      <c r="AP45" s="82">
+      <c r="AP45" s="72">
         <f>IF(OR(Eva!AP45="",'Pre-Tx'!AP45=""),"",Eva!AP45-'Pre-Tx'!AP45)</f>
         <v/>
       </c>
-      <c r="AQ45" s="83">
+      <c r="AQ45" s="73">
         <f>IF(OR(Eva!AQ45="",'Pre-Tx'!AQ45=""),"",Eva!AQ45-'Pre-Tx'!AQ45)</f>
         <v/>
       </c>
-      <c r="AR45" s="83">
+      <c r="AR45" s="73">
         <f>IF(OR(Eva!AR45="",'Pre-Tx'!AR45=""),"",Eva!AR45-'Pre-Tx'!AR45)</f>
         <v/>
       </c>
-      <c r="AS45" s="82">
+      <c r="AS45" s="72">
         <f>IF(OR(Eva!AS45="",'Pre-Tx'!AS45=""),"",Eva!AS45-'Pre-Tx'!AS45)</f>
         <v/>
       </c>
-      <c r="AT45" s="83">
+      <c r="AT45" s="73">
         <f>IF(OR(Eva!AT45="",'Pre-Tx'!AT45=""),"",Eva!AT45-'Pre-Tx'!AT45)</f>
         <v/>
       </c>
-      <c r="AU45" s="83">
+      <c r="AU45" s="73">
         <f>IF(OR(Eva!AU45="",'Pre-Tx'!AU45=""),"",Eva!AU45-'Pre-Tx'!AU45)</f>
         <v/>
       </c>
-      <c r="AV45" s="82">
+      <c r="AV45" s="72">
         <f>IF(OR(Eva!AV45="",'Pre-Tx'!AV45=""),"",Eva!AV45-'Pre-Tx'!AV45)</f>
         <v/>
       </c>
-      <c r="AW45" s="83">
+      <c r="AW45" s="73">
         <f>IF(OR(Eva!AW45="",'Pre-Tx'!AW45=""),"",Eva!AW45-'Pre-Tx'!AW45)</f>
         <v/>
       </c>
-      <c r="AX45" s="83">
+      <c r="AX45" s="73">
         <f>IF(OR(Eva!AX45="",'Pre-Tx'!AX45=""),"",Eva!AX45-'Pre-Tx'!AX45)</f>
         <v/>
       </c>
@@ -22163,195 +21191,195 @@
           <t>CEJ-GM</t>
         </is>
       </c>
-      <c r="C46" s="79">
+      <c r="C46" s="69">
         <f>IF(OR(Eva!C46="",'Pre-Tx'!C46=""),"",Eva!C46-'Pre-Tx'!C46)</f>
         <v/>
       </c>
-      <c r="D46" s="80">
+      <c r="D46" s="70">
         <f>IF(OR(Eva!D46="",'Pre-Tx'!D46=""),"",Eva!D46-'Pre-Tx'!D46)</f>
         <v/>
       </c>
-      <c r="E46" s="80">
+      <c r="E46" s="70">
         <f>IF(OR(Eva!E46="",'Pre-Tx'!E46=""),"",Eva!E46-'Pre-Tx'!E46)</f>
         <v/>
       </c>
-      <c r="F46" s="79">
+      <c r="F46" s="69">
         <f>IF(OR(Eva!F46="",'Pre-Tx'!F46=""),"",Eva!F46-'Pre-Tx'!F46)</f>
         <v/>
       </c>
-      <c r="G46" s="80">
+      <c r="G46" s="70">
         <f>IF(OR(Eva!G46="",'Pre-Tx'!G46=""),"",Eva!G46-'Pre-Tx'!G46)</f>
         <v/>
       </c>
-      <c r="H46" s="80">
+      <c r="H46" s="70">
         <f>IF(OR(Eva!H46="",'Pre-Tx'!H46=""),"",Eva!H46-'Pre-Tx'!H46)</f>
         <v/>
       </c>
-      <c r="I46" s="79">
+      <c r="I46" s="69">
         <f>IF(OR(Eva!I46="",'Pre-Tx'!I46=""),"",Eva!I46-'Pre-Tx'!I46)</f>
         <v/>
       </c>
-      <c r="J46" s="80">
+      <c r="J46" s="70">
         <f>IF(OR(Eva!J46="",'Pre-Tx'!J46=""),"",Eva!J46-'Pre-Tx'!J46)</f>
         <v/>
       </c>
-      <c r="K46" s="80">
+      <c r="K46" s="70">
         <f>IF(OR(Eva!K46="",'Pre-Tx'!K46=""),"",Eva!K46-'Pre-Tx'!K46)</f>
         <v/>
       </c>
-      <c r="L46" s="79">
+      <c r="L46" s="69">
         <f>IF(OR(Eva!L46="",'Pre-Tx'!L46=""),"",Eva!L46-'Pre-Tx'!L46)</f>
         <v/>
       </c>
-      <c r="M46" s="80">
+      <c r="M46" s="70">
         <f>IF(OR(Eva!M46="",'Pre-Tx'!M46=""),"",Eva!M46-'Pre-Tx'!M46)</f>
         <v/>
       </c>
-      <c r="N46" s="80">
+      <c r="N46" s="70">
         <f>IF(OR(Eva!N46="",'Pre-Tx'!N46=""),"",Eva!N46-'Pre-Tx'!N46)</f>
         <v/>
       </c>
-      <c r="O46" s="79">
+      <c r="O46" s="69">
         <f>IF(OR(Eva!O46="",'Pre-Tx'!O46=""),"",Eva!O46-'Pre-Tx'!O46)</f>
         <v/>
       </c>
-      <c r="P46" s="80">
+      <c r="P46" s="70">
         <f>IF(OR(Eva!P46="",'Pre-Tx'!P46=""),"",Eva!P46-'Pre-Tx'!P46)</f>
         <v/>
       </c>
-      <c r="Q46" s="80">
+      <c r="Q46" s="70">
         <f>IF(OR(Eva!Q46="",'Pre-Tx'!Q46=""),"",Eva!Q46-'Pre-Tx'!Q46)</f>
         <v/>
       </c>
-      <c r="R46" s="79">
+      <c r="R46" s="69">
         <f>IF(OR(Eva!R46="",'Pre-Tx'!R46=""),"",Eva!R46-'Pre-Tx'!R46)</f>
         <v/>
       </c>
-      <c r="S46" s="80">
+      <c r="S46" s="70">
         <f>IF(OR(Eva!S46="",'Pre-Tx'!S46=""),"",Eva!S46-'Pre-Tx'!S46)</f>
         <v/>
       </c>
-      <c r="T46" s="80">
+      <c r="T46" s="70">
         <f>IF(OR(Eva!T46="",'Pre-Tx'!T46=""),"",Eva!T46-'Pre-Tx'!T46)</f>
         <v/>
       </c>
-      <c r="U46" s="79">
+      <c r="U46" s="69">
         <f>IF(OR(Eva!U46="",'Pre-Tx'!U46=""),"",Eva!U46-'Pre-Tx'!U46)</f>
         <v/>
       </c>
-      <c r="V46" s="80">
+      <c r="V46" s="70">
         <f>IF(OR(Eva!V46="",'Pre-Tx'!V46=""),"",Eva!V46-'Pre-Tx'!V46)</f>
         <v/>
       </c>
-      <c r="W46" s="80">
+      <c r="W46" s="70">
         <f>IF(OR(Eva!W46="",'Pre-Tx'!W46=""),"",Eva!W46-'Pre-Tx'!W46)</f>
         <v/>
       </c>
-      <c r="X46" s="79">
+      <c r="X46" s="69">
         <f>IF(OR(Eva!X46="",'Pre-Tx'!X46=""),"",Eva!X46-'Pre-Tx'!X46)</f>
         <v/>
       </c>
-      <c r="Y46" s="80">
+      <c r="Y46" s="70">
         <f>IF(OR(Eva!Y46="",'Pre-Tx'!Y46=""),"",Eva!Y46-'Pre-Tx'!Y46)</f>
         <v/>
       </c>
-      <c r="Z46" s="80">
+      <c r="Z46" s="70">
         <f>IF(OR(Eva!Z46="",'Pre-Tx'!Z46=""),"",Eva!Z46-'Pre-Tx'!Z46)</f>
         <v/>
       </c>
-      <c r="AA46" s="81">
+      <c r="AA46" s="71">
         <f>IF(OR(Eva!AA46="",'Pre-Tx'!AA46=""),"",Eva!AA46-'Pre-Tx'!AA46)</f>
         <v/>
       </c>
-      <c r="AB46" s="80">
+      <c r="AB46" s="70">
         <f>IF(OR(Eva!AB46="",'Pre-Tx'!AB46=""),"",Eva!AB46-'Pre-Tx'!AB46)</f>
         <v/>
       </c>
-      <c r="AC46" s="80">
+      <c r="AC46" s="70">
         <f>IF(OR(Eva!AC46="",'Pre-Tx'!AC46=""),"",Eva!AC46-'Pre-Tx'!AC46)</f>
         <v/>
       </c>
-      <c r="AD46" s="79">
+      <c r="AD46" s="69">
         <f>IF(OR(Eva!AD46="",'Pre-Tx'!AD46=""),"",Eva!AD46-'Pre-Tx'!AD46)</f>
         <v/>
       </c>
-      <c r="AE46" s="80">
+      <c r="AE46" s="70">
         <f>IF(OR(Eva!AE46="",'Pre-Tx'!AE46=""),"",Eva!AE46-'Pre-Tx'!AE46)</f>
         <v/>
       </c>
-      <c r="AF46" s="80">
+      <c r="AF46" s="70">
         <f>IF(OR(Eva!AF46="",'Pre-Tx'!AF46=""),"",Eva!AF46-'Pre-Tx'!AF46)</f>
         <v/>
       </c>
-      <c r="AG46" s="79">
+      <c r="AG46" s="69">
         <f>IF(OR(Eva!AG46="",'Pre-Tx'!AG46=""),"",Eva!AG46-'Pre-Tx'!AG46)</f>
         <v/>
       </c>
-      <c r="AH46" s="80">
+      <c r="AH46" s="70">
         <f>IF(OR(Eva!AH46="",'Pre-Tx'!AH46=""),"",Eva!AH46-'Pre-Tx'!AH46)</f>
         <v/>
       </c>
-      <c r="AI46" s="80">
+      <c r="AI46" s="70">
         <f>IF(OR(Eva!AI46="",'Pre-Tx'!AI46=""),"",Eva!AI46-'Pre-Tx'!AI46)</f>
         <v/>
       </c>
-      <c r="AJ46" s="79">
+      <c r="AJ46" s="69">
         <f>IF(OR(Eva!AJ46="",'Pre-Tx'!AJ46=""),"",Eva!AJ46-'Pre-Tx'!AJ46)</f>
         <v/>
       </c>
-      <c r="AK46" s="80">
+      <c r="AK46" s="70">
         <f>IF(OR(Eva!AK46="",'Pre-Tx'!AK46=""),"",Eva!AK46-'Pre-Tx'!AK46)</f>
         <v/>
       </c>
-      <c r="AL46" s="80">
+      <c r="AL46" s="70">
         <f>IF(OR(Eva!AL46="",'Pre-Tx'!AL46=""),"",Eva!AL46-'Pre-Tx'!AL46)</f>
         <v/>
       </c>
-      <c r="AM46" s="79">
+      <c r="AM46" s="69">
         <f>IF(OR(Eva!AM46="",'Pre-Tx'!AM46=""),"",Eva!AM46-'Pre-Tx'!AM46)</f>
         <v/>
       </c>
-      <c r="AN46" s="80">
+      <c r="AN46" s="70">
         <f>IF(OR(Eva!AN46="",'Pre-Tx'!AN46=""),"",Eva!AN46-'Pre-Tx'!AN46)</f>
         <v/>
       </c>
-      <c r="AO46" s="80">
+      <c r="AO46" s="70">
         <f>IF(OR(Eva!AO46="",'Pre-Tx'!AO46=""),"",Eva!AO46-'Pre-Tx'!AO46)</f>
         <v/>
       </c>
-      <c r="AP46" s="79">
+      <c r="AP46" s="69">
         <f>IF(OR(Eva!AP46="",'Pre-Tx'!AP46=""),"",Eva!AP46-'Pre-Tx'!AP46)</f>
         <v/>
       </c>
-      <c r="AQ46" s="80">
+      <c r="AQ46" s="70">
         <f>IF(OR(Eva!AQ46="",'Pre-Tx'!AQ46=""),"",Eva!AQ46-'Pre-Tx'!AQ46)</f>
         <v/>
       </c>
-      <c r="AR46" s="80">
+      <c r="AR46" s="70">
         <f>IF(OR(Eva!AR46="",'Pre-Tx'!AR46=""),"",Eva!AR46-'Pre-Tx'!AR46)</f>
         <v/>
       </c>
-      <c r="AS46" s="79">
+      <c r="AS46" s="69">
         <f>IF(OR(Eva!AS46="",'Pre-Tx'!AS46=""),"",Eva!AS46-'Pre-Tx'!AS46)</f>
         <v/>
       </c>
-      <c r="AT46" s="80">
+      <c r="AT46" s="70">
         <f>IF(OR(Eva!AT46="",'Pre-Tx'!AT46=""),"",Eva!AT46-'Pre-Tx'!AT46)</f>
         <v/>
       </c>
-      <c r="AU46" s="80">
+      <c r="AU46" s="70">
         <f>IF(OR(Eva!AU46="",'Pre-Tx'!AU46=""),"",Eva!AU46-'Pre-Tx'!AU46)</f>
         <v/>
       </c>
-      <c r="AV46" s="79">
+      <c r="AV46" s="69">
         <f>IF(OR(Eva!AV46="",'Pre-Tx'!AV46=""),"",Eva!AV46-'Pre-Tx'!AV46)</f>
         <v/>
       </c>
-      <c r="AW46" s="80">
+      <c r="AW46" s="70">
         <f>IF(OR(Eva!AW46="",'Pre-Tx'!AW46=""),"",Eva!AW46-'Pre-Tx'!AW46)</f>
         <v/>
       </c>
-      <c r="AX46" s="80">
+      <c r="AX46" s="70">
         <f>IF(OR(Eva!AX46="",'Pre-Tx'!AX46=""),"",Eva!AX46-'Pre-Tx'!AX46)</f>
         <v/>
       </c>
@@ -22778,195 +21806,195 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="C49" s="79">
+      <c r="C49" s="69">
         <f>IF(OR(Eva!C49="",'Pre-Tx'!C49=""),"",Eva!C49-'Pre-Tx'!C49)</f>
         <v/>
       </c>
-      <c r="D49" s="80">
+      <c r="D49" s="70">
         <f>IF(OR(Eva!D49="",'Pre-Tx'!D49=""),"",Eva!D49-'Pre-Tx'!D49)</f>
         <v/>
       </c>
-      <c r="E49" s="80">
+      <c r="E49" s="70">
         <f>IF(OR(Eva!E49="",'Pre-Tx'!E49=""),"",Eva!E49-'Pre-Tx'!E49)</f>
         <v/>
       </c>
-      <c r="F49" s="79">
+      <c r="F49" s="69">
         <f>IF(OR(Eva!F49="",'Pre-Tx'!F49=""),"",Eva!F49-'Pre-Tx'!F49)</f>
         <v/>
       </c>
-      <c r="G49" s="80">
+      <c r="G49" s="70">
         <f>IF(OR(Eva!G49="",'Pre-Tx'!G49=""),"",Eva!G49-'Pre-Tx'!G49)</f>
         <v/>
       </c>
-      <c r="H49" s="80">
+      <c r="H49" s="70">
         <f>IF(OR(Eva!H49="",'Pre-Tx'!H49=""),"",Eva!H49-'Pre-Tx'!H49)</f>
         <v/>
       </c>
-      <c r="I49" s="79">
+      <c r="I49" s="69">
         <f>IF(OR(Eva!I49="",'Pre-Tx'!I49=""),"",Eva!I49-'Pre-Tx'!I49)</f>
         <v/>
       </c>
-      <c r="J49" s="80">
+      <c r="J49" s="70">
         <f>IF(OR(Eva!J49="",'Pre-Tx'!J49=""),"",Eva!J49-'Pre-Tx'!J49)</f>
         <v/>
       </c>
-      <c r="K49" s="80">
+      <c r="K49" s="70">
         <f>IF(OR(Eva!K49="",'Pre-Tx'!K49=""),"",Eva!K49-'Pre-Tx'!K49)</f>
         <v/>
       </c>
-      <c r="L49" s="79">
+      <c r="L49" s="69">
         <f>IF(OR(Eva!L49="",'Pre-Tx'!L49=""),"",Eva!L49-'Pre-Tx'!L49)</f>
         <v/>
       </c>
-      <c r="M49" s="80">
+      <c r="M49" s="70">
         <f>IF(OR(Eva!M49="",'Pre-Tx'!M49=""),"",Eva!M49-'Pre-Tx'!M49)</f>
         <v/>
       </c>
-      <c r="N49" s="80">
+      <c r="N49" s="70">
         <f>IF(OR(Eva!N49="",'Pre-Tx'!N49=""),"",Eva!N49-'Pre-Tx'!N49)</f>
         <v/>
       </c>
-      <c r="O49" s="79">
+      <c r="O49" s="69">
         <f>IF(OR(Eva!O49="",'Pre-Tx'!O49=""),"",Eva!O49-'Pre-Tx'!O49)</f>
         <v/>
       </c>
-      <c r="P49" s="80">
+      <c r="P49" s="70">
         <f>IF(OR(Eva!P49="",'Pre-Tx'!P49=""),"",Eva!P49-'Pre-Tx'!P49)</f>
         <v/>
       </c>
-      <c r="Q49" s="80">
+      <c r="Q49" s="70">
         <f>IF(OR(Eva!Q49="",'Pre-Tx'!Q49=""),"",Eva!Q49-'Pre-Tx'!Q49)</f>
         <v/>
       </c>
-      <c r="R49" s="79">
+      <c r="R49" s="69">
         <f>IF(OR(Eva!R49="",'Pre-Tx'!R49=""),"",Eva!R49-'Pre-Tx'!R49)</f>
         <v/>
       </c>
-      <c r="S49" s="80">
+      <c r="S49" s="70">
         <f>IF(OR(Eva!S49="",'Pre-Tx'!S49=""),"",Eva!S49-'Pre-Tx'!S49)</f>
         <v/>
       </c>
-      <c r="T49" s="80">
+      <c r="T49" s="70">
         <f>IF(OR(Eva!T49="",'Pre-Tx'!T49=""),"",Eva!T49-'Pre-Tx'!T49)</f>
         <v/>
       </c>
-      <c r="U49" s="79">
+      <c r="U49" s="69">
         <f>IF(OR(Eva!U49="",'Pre-Tx'!U49=""),"",Eva!U49-'Pre-Tx'!U49)</f>
         <v/>
       </c>
-      <c r="V49" s="80">
+      <c r="V49" s="70">
         <f>IF(OR(Eva!V49="",'Pre-Tx'!V49=""),"",Eva!V49-'Pre-Tx'!V49)</f>
         <v/>
       </c>
-      <c r="W49" s="80">
+      <c r="W49" s="70">
         <f>IF(OR(Eva!W49="",'Pre-Tx'!W49=""),"",Eva!W49-'Pre-Tx'!W49)</f>
         <v/>
       </c>
-      <c r="X49" s="79">
+      <c r="X49" s="69">
         <f>IF(OR(Eva!X49="",'Pre-Tx'!X49=""),"",Eva!X49-'Pre-Tx'!X49)</f>
         <v/>
       </c>
-      <c r="Y49" s="80">
+      <c r="Y49" s="70">
         <f>IF(OR(Eva!Y49="",'Pre-Tx'!Y49=""),"",Eva!Y49-'Pre-Tx'!Y49)</f>
         <v/>
       </c>
-      <c r="Z49" s="80">
+      <c r="Z49" s="70">
         <f>IF(OR(Eva!Z49="",'Pre-Tx'!Z49=""),"",Eva!Z49-'Pre-Tx'!Z49)</f>
         <v/>
       </c>
-      <c r="AA49" s="81">
+      <c r="AA49" s="71">
         <f>IF(OR(Eva!AA49="",'Pre-Tx'!AA49=""),"",Eva!AA49-'Pre-Tx'!AA49)</f>
         <v/>
       </c>
-      <c r="AB49" s="80">
+      <c r="AB49" s="70">
         <f>IF(OR(Eva!AB49="",'Pre-Tx'!AB49=""),"",Eva!AB49-'Pre-Tx'!AB49)</f>
         <v/>
       </c>
-      <c r="AC49" s="80">
+      <c r="AC49" s="70">
         <f>IF(OR(Eva!AC49="",'Pre-Tx'!AC49=""),"",Eva!AC49-'Pre-Tx'!AC49)</f>
         <v/>
       </c>
-      <c r="AD49" s="79">
+      <c r="AD49" s="69">
         <f>IF(OR(Eva!AD49="",'Pre-Tx'!AD49=""),"",Eva!AD49-'Pre-Tx'!AD49)</f>
         <v/>
       </c>
-      <c r="AE49" s="80">
+      <c r="AE49" s="70">
         <f>IF(OR(Eva!AE49="",'Pre-Tx'!AE49=""),"",Eva!AE49-'Pre-Tx'!AE49)</f>
         <v/>
       </c>
-      <c r="AF49" s="80">
+      <c r="AF49" s="70">
         <f>IF(OR(Eva!AF49="",'Pre-Tx'!AF49=""),"",Eva!AF49-'Pre-Tx'!AF49)</f>
         <v/>
       </c>
-      <c r="AG49" s="79">
+      <c r="AG49" s="69">
         <f>IF(OR(Eva!AG49="",'Pre-Tx'!AG49=""),"",Eva!AG49-'Pre-Tx'!AG49)</f>
         <v/>
       </c>
-      <c r="AH49" s="80">
+      <c r="AH49" s="70">
         <f>IF(OR(Eva!AH49="",'Pre-Tx'!AH49=""),"",Eva!AH49-'Pre-Tx'!AH49)</f>
         <v/>
       </c>
-      <c r="AI49" s="80">
+      <c r="AI49" s="70">
         <f>IF(OR(Eva!AI49="",'Pre-Tx'!AI49=""),"",Eva!AI49-'Pre-Tx'!AI49)</f>
         <v/>
       </c>
-      <c r="AJ49" s="79">
+      <c r="AJ49" s="69">
         <f>IF(OR(Eva!AJ49="",'Pre-Tx'!AJ49=""),"",Eva!AJ49-'Pre-Tx'!AJ49)</f>
         <v/>
       </c>
-      <c r="AK49" s="80">
+      <c r="AK49" s="70">
         <f>IF(OR(Eva!AK49="",'Pre-Tx'!AK49=""),"",Eva!AK49-'Pre-Tx'!AK49)</f>
         <v/>
       </c>
-      <c r="AL49" s="80">
+      <c r="AL49" s="70">
         <f>IF(OR(Eva!AL49="",'Pre-Tx'!AL49=""),"",Eva!AL49-'Pre-Tx'!AL49)</f>
         <v/>
       </c>
-      <c r="AM49" s="79">
+      <c r="AM49" s="69">
         <f>IF(OR(Eva!AM49="",'Pre-Tx'!AM49=""),"",Eva!AM49-'Pre-Tx'!AM49)</f>
         <v/>
       </c>
-      <c r="AN49" s="80">
+      <c r="AN49" s="70">
         <f>IF(OR(Eva!AN49="",'Pre-Tx'!AN49=""),"",Eva!AN49-'Pre-Tx'!AN49)</f>
         <v/>
       </c>
-      <c r="AO49" s="80">
+      <c r="AO49" s="70">
         <f>IF(OR(Eva!AO49="",'Pre-Tx'!AO49=""),"",Eva!AO49-'Pre-Tx'!AO49)</f>
         <v/>
       </c>
-      <c r="AP49" s="79">
+      <c r="AP49" s="69">
         <f>IF(OR(Eva!AP49="",'Pre-Tx'!AP49=""),"",Eva!AP49-'Pre-Tx'!AP49)</f>
         <v/>
       </c>
-      <c r="AQ49" s="80">
+      <c r="AQ49" s="70">
         <f>IF(OR(Eva!AQ49="",'Pre-Tx'!AQ49=""),"",Eva!AQ49-'Pre-Tx'!AQ49)</f>
         <v/>
       </c>
-      <c r="AR49" s="80">
+      <c r="AR49" s="70">
         <f>IF(OR(Eva!AR49="",'Pre-Tx'!AR49=""),"",Eva!AR49-'Pre-Tx'!AR49)</f>
         <v/>
       </c>
-      <c r="AS49" s="79">
+      <c r="AS49" s="69">
         <f>IF(OR(Eva!AS49="",'Pre-Tx'!AS49=""),"",Eva!AS49-'Pre-Tx'!AS49)</f>
         <v/>
       </c>
-      <c r="AT49" s="80">
+      <c r="AT49" s="70">
         <f>IF(OR(Eva!AT49="",'Pre-Tx'!AT49=""),"",Eva!AT49-'Pre-Tx'!AT49)</f>
         <v/>
       </c>
-      <c r="AU49" s="80">
+      <c r="AU49" s="70">
         <f>IF(OR(Eva!AU49="",'Pre-Tx'!AU49=""),"",Eva!AU49-'Pre-Tx'!AU49)</f>
         <v/>
       </c>
-      <c r="AV49" s="79">
+      <c r="AV49" s="69">
         <f>IF(OR(Eva!AV49="",'Pre-Tx'!AV49=""),"",Eva!AV49-'Pre-Tx'!AV49)</f>
         <v/>
       </c>
-      <c r="AW49" s="80">
+      <c r="AW49" s="70">
         <f>IF(OR(Eva!AW49="",'Pre-Tx'!AW49=""),"",Eva!AW49-'Pre-Tx'!AW49)</f>
         <v/>
       </c>
-      <c r="AX49" s="80">
+      <c r="AX49" s="70">
         <f>IF(OR(Eva!AX49="",'Pre-Tx'!AX49=""),"",Eva!AX49-'Pre-Tx'!AX49)</f>
         <v/>
       </c>
@@ -23065,469 +22093,155 @@
       <c r="AX50" s="64" t="n"/>
       <c r="AY50" s="66" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>MISSING TEETH  ·  from the Eva sheet</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="9" t="n"/>
-      <c r="T52" s="9" t="n"/>
-      <c r="U52" s="9" t="n"/>
-      <c r="V52" s="9" t="n"/>
-      <c r="W52" s="9" t="n"/>
-      <c r="X52" s="9" t="n"/>
-      <c r="Y52" s="9" t="n"/>
-      <c r="Z52" s="9" t="n"/>
-      <c r="AA52" s="9" t="n"/>
-      <c r="AB52" s="9" t="n"/>
-      <c r="AC52" s="9" t="n"/>
-      <c r="AD52" s="9" t="n"/>
-      <c r="AE52" s="9" t="n"/>
-      <c r="AF52" s="9" t="n"/>
-      <c r="AG52" s="9" t="n"/>
-      <c r="AH52" s="9" t="n"/>
-      <c r="AI52" s="9" t="n"/>
-      <c r="AJ52" s="9" t="n"/>
-      <c r="AK52" s="9" t="n"/>
-      <c r="AL52" s="9" t="n"/>
-      <c r="AM52" s="9" t="n"/>
-      <c r="AN52" s="9" t="n"/>
-      <c r="AO52" s="9" t="n"/>
-      <c r="AP52" s="9" t="n"/>
-      <c r="AQ52" s="9" t="n"/>
-      <c r="AR52" s="9" t="n"/>
-      <c r="AS52" s="9" t="n"/>
-      <c r="AT52" s="9" t="n"/>
-      <c r="AU52" s="9" t="n"/>
-      <c r="AV52" s="9" t="n"/>
-      <c r="AW52" s="9" t="n"/>
-      <c r="AX52" s="9" t="n"/>
+    <row r="54" hidden="1">
+      <c r="C54">
+        <f>IF(Eva!C54="","",Eva!C54)</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>IF(Eva!F54="","",Eva!F54)</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>IF(Eva!I54="","",Eva!I54)</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>IF(Eva!L54="","",Eva!L54)</f>
+        <v/>
+      </c>
+      <c r="O54">
+        <f>IF(Eva!O54="","",Eva!O54)</f>
+        <v/>
+      </c>
+      <c r="R54">
+        <f>IF(Eva!R54="","",Eva!R54)</f>
+        <v/>
+      </c>
+      <c r="U54">
+        <f>IF(Eva!U54="","",Eva!U54)</f>
+        <v/>
+      </c>
+      <c r="X54">
+        <f>IF(Eva!X54="","",Eva!X54)</f>
+        <v/>
+      </c>
+      <c r="AA54">
+        <f>IF(Eva!AA54="","",Eva!AA54)</f>
+        <v/>
+      </c>
+      <c r="AD54">
+        <f>IF(Eva!AD54="","",Eva!AD54)</f>
+        <v/>
+      </c>
+      <c r="AG54">
+        <f>IF(Eva!AG54="","",Eva!AG54)</f>
+        <v/>
+      </c>
+      <c r="AJ54">
+        <f>IF(Eva!AJ54="","",Eva!AJ54)</f>
+        <v/>
+      </c>
+      <c r="AM54">
+        <f>IF(Eva!AM54="","",Eva!AM54)</f>
+        <v/>
+      </c>
+      <c r="AP54">
+        <f>IF(Eva!AP54="","",Eva!AP54)</f>
+        <v/>
+      </c>
+      <c r="AS54">
+        <f>IF(Eva!AS54="","",Eva!AS54)</f>
+        <v/>
+      </c>
+      <c r="AV54">
+        <f>IF(Eva!AV54="","",Eva!AV54)</f>
+        <v/>
+      </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="67" t="inlineStr">
-        <is>
-          <t>MAXILLA</t>
-        </is>
-      </c>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="69" t="n">
-        <v>18</v>
-      </c>
-      <c r="D53" s="70" t="n"/>
-      <c r="E53" s="70" t="n"/>
-      <c r="F53" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="G53" s="70" t="n"/>
-      <c r="H53" s="70" t="n"/>
-      <c r="I53" s="69" t="n">
-        <v>16</v>
-      </c>
-      <c r="J53" s="70" t="n"/>
-      <c r="K53" s="70" t="n"/>
-      <c r="L53" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="M53" s="70" t="n"/>
-      <c r="N53" s="70" t="n"/>
-      <c r="O53" s="69" t="n">
-        <v>14</v>
-      </c>
-      <c r="P53" s="70" t="n"/>
-      <c r="Q53" s="70" t="n"/>
-      <c r="R53" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="S53" s="70" t="n"/>
-      <c r="T53" s="70" t="n"/>
-      <c r="U53" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="V53" s="70" t="n"/>
-      <c r="W53" s="70" t="n"/>
-      <c r="X53" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y53" s="70" t="n"/>
-      <c r="Z53" s="70" t="n"/>
-      <c r="AA53" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB53" s="70" t="n"/>
-      <c r="AC53" s="70" t="n"/>
-      <c r="AD53" s="69" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE53" s="70" t="n"/>
-      <c r="AF53" s="70" t="n"/>
-      <c r="AG53" s="69" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH53" s="70" t="n"/>
-      <c r="AI53" s="70" t="n"/>
-      <c r="AJ53" s="69" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK53" s="70" t="n"/>
-      <c r="AL53" s="70" t="n"/>
-      <c r="AM53" s="69" t="n">
-        <v>25</v>
-      </c>
-      <c r="AN53" s="70" t="n"/>
-      <c r="AO53" s="70" t="n"/>
-      <c r="AP53" s="69" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ53" s="70" t="n"/>
-      <c r="AR53" s="70" t="n"/>
-      <c r="AS53" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT53" s="70" t="n"/>
-      <c r="AU53" s="70" t="n"/>
-      <c r="AV53" s="69" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW53" s="70" t="n"/>
-      <c r="AX53" s="71" t="n"/>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="72" t="inlineStr">
-        <is>
-          <t>X / I</t>
-        </is>
-      </c>
-      <c r="B54" s="73" t="n"/>
-      <c r="C54" s="74">
-        <f>IF(Eva!C54="","",Eva!C54)</f>
-        <v/>
-      </c>
-      <c r="D54" s="75" t="n"/>
-      <c r="E54" s="75" t="n"/>
-      <c r="F54" s="74">
-        <f>IF(Eva!F54="","",Eva!F54)</f>
-        <v/>
-      </c>
-      <c r="G54" s="75" t="n"/>
-      <c r="H54" s="75" t="n"/>
-      <c r="I54" s="74">
-        <f>IF(Eva!I54="","",Eva!I54)</f>
-        <v/>
-      </c>
-      <c r="J54" s="75" t="n"/>
-      <c r="K54" s="75" t="n"/>
-      <c r="L54" s="74">
-        <f>IF(Eva!L54="","",Eva!L54)</f>
-        <v/>
-      </c>
-      <c r="M54" s="75" t="n"/>
-      <c r="N54" s="75" t="n"/>
-      <c r="O54" s="74">
-        <f>IF(Eva!O54="","",Eva!O54)</f>
-        <v/>
-      </c>
-      <c r="P54" s="75" t="n"/>
-      <c r="Q54" s="75" t="n"/>
-      <c r="R54" s="74">
-        <f>IF(Eva!R54="","",Eva!R54)</f>
-        <v/>
-      </c>
-      <c r="S54" s="75" t="n"/>
-      <c r="T54" s="75" t="n"/>
-      <c r="U54" s="74">
-        <f>IF(Eva!U54="","",Eva!U54)</f>
-        <v/>
-      </c>
-      <c r="V54" s="75" t="n"/>
-      <c r="W54" s="75" t="n"/>
-      <c r="X54" s="74">
-        <f>IF(Eva!X54="","",Eva!X54)</f>
-        <v/>
-      </c>
-      <c r="Y54" s="75" t="n"/>
-      <c r="Z54" s="75" t="n"/>
-      <c r="AA54" s="74">
-        <f>IF(Eva!AA54="","",Eva!AA54)</f>
-        <v/>
-      </c>
-      <c r="AB54" s="75" t="n"/>
-      <c r="AC54" s="75" t="n"/>
-      <c r="AD54" s="74">
-        <f>IF(Eva!AD54="","",Eva!AD54)</f>
-        <v/>
-      </c>
-      <c r="AE54" s="75" t="n"/>
-      <c r="AF54" s="75" t="n"/>
-      <c r="AG54" s="74">
-        <f>IF(Eva!AG54="","",Eva!AG54)</f>
-        <v/>
-      </c>
-      <c r="AH54" s="75" t="n"/>
-      <c r="AI54" s="75" t="n"/>
-      <c r="AJ54" s="74">
-        <f>IF(Eva!AJ54="","",Eva!AJ54)</f>
-        <v/>
-      </c>
-      <c r="AK54" s="75" t="n"/>
-      <c r="AL54" s="75" t="n"/>
-      <c r="AM54" s="74">
-        <f>IF(Eva!AM54="","",Eva!AM54)</f>
-        <v/>
-      </c>
-      <c r="AN54" s="75" t="n"/>
-      <c r="AO54" s="75" t="n"/>
-      <c r="AP54" s="74">
-        <f>IF(Eva!AP54="","",Eva!AP54)</f>
-        <v/>
-      </c>
-      <c r="AQ54" s="75" t="n"/>
-      <c r="AR54" s="75" t="n"/>
-      <c r="AS54" s="74">
-        <f>IF(Eva!AS54="","",Eva!AS54)</f>
-        <v/>
-      </c>
-      <c r="AT54" s="75" t="n"/>
-      <c r="AU54" s="75" t="n"/>
-      <c r="AV54" s="74">
-        <f>IF(Eva!AV54="","",Eva!AV54)</f>
-        <v/>
-      </c>
-      <c r="AW54" s="75" t="n"/>
-      <c r="AX54" s="76" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="67" t="inlineStr">
-        <is>
-          <t>MANDIBLE</t>
-        </is>
-      </c>
-      <c r="B55" s="68" t="n"/>
-      <c r="C55" s="69" t="n">
-        <v>48</v>
-      </c>
-      <c r="D55" s="70" t="n"/>
-      <c r="E55" s="70" t="n"/>
-      <c r="F55" s="69" t="n">
-        <v>47</v>
-      </c>
-      <c r="G55" s="70" t="n"/>
-      <c r="H55" s="70" t="n"/>
-      <c r="I55" s="69" t="n">
-        <v>46</v>
-      </c>
-      <c r="J55" s="70" t="n"/>
-      <c r="K55" s="70" t="n"/>
-      <c r="L55" s="69" t="n">
-        <v>45</v>
-      </c>
-      <c r="M55" s="70" t="n"/>
-      <c r="N55" s="70" t="n"/>
-      <c r="O55" s="69" t="n">
-        <v>44</v>
-      </c>
-      <c r="P55" s="70" t="n"/>
-      <c r="Q55" s="70" t="n"/>
-      <c r="R55" s="69" t="n">
-        <v>43</v>
-      </c>
-      <c r="S55" s="70" t="n"/>
-      <c r="T55" s="70" t="n"/>
-      <c r="U55" s="69" t="n">
-        <v>42</v>
-      </c>
-      <c r="V55" s="70" t="n"/>
-      <c r="W55" s="70" t="n"/>
-      <c r="X55" s="69" t="n">
-        <v>41</v>
-      </c>
-      <c r="Y55" s="70" t="n"/>
-      <c r="Z55" s="70" t="n"/>
-      <c r="AA55" s="69" t="n">
-        <v>31</v>
-      </c>
-      <c r="AB55" s="70" t="n"/>
-      <c r="AC55" s="70" t="n"/>
-      <c r="AD55" s="69" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE55" s="70" t="n"/>
-      <c r="AF55" s="70" t="n"/>
-      <c r="AG55" s="69" t="n">
-        <v>33</v>
-      </c>
-      <c r="AH55" s="70" t="n"/>
-      <c r="AI55" s="70" t="n"/>
-      <c r="AJ55" s="69" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK55" s="70" t="n"/>
-      <c r="AL55" s="70" t="n"/>
-      <c r="AM55" s="69" t="n">
-        <v>35</v>
-      </c>
-      <c r="AN55" s="70" t="n"/>
-      <c r="AO55" s="70" t="n"/>
-      <c r="AP55" s="69" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ55" s="70" t="n"/>
-      <c r="AR55" s="70" t="n"/>
-      <c r="AS55" s="69" t="n">
-        <v>37</v>
-      </c>
-      <c r="AT55" s="70" t="n"/>
-      <c r="AU55" s="70" t="n"/>
-      <c r="AV55" s="69" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW55" s="70" t="n"/>
-      <c r="AX55" s="71" t="n"/>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="72" t="inlineStr">
-        <is>
-          <t>X / I</t>
-        </is>
-      </c>
-      <c r="B56" s="73" t="n"/>
-      <c r="C56" s="74">
+    <row r="56" hidden="1">
+      <c r="C56">
         <f>IF(Eva!C56="","",Eva!C56)</f>
         <v/>
       </c>
-      <c r="D56" s="75" t="n"/>
-      <c r="E56" s="75" t="n"/>
-      <c r="F56" s="74">
+      <c r="F56">
         <f>IF(Eva!F56="","",Eva!F56)</f>
         <v/>
       </c>
-      <c r="G56" s="75" t="n"/>
-      <c r="H56" s="75" t="n"/>
-      <c r="I56" s="74">
+      <c r="I56">
         <f>IF(Eva!I56="","",Eva!I56)</f>
         <v/>
       </c>
-      <c r="J56" s="75" t="n"/>
-      <c r="K56" s="75" t="n"/>
-      <c r="L56" s="74">
+      <c r="L56">
         <f>IF(Eva!L56="","",Eva!L56)</f>
         <v/>
       </c>
-      <c r="M56" s="75" t="n"/>
-      <c r="N56" s="75" t="n"/>
-      <c r="O56" s="74">
+      <c r="O56">
         <f>IF(Eva!O56="","",Eva!O56)</f>
         <v/>
       </c>
-      <c r="P56" s="75" t="n"/>
-      <c r="Q56" s="75" t="n"/>
-      <c r="R56" s="74">
+      <c r="R56">
         <f>IF(Eva!R56="","",Eva!R56)</f>
         <v/>
       </c>
-      <c r="S56" s="75" t="n"/>
-      <c r="T56" s="75" t="n"/>
-      <c r="U56" s="74">
+      <c r="U56">
         <f>IF(Eva!U56="","",Eva!U56)</f>
         <v/>
       </c>
-      <c r="V56" s="75" t="n"/>
-      <c r="W56" s="75" t="n"/>
-      <c r="X56" s="74">
+      <c r="X56">
         <f>IF(Eva!X56="","",Eva!X56)</f>
         <v/>
       </c>
-      <c r="Y56" s="75" t="n"/>
-      <c r="Z56" s="75" t="n"/>
-      <c r="AA56" s="74">
+      <c r="AA56">
         <f>IF(Eva!AA56="","",Eva!AA56)</f>
         <v/>
       </c>
-      <c r="AB56" s="75" t="n"/>
-      <c r="AC56" s="75" t="n"/>
-      <c r="AD56" s="74">
+      <c r="AD56">
         <f>IF(Eva!AD56="","",Eva!AD56)</f>
         <v/>
       </c>
-      <c r="AE56" s="75" t="n"/>
-      <c r="AF56" s="75" t="n"/>
-      <c r="AG56" s="74">
+      <c r="AG56">
         <f>IF(Eva!AG56="","",Eva!AG56)</f>
         <v/>
       </c>
-      <c r="AH56" s="75" t="n"/>
-      <c r="AI56" s="75" t="n"/>
-      <c r="AJ56" s="74">
+      <c r="AJ56">
         <f>IF(Eva!AJ56="","",Eva!AJ56)</f>
         <v/>
       </c>
-      <c r="AK56" s="75" t="n"/>
-      <c r="AL56" s="75" t="n"/>
-      <c r="AM56" s="74">
+      <c r="AM56">
         <f>IF(Eva!AM56="","",Eva!AM56)</f>
         <v/>
       </c>
-      <c r="AN56" s="75" t="n"/>
-      <c r="AO56" s="75" t="n"/>
-      <c r="AP56" s="74">
+      <c r="AP56">
         <f>IF(Eva!AP56="","",Eva!AP56)</f>
         <v/>
       </c>
-      <c r="AQ56" s="75" t="n"/>
-      <c r="AR56" s="75" t="n"/>
-      <c r="AS56" s="74">
+      <c r="AS56">
         <f>IF(Eva!AS56="","",Eva!AS56)</f>
         <v/>
       </c>
-      <c r="AT56" s="75" t="n"/>
-      <c r="AU56" s="75" t="n"/>
-      <c r="AV56" s="74">
+      <c r="AV56">
         <f>IF(Eva!AV56="","",Eva!AV56)</f>
         <v/>
       </c>
-      <c r="AW56" s="75" t="n"/>
-      <c r="AX56" s="76" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="152">
-    <mergeCell ref="I54:K54"/>
+  <mergeCells count="83">
     <mergeCell ref="AD28:AF28"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="I56:K56"/>
     <mergeCell ref="A32:A36"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="O56:Q56"/>
     <mergeCell ref="L9:N9"/>
     <mergeCell ref="AV9:AX9"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="A56:B56"/>
     <mergeCell ref="I50:K50"/>
-    <mergeCell ref="AD55:AF55"/>
     <mergeCell ref="X31:Z31"/>
     <mergeCell ref="U50:W50"/>
     <mergeCell ref="AD9:AF9"/>
     <mergeCell ref="AJ31:AL31"/>
-    <mergeCell ref="A53:B53"/>
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="O9:Q9"/>
     <mergeCell ref="A28:B28"/>
@@ -23539,7 +22253,6 @@
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="AM9:AO9"/>
     <mergeCell ref="F50:H50"/>
-    <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="O50:Q50"/>
     <mergeCell ref="AS2:AX2"/>
     <mergeCell ref="L50:N50"/>
@@ -23547,113 +22260,53 @@
     <mergeCell ref="AA31:AC31"/>
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="U54:W54"/>
-    <mergeCell ref="U55:W55"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="X9:Z9"/>
     <mergeCell ref="R9:T9"/>
-    <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="AJ50:AL50"/>
-    <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="AV50:AX50"/>
-    <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="L28:N28"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="R31:T31"/>
-    <mergeCell ref="AP54:AR54"/>
-    <mergeCell ref="AV55:AX55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="AP55:AR55"/>
-    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="C50:E50"/>
     <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="I53:K53"/>
     <mergeCell ref="C1:Z1"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="AA53:AC53"/>
     <mergeCell ref="AH2:AN2"/>
     <mergeCell ref="AP31:AR31"/>
-    <mergeCell ref="L55:N55"/>
-    <mergeCell ref="U53:W53"/>
-    <mergeCell ref="X55:Z55"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="I55:K55"/>
     <mergeCell ref="U28:W28"/>
-    <mergeCell ref="L54:N54"/>
-    <mergeCell ref="AV53:AX53"/>
-    <mergeCell ref="AD54:AF54"/>
     <mergeCell ref="R50:T50"/>
     <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="AO2:AR2"/>
-    <mergeCell ref="R56:T56"/>
     <mergeCell ref="AA50:AC50"/>
-    <mergeCell ref="L56:N56"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="AA55:AC55"/>
     <mergeCell ref="AM50:AO50"/>
-    <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C52:AX52"/>
-    <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="I31:K31"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="AG55:AI55"/>
-    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="U31:W31"/>
-    <mergeCell ref="O53:Q53"/>
     <mergeCell ref="R28:T28"/>
-    <mergeCell ref="L53:N53"/>
     <mergeCell ref="AS31:AU31"/>
-    <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="A44:A49"/>
-    <mergeCell ref="C54:E54"/>
     <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="O54:Q54"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="AD31:AF31"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="U56:W56"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="F2:T2"/>
-    <mergeCell ref="AA54:AC54"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="AJ53:AL53"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="U2:V2"/>
-    <mergeCell ref="AM54:AO54"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="AA56:AC56"/>
     <mergeCell ref="L31:N31"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="C53:E53"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="X56:Z56"/>
     <mergeCell ref="U9:W9"/>
     <mergeCell ref="AV31:AX31"/>
-    <mergeCell ref="AP56:AR56"/>
-    <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="F54:H54"/>
     <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="W2:AD2"/>
     <mergeCell ref="AA1:AX1"/>
     <mergeCell ref="AA9:AC9"/>
-    <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="A31:B31"/>
